--- a/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\github_corrigido_dashboard_obrasRev1\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38D3F51D-200A-4500-8FFE-9E4651753B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE97603-A5C3-4271-951A-6B91FEF1BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -403,7 +403,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -432,13 +432,32 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -453,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -466,12 +485,309 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="22">
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b/>
@@ -501,33 +817,33 @@
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Bloco"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Tipo_Extensao"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Extensao_Planejada_m"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Extensao_Executada_m" dataDxfId="0"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Extensao_Executada_m" dataDxfId="21"/>
     <tableColumn id="6" xr3:uid="{6BB83A0A-92EF-4D0A-89EF-C6F503D3B7CB}" name="PV"/>
     <tableColumn id="7" xr3:uid="{16D84CF1-E783-4000-847C-89A0C712ADDD}" name="Profundidade_PV_m"/>
     <tableColumn id="8" xr3:uid="{CCC7E282-906C-4070-A05D-0C12B88259D5}" name="Economias prevista"/>
     <tableColumn id="9" xr3:uid="{141F879B-3CB0-49C0-B696-841DCF5BEDB4}" name="Economias Recebidas"/>
     <tableColumn id="10" xr3:uid="{C0195FBC-3466-4999-8402-DBEE3F7978C5}" name="produção março 2025"/>
-    <tableColumn id="11" xr3:uid="{9560D17C-B2DC-4B87-9E68-8B0334D1A5F1}" name="produção Abril 2025"/>
-    <tableColumn id="12" xr3:uid="{2CC935E5-AE57-401D-B0B9-16AA7CE547C9}" name="produção Maio 2025"/>
-    <tableColumn id="13" xr3:uid="{D4A32E48-58F4-4347-A22F-3EC617F115ED}" name="produção Junho 2025"/>
-    <tableColumn id="14" xr3:uid="{FD08EE1C-24D6-435D-BFB5-DE8525365C0B}" name="produção Julho 2025"/>
-    <tableColumn id="15" xr3:uid="{0E3143BC-7DD4-42C2-9632-F4C84435B02B}" name="produção Agosto 2025"/>
-    <tableColumn id="16" xr3:uid="{1A595E00-BFE2-4CB2-88ED-7BAD72BCDC1D}" name="produção Setembro 2025"/>
-    <tableColumn id="17" xr3:uid="{8A59EA87-2170-4E3A-8757-7A5746B89A12}" name="produção Outubro 2025"/>
-    <tableColumn id="18" xr3:uid="{E9DBE3BD-B4AB-4971-9574-0FF7FA5803DD}" name="produção Novembro 2025"/>
-    <tableColumn id="19" xr3:uid="{1D73A10C-A301-48D5-96BD-32A1DB452BFA}" name="produção Dezembro 2025"/>
-    <tableColumn id="20" xr3:uid="{D518955F-FB3C-479D-B0A0-C858B4EE0CF2}" name="produção Janeiro 2026"/>
-    <tableColumn id="21" xr3:uid="{2643BDE6-67AE-4701-982B-BBA15C7E24D7}" name="produção Fevereiro 2026"/>
-    <tableColumn id="22" xr3:uid="{25EDB414-06AF-467B-BEAF-CBFA34B0E3FE}" name="produção Março 2026"/>
-    <tableColumn id="23" xr3:uid="{ACC94B2B-3C05-4E69-BC1D-31E6BC6BF41F}" name="produção Abril 2026"/>
-    <tableColumn id="24" xr3:uid="{434478D3-9DE1-40FA-BAE2-5B310B23261F}" name="produção Maio 2026"/>
-    <tableColumn id="25" xr3:uid="{F969BF45-8403-448D-ADFE-D1E4B359F4FC}" name="produção Junho 2026"/>
-    <tableColumn id="26" xr3:uid="{3190B8C0-F461-4D5F-9042-D3DA4392D852}" name="produção Julho 2026"/>
-    <tableColumn id="27" xr3:uid="{1296E3F8-3AB4-4A3B-8378-6F3E29C9E2CA}" name="produção Agosto 2026"/>
-    <tableColumn id="28" xr3:uid="{8DDEDC24-3476-4DA6-AF25-63FF4B848894}" name="produção Setembro 2026"/>
-    <tableColumn id="29" xr3:uid="{CCF3E2AD-2E1F-42BE-8A16-B57AE967B62C}" name="produção Outubro 2026"/>
-    <tableColumn id="30" xr3:uid="{AEDAF9C8-4CB3-46E6-9E05-502560E49621}" name="produção Novembro 2026"/>
-    <tableColumn id="31" xr3:uid="{224F4735-9E51-4718-AB11-1FC679A00B87}" name="produção Dezembro 2026"/>
+    <tableColumn id="11" xr3:uid="{9560D17C-B2DC-4B87-9E68-8B0334D1A5F1}" name="produção Abril 2025" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{2CC935E5-AE57-401D-B0B9-16AA7CE547C9}" name="produção Maio 2025" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{D4A32E48-58F4-4347-A22F-3EC617F115ED}" name="produção Junho 2025" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{FD08EE1C-24D6-435D-BFB5-DE8525365C0B}" name="produção Julho 2025" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{0E3143BC-7DD4-42C2-9632-F4C84435B02B}" name="produção Agosto 2025" dataDxfId="16"/>
+    <tableColumn id="16" xr3:uid="{1A595E00-BFE2-4CB2-88ED-7BAD72BCDC1D}" name="produção Setembro 2025" dataDxfId="15"/>
+    <tableColumn id="17" xr3:uid="{8A59EA87-2170-4E3A-8757-7A5746B89A12}" name="produção Outubro 2025" dataDxfId="14"/>
+    <tableColumn id="18" xr3:uid="{E9DBE3BD-B4AB-4971-9574-0FF7FA5803DD}" name="produção Novembro 2025" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{1D73A10C-A301-48D5-96BD-32A1DB452BFA}" name="produção Dezembro 2025" dataDxfId="12"/>
+    <tableColumn id="20" xr3:uid="{D518955F-FB3C-479D-B0A0-C858B4EE0CF2}" name="produção Janeiro 2026" dataDxfId="11"/>
+    <tableColumn id="21" xr3:uid="{2643BDE6-67AE-4701-982B-BBA15C7E24D7}" name="produção Fevereiro 2026" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{25EDB414-06AF-467B-BEAF-CBFA34B0E3FE}" name="produção Março 2026" dataDxfId="9"/>
+    <tableColumn id="23" xr3:uid="{ACC94B2B-3C05-4E69-BC1D-31E6BC6BF41F}" name="produção Abril 2026" dataDxfId="8"/>
+    <tableColumn id="24" xr3:uid="{434478D3-9DE1-40FA-BAE2-5B310B23261F}" name="produção Maio 2026" dataDxfId="7"/>
+    <tableColumn id="25" xr3:uid="{F969BF45-8403-448D-ADFE-D1E4B359F4FC}" name="produção Junho 2026" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{3190B8C0-F461-4D5F-9042-D3DA4392D852}" name="produção Julho 2026" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{1296E3F8-3AB4-4A3B-8378-6F3E29C9E2CA}" name="produção Agosto 2026" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{8DDEDC24-3476-4DA6-AF25-63FF4B848894}" name="produção Setembro 2026" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{CCF3E2AD-2E1F-42BE-8A16-B57AE967B62C}" name="produção Outubro 2026" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{AEDAF9C8-4CB3-46E6-9E05-502560E49621}" name="produção Novembro 2026" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{224F4735-9E51-4718-AB11-1FC679A00B87}" name="produção Dezembro 2026" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -831,7 +1147,11 @@
     <col min="8" max="8" width="8.88671875" customWidth="1"/>
     <col min="9" max="9" width="26.5546875" customWidth="1"/>
     <col min="10" max="10" width="10.44140625" customWidth="1"/>
-    <col min="11" max="32" width="7.6640625" customWidth="1"/>
+    <col min="11" max="12" width="7.6640625" customWidth="1"/>
+    <col min="13" max="13" width="14" customWidth="1"/>
+    <col min="14" max="15" width="7.6640625" customWidth="1"/>
+    <col min="16" max="16" width="14.5546875" customWidth="1"/>
+    <col min="17" max="32" width="7.6640625" customWidth="1"/>
     <col min="33" max="33" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -955,17 +1275,29 @@
       <c r="G2">
         <v>10</v>
       </c>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4">
+      <c r="L2" s="6"/>
+      <c r="M2" s="8">
         <v>162.59</v>
       </c>
-      <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
-      <c r="P2" s="4"/>
-      <c r="Q2" s="4"/>
-      <c r="R2" s="4"/>
-      <c r="S2" s="4"/>
-      <c r="T2" s="4"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
       <c r="AG2" t="s">
         <v>114</v>
       </c>
@@ -986,17 +1318,29 @@
       <c r="F3" s="5">
         <v>6.19</v>
       </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4">
+      <c r="L3" s="6"/>
+      <c r="M3" s="8">
         <v>6.19</v>
       </c>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="4"/>
-      <c r="Q3" s="4"/>
-      <c r="R3" s="4"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="4"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
+      <c r="AA3" s="6"/>
+      <c r="AB3" s="6"/>
+      <c r="AC3" s="6"/>
+      <c r="AD3" s="6"/>
+      <c r="AE3" s="6"/>
+      <c r="AF3" s="6"/>
       <c r="AG3" t="s">
         <v>114</v>
       </c>
@@ -1017,19 +1361,31 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4">
+      <c r="L4" s="6"/>
+      <c r="M4" s="8">
         <v>47.94</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="8">
         <v>11.7</v>
       </c>
-      <c r="O4" s="4"/>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="4"/>
-      <c r="R4" s="4"/>
-      <c r="S4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
+      <c r="AA4" s="6"/>
+      <c r="AB4" s="6"/>
+      <c r="AC4" s="6"/>
+      <c r="AD4" s="6"/>
+      <c r="AE4" s="6"/>
+      <c r="AF4" s="6"/>
       <c r="AG4" t="s">
         <v>114</v>
       </c>
@@ -1050,17 +1406,29 @@
       <c r="F5" s="5">
         <v>47.5</v>
       </c>
-      <c r="L5" s="4">
+      <c r="L5" s="8">
         <v>47.5</v>
       </c>
-      <c r="M5" s="4"/>
-      <c r="N5" s="4"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="4"/>
-      <c r="Q5" s="4"/>
-      <c r="R5" s="4"/>
-      <c r="S5" s="4"/>
-      <c r="T5" s="4"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
+      <c r="AA5" s="6"/>
+      <c r="AB5" s="6"/>
+      <c r="AC5" s="6"/>
+      <c r="AD5" s="6"/>
+      <c r="AE5" s="6"/>
+      <c r="AF5" s="6"/>
       <c r="AG5" t="s">
         <v>114</v>
       </c>
@@ -1081,17 +1449,29 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4">
+      <c r="L6" s="6"/>
+      <c r="M6" s="8">
         <v>105.6</v>
       </c>
-      <c r="N6" s="4"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
-      <c r="R6" s="4"/>
-      <c r="S6" s="4"/>
-      <c r="T6" s="4"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="6"/>
+      <c r="AB6" s="6"/>
+      <c r="AC6" s="6"/>
+      <c r="AD6" s="6"/>
+      <c r="AE6" s="6"/>
+      <c r="AF6" s="6"/>
       <c r="AG6" t="s">
         <v>114</v>
       </c>
@@ -1112,17 +1492,29 @@
       <c r="F7" s="5">
         <v>2.2999999999999998</v>
       </c>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-      <c r="N7" s="4">
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="8">
         <v>2.2999999999999998</v>
       </c>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
+      <c r="AA7" s="6"/>
+      <c r="AB7" s="6"/>
+      <c r="AC7" s="6"/>
+      <c r="AD7" s="6"/>
+      <c r="AE7" s="6"/>
+      <c r="AF7" s="6"/>
       <c r="AG7" t="s">
         <v>114</v>
       </c>
@@ -1146,19 +1538,31 @@
       <c r="G8">
         <v>2</v>
       </c>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4">
+      <c r="L8" s="6"/>
+      <c r="M8" s="8">
         <v>66.83</v>
       </c>
-      <c r="N8" s="4">
+      <c r="N8" s="8">
         <v>64.599999999999994</v>
       </c>
-      <c r="O8" s="4"/>
-      <c r="P8" s="4"/>
-      <c r="Q8" s="4"/>
-      <c r="R8" s="4"/>
-      <c r="S8" s="4"/>
-      <c r="T8" s="4"/>
+      <c r="O8" s="6"/>
+      <c r="P8" s="6"/>
+      <c r="Q8" s="6"/>
+      <c r="R8" s="6"/>
+      <c r="S8" s="6"/>
+      <c r="T8" s="6"/>
+      <c r="U8" s="6"/>
+      <c r="V8" s="6"/>
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6"/>
+      <c r="Z8" s="6"/>
+      <c r="AA8" s="6"/>
+      <c r="AB8" s="6"/>
+      <c r="AC8" s="6"/>
+      <c r="AD8" s="6"/>
+      <c r="AE8" s="6"/>
+      <c r="AF8" s="6"/>
       <c r="AG8" t="s">
         <v>114</v>
       </c>
@@ -1182,15 +1586,27 @@
       <c r="J9">
         <v>2706</v>
       </c>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-      <c r="N9" s="4"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
-      <c r="R9" s="4"/>
-      <c r="S9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6"/>
+      <c r="O9" s="6"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6"/>
+      <c r="R9" s="6"/>
+      <c r="S9" s="6"/>
+      <c r="T9" s="6"/>
+      <c r="U9" s="6"/>
+      <c r="V9" s="6"/>
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6"/>
+      <c r="Z9" s="6"/>
+      <c r="AA9" s="6"/>
+      <c r="AB9" s="6"/>
+      <c r="AC9" s="6"/>
+      <c r="AD9" s="6"/>
+      <c r="AE9" s="6"/>
+      <c r="AF9" s="6"/>
       <c r="AG9" t="s">
         <v>114</v>
       </c>
@@ -1209,7 +1625,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="5">
-        <v>523.63</v>
+        <v>523.65499999999997</v>
       </c>
       <c r="G10">
         <v>47</v>
@@ -1223,19 +1639,31 @@
       <c r="J10">
         <v>599</v>
       </c>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4">
+      <c r="L10" s="6"/>
+      <c r="M10" s="6"/>
+      <c r="N10" s="8">
         <v>217.93</v>
       </c>
-      <c r="O10" s="4">
+      <c r="O10" s="8">
         <v>305.72500000000002</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="4"/>
-      <c r="T10" s="4"/>
+      <c r="P10" s="6"/>
+      <c r="Q10" s="6"/>
+      <c r="R10" s="6"/>
+      <c r="S10" s="6"/>
+      <c r="T10" s="6"/>
+      <c r="U10" s="6"/>
+      <c r="V10" s="6"/>
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6"/>
+      <c r="Z10" s="6"/>
+      <c r="AA10" s="6"/>
+      <c r="AB10" s="6"/>
+      <c r="AC10" s="6"/>
+      <c r="AD10" s="6"/>
+      <c r="AE10" s="6"/>
+      <c r="AF10" s="6"/>
       <c r="AG10" t="s">
         <v>114</v>
       </c>
@@ -1253,15 +1681,27 @@
       <c r="E11">
         <v>469.7</v>
       </c>
-      <c r="L11" s="4"/>
-      <c r="M11" s="4"/>
-      <c r="N11" s="4"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="4"/>
-      <c r="Q11" s="4"/>
-      <c r="R11" s="4"/>
-      <c r="S11" s="4"/>
-      <c r="T11" s="4"/>
+      <c r="L11" s="6"/>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6"/>
+      <c r="O11" s="6"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6"/>
+      <c r="R11" s="6"/>
+      <c r="S11" s="6"/>
+      <c r="T11" s="6"/>
+      <c r="U11" s="6"/>
+      <c r="V11" s="6"/>
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6"/>
+      <c r="Z11" s="6"/>
+      <c r="AA11" s="6"/>
+      <c r="AB11" s="6"/>
+      <c r="AC11" s="6"/>
+      <c r="AD11" s="6"/>
+      <c r="AE11" s="6"/>
+      <c r="AF11" s="6"/>
       <c r="AG11" t="s">
         <v>114</v>
       </c>
@@ -1288,19 +1728,31 @@
       <c r="J12">
         <v>595</v>
       </c>
-      <c r="L12" s="4"/>
-      <c r="M12" s="4"/>
-      <c r="N12" s="4"/>
-      <c r="O12" s="4">
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+      <c r="O12" s="8">
         <v>134.10499999999999</v>
       </c>
-      <c r="P12" s="4">
+      <c r="P12" s="8">
         <v>208.60499999999999</v>
       </c>
-      <c r="Q12" s="4"/>
-      <c r="R12" s="4"/>
-      <c r="S12" s="4"/>
-      <c r="T12" s="4"/>
+      <c r="Q12" s="6"/>
+      <c r="R12" s="6"/>
+      <c r="S12" s="6"/>
+      <c r="T12" s="6"/>
+      <c r="U12" s="6"/>
+      <c r="V12" s="6"/>
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6"/>
+      <c r="Z12" s="6"/>
+      <c r="AA12" s="6"/>
+      <c r="AB12" s="6"/>
+      <c r="AC12" s="6"/>
+      <c r="AD12" s="6"/>
+      <c r="AE12" s="6"/>
+      <c r="AF12" s="6"/>
       <c r="AG12" t="s">
         <v>114</v>
       </c>
@@ -1321,15 +1773,27 @@
       <c r="F13" s="5">
         <v>0</v>
       </c>
-      <c r="L13" s="4"/>
-      <c r="M13" s="4"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="4"/>
-      <c r="S13" s="4"/>
-      <c r="T13" s="4"/>
+      <c r="L13" s="6"/>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6"/>
+      <c r="O13" s="6"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6"/>
+      <c r="R13" s="6"/>
+      <c r="S13" s="6"/>
+      <c r="T13" s="6"/>
+      <c r="U13" s="6"/>
+      <c r="V13" s="6"/>
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6"/>
+      <c r="Z13" s="6"/>
+      <c r="AA13" s="6"/>
+      <c r="AB13" s="6"/>
+      <c r="AC13" s="6"/>
+      <c r="AD13" s="6"/>
+      <c r="AE13" s="6"/>
+      <c r="AF13" s="6"/>
       <c r="AG13" t="s">
         <v>114</v>
       </c>
@@ -1356,17 +1820,29 @@
       <c r="J14">
         <v>109</v>
       </c>
-      <c r="L14" s="4"/>
-      <c r="M14" s="4"/>
-      <c r="N14" s="4"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="4">
+      <c r="L14" s="6"/>
+      <c r="M14" s="6"/>
+      <c r="N14" s="6"/>
+      <c r="O14" s="6"/>
+      <c r="P14" s="8">
         <v>231.85</v>
       </c>
-      <c r="Q14" s="4"/>
-      <c r="R14" s="4"/>
-      <c r="S14" s="4"/>
-      <c r="T14" s="4"/>
+      <c r="Q14" s="6"/>
+      <c r="R14" s="6"/>
+      <c r="S14" s="6"/>
+      <c r="T14" s="6"/>
+      <c r="U14" s="6"/>
+      <c r="V14" s="6"/>
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6"/>
+      <c r="Z14" s="6"/>
+      <c r="AA14" s="6"/>
+      <c r="AB14" s="6"/>
+      <c r="AC14" s="6"/>
+      <c r="AD14" s="6"/>
+      <c r="AE14" s="6"/>
+      <c r="AF14" s="6"/>
       <c r="AG14" t="s">
         <v>114</v>
       </c>
@@ -1387,17 +1863,29 @@
       <c r="F15" s="5">
         <v>4.0599999999999996</v>
       </c>
-      <c r="L15" s="4"/>
-      <c r="M15" s="4"/>
-      <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="4">
+      <c r="L15" s="6"/>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6"/>
+      <c r="O15" s="6"/>
+      <c r="P15" s="8">
         <v>4.0599999999999996</v>
       </c>
-      <c r="Q15" s="4"/>
-      <c r="R15" s="4"/>
-      <c r="S15" s="4"/>
-      <c r="T15" s="4"/>
+      <c r="Q15" s="6"/>
+      <c r="R15" s="6"/>
+      <c r="S15" s="6"/>
+      <c r="T15" s="6"/>
+      <c r="U15" s="6"/>
+      <c r="V15" s="6"/>
+      <c r="W15" s="6"/>
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6"/>
+      <c r="Z15" s="6"/>
+      <c r="AA15" s="6"/>
+      <c r="AB15" s="6"/>
+      <c r="AC15" s="6"/>
+      <c r="AD15" s="6"/>
+      <c r="AE15" s="6"/>
+      <c r="AF15" s="6"/>
       <c r="AG15" t="s">
         <v>114</v>
       </c>
@@ -1424,19 +1912,31 @@
       <c r="J16">
         <v>3229</v>
       </c>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4">
+      <c r="L16" s="6"/>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6"/>
+      <c r="O16" s="6"/>
+      <c r="P16" s="8">
         <v>132.27000000000001</v>
       </c>
-      <c r="Q16" s="4">
+      <c r="Q16" s="8">
         <v>235.44</v>
       </c>
-      <c r="R16" s="4"/>
-      <c r="S16" s="4"/>
-      <c r="T16" s="4"/>
+      <c r="R16" s="6"/>
+      <c r="S16" s="6"/>
+      <c r="T16" s="6"/>
+      <c r="U16" s="6"/>
+      <c r="V16" s="6"/>
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6"/>
+      <c r="Z16" s="6"/>
+      <c r="AA16" s="6"/>
+      <c r="AB16" s="6"/>
+      <c r="AC16" s="6"/>
+      <c r="AD16" s="6"/>
+      <c r="AE16" s="6"/>
+      <c r="AF16" s="6"/>
       <c r="AG16" t="s">
         <v>114</v>
       </c>
@@ -1454,17 +1954,29 @@
       <c r="E17">
         <v>232.1</v>
       </c>
-      <c r="L17" s="4"/>
-      <c r="M17" s="4"/>
-      <c r="N17" s="4"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="4"/>
-      <c r="Q17" s="4">
+      <c r="L17" s="6"/>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6"/>
+      <c r="O17" s="6"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="9">
         <v>154.93</v>
       </c>
-      <c r="R17" s="4"/>
-      <c r="S17" s="4"/>
-      <c r="T17" s="4"/>
+      <c r="R17" s="6"/>
+      <c r="S17" s="6"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="6"/>
+      <c r="V17" s="6"/>
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6"/>
+      <c r="Z17" s="6"/>
+      <c r="AA17" s="6"/>
+      <c r="AB17" s="6"/>
+      <c r="AC17" s="6"/>
+      <c r="AD17" s="6"/>
+      <c r="AE17" s="6"/>
+      <c r="AF17" s="6"/>
       <c r="AG17" t="s">
         <v>114</v>
       </c>
@@ -1491,17 +2003,29 @@
       <c r="J18">
         <v>42</v>
       </c>
-      <c r="L18" s="4"/>
-      <c r="M18" s="4"/>
-      <c r="N18" s="4"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="4"/>
-      <c r="Q18" s="4">
+      <c r="L18" s="6"/>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6">
         <v>253.94</v>
       </c>
-      <c r="R18" s="4"/>
-      <c r="S18" s="4"/>
-      <c r="T18" s="4"/>
+      <c r="R18" s="6"/>
+      <c r="S18" s="6"/>
+      <c r="T18" s="6"/>
+      <c r="U18" s="6"/>
+      <c r="V18" s="6"/>
+      <c r="W18" s="6"/>
+      <c r="X18" s="6"/>
+      <c r="Y18" s="6"/>
+      <c r="Z18" s="6"/>
+      <c r="AA18" s="6"/>
+      <c r="AB18" s="6"/>
+      <c r="AC18" s="6"/>
+      <c r="AD18" s="6"/>
+      <c r="AE18" s="6"/>
+      <c r="AF18" s="6"/>
       <c r="AG18" t="s">
         <v>114</v>
       </c>
@@ -1522,21 +2046,33 @@
       <c r="F19" s="5">
         <v>445.46</v>
       </c>
-      <c r="L19" s="4"/>
-      <c r="M19" s="4"/>
-      <c r="N19" s="4"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="4">
+      <c r="L19" s="6"/>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6">
         <v>242.97</v>
       </c>
-      <c r="Q19" s="4">
+      <c r="Q19" s="6">
         <v>148.49</v>
       </c>
-      <c r="R19" s="4"/>
-      <c r="S19" s="4"/>
-      <c r="T19" s="4">
+      <c r="R19" s="6"/>
+      <c r="S19" s="6"/>
+      <c r="T19" s="6">
         <v>54</v>
       </c>
+      <c r="U19" s="6"/>
+      <c r="V19" s="6"/>
+      <c r="W19" s="6"/>
+      <c r="X19" s="6"/>
+      <c r="Y19" s="6"/>
+      <c r="Z19" s="6"/>
+      <c r="AA19" s="6"/>
+      <c r="AB19" s="6"/>
+      <c r="AC19" s="6"/>
+      <c r="AD19" s="6"/>
+      <c r="AE19" s="6"/>
+      <c r="AF19" s="6"/>
       <c r="AG19" t="s">
         <v>114</v>
       </c>
@@ -1569,17 +2105,29 @@
       <c r="J20">
         <v>661</v>
       </c>
-      <c r="L20" s="4"/>
-      <c r="M20" s="4"/>
-      <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="4"/>
-      <c r="Q20" s="4"/>
-      <c r="R20" s="4">
+      <c r="L20" s="6"/>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6"/>
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6"/>
+      <c r="R20" s="6">
         <v>192.04</v>
       </c>
-      <c r="S20" s="4"/>
-      <c r="T20" s="4"/>
+      <c r="S20" s="6"/>
+      <c r="T20" s="6"/>
+      <c r="U20" s="6"/>
+      <c r="V20" s="6"/>
+      <c r="W20" s="6"/>
+      <c r="X20" s="6"/>
+      <c r="Y20" s="6"/>
+      <c r="Z20" s="6"/>
+      <c r="AA20" s="6"/>
+      <c r="AB20" s="6"/>
+      <c r="AC20" s="6"/>
+      <c r="AD20" s="6"/>
+      <c r="AE20" s="6"/>
+      <c r="AF20" s="6"/>
       <c r="AG20" t="s">
         <v>114</v>
       </c>
@@ -1600,17 +2148,29 @@
       <c r="F21" s="5">
         <v>19.91</v>
       </c>
-      <c r="L21" s="4"/>
-      <c r="M21" s="4"/>
-      <c r="N21" s="4"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="4"/>
-      <c r="Q21" s="4"/>
-      <c r="R21" s="4">
+      <c r="L21" s="6"/>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6"/>
+      <c r="O21" s="6"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6"/>
+      <c r="R21" s="6">
         <v>19.91</v>
       </c>
-      <c r="S21" s="4"/>
-      <c r="T21" s="4"/>
+      <c r="S21" s="6"/>
+      <c r="T21" s="6"/>
+      <c r="U21" s="6"/>
+      <c r="V21" s="6"/>
+      <c r="W21" s="6"/>
+      <c r="X21" s="6"/>
+      <c r="Y21" s="6"/>
+      <c r="Z21" s="6"/>
+      <c r="AA21" s="6"/>
+      <c r="AB21" s="6"/>
+      <c r="AC21" s="6"/>
+      <c r="AD21" s="6"/>
+      <c r="AE21" s="6"/>
+      <c r="AF21" s="6"/>
       <c r="AG21" t="s">
         <v>114</v>
       </c>
@@ -1637,17 +2197,29 @@
       <c r="J22">
         <v>270</v>
       </c>
-      <c r="L22" s="4"/>
-      <c r="M22" s="4"/>
-      <c r="N22" s="4"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="4"/>
-      <c r="Q22" s="4"/>
-      <c r="R22" s="4">
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6"/>
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="6">
         <v>259.3</v>
       </c>
-      <c r="S22" s="4"/>
-      <c r="T22" s="4"/>
+      <c r="S22" s="6"/>
+      <c r="T22" s="6"/>
+      <c r="U22" s="6"/>
+      <c r="V22" s="6"/>
+      <c r="W22" s="6"/>
+      <c r="X22" s="6"/>
+      <c r="Y22" s="6"/>
+      <c r="Z22" s="6"/>
+      <c r="AA22" s="6"/>
+      <c r="AB22" s="6"/>
+      <c r="AC22" s="6"/>
+      <c r="AD22" s="6"/>
+      <c r="AE22" s="6"/>
+      <c r="AF22" s="6"/>
       <c r="AG22" t="s">
         <v>114</v>
       </c>
@@ -1668,17 +2240,29 @@
       <c r="F23" s="5">
         <v>39.75</v>
       </c>
-      <c r="L23" s="4"/>
-      <c r="M23" s="4"/>
-      <c r="N23" s="4"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="4"/>
-      <c r="Q23" s="4"/>
-      <c r="R23" s="4">
+      <c r="L23" s="6"/>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6"/>
+      <c r="O23" s="6"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="6"/>
+      <c r="R23" s="6">
         <v>39.75</v>
       </c>
-      <c r="S23" s="4"/>
-      <c r="T23" s="4"/>
+      <c r="S23" s="6"/>
+      <c r="T23" s="6"/>
+      <c r="U23" s="6"/>
+      <c r="V23" s="6"/>
+      <c r="W23" s="6"/>
+      <c r="X23" s="6"/>
+      <c r="Y23" s="6"/>
+      <c r="Z23" s="6"/>
+      <c r="AA23" s="6"/>
+      <c r="AB23" s="6"/>
+      <c r="AC23" s="6"/>
+      <c r="AD23" s="6"/>
+      <c r="AE23" s="6"/>
+      <c r="AF23" s="6"/>
       <c r="AG23" t="s">
         <v>114</v>
       </c>
@@ -1699,15 +2283,27 @@
       <c r="I24">
         <v>43</v>
       </c>
-      <c r="L24" s="4"/>
-      <c r="M24" s="4"/>
-      <c r="N24" s="4"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="4"/>
-      <c r="Q24" s="4"/>
-      <c r="R24" s="4"/>
-      <c r="S24" s="4"/>
-      <c r="T24" s="4"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6"/>
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="6"/>
+      <c r="S24" s="6"/>
+      <c r="T24" s="6"/>
+      <c r="U24" s="6"/>
+      <c r="V24" s="6"/>
+      <c r="W24" s="6"/>
+      <c r="X24" s="6"/>
+      <c r="Y24" s="6"/>
+      <c r="Z24" s="6"/>
+      <c r="AA24" s="6"/>
+      <c r="AB24" s="6"/>
+      <c r="AC24" s="6"/>
+      <c r="AD24" s="6"/>
+      <c r="AE24" s="6"/>
+      <c r="AF24" s="6"/>
       <c r="AG24" t="s">
         <v>115</v>
       </c>
@@ -1722,6 +2318,27 @@
       <c r="D25" t="s">
         <v>7</v>
       </c>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="6"/>
+      <c r="R25" s="6"/>
+      <c r="S25" s="6"/>
+      <c r="T25" s="6"/>
+      <c r="U25" s="6"/>
+      <c r="V25" s="6"/>
+      <c r="W25" s="6"/>
+      <c r="X25" s="6"/>
+      <c r="Y25" s="6"/>
+      <c r="Z25" s="6"/>
+      <c r="AA25" s="6"/>
+      <c r="AB25" s="6"/>
+      <c r="AC25" s="6"/>
+      <c r="AD25" s="6"/>
+      <c r="AE25" s="6"/>
+      <c r="AF25" s="6"/>
       <c r="AG25" t="s">
         <v>115</v>
       </c>
@@ -1739,6 +2356,27 @@
       <c r="E26">
         <v>137</v>
       </c>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6"/>
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="6"/>
+      <c r="S26" s="6"/>
+      <c r="T26" s="6"/>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+      <c r="W26" s="6"/>
+      <c r="X26" s="6"/>
+      <c r="Y26" s="6"/>
+      <c r="Z26" s="6"/>
+      <c r="AA26" s="6"/>
+      <c r="AB26" s="6"/>
+      <c r="AC26" s="6"/>
+      <c r="AD26" s="6"/>
+      <c r="AE26" s="6"/>
+      <c r="AF26" s="6"/>
     </row>
     <row r="27" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B27" t="s">
@@ -1753,6 +2391,27 @@
       <c r="E27">
         <v>636</v>
       </c>
+      <c r="L27" s="6"/>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6"/>
+      <c r="O27" s="6"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="6"/>
+      <c r="R27" s="6"/>
+      <c r="S27" s="6"/>
+      <c r="T27" s="6"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6"/>
+      <c r="W27" s="6"/>
+      <c r="X27" s="6"/>
+      <c r="Y27" s="6"/>
+      <c r="Z27" s="6"/>
+      <c r="AA27" s="6"/>
+      <c r="AB27" s="6"/>
+      <c r="AC27" s="6"/>
+      <c r="AD27" s="6"/>
+      <c r="AE27" s="6"/>
+      <c r="AF27" s="6"/>
     </row>
     <row r="28" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B28" t="s">
@@ -1767,6 +2426,27 @@
       <c r="E28">
         <v>20</v>
       </c>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="6"/>
+      <c r="S28" s="6"/>
+      <c r="T28" s="6"/>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+      <c r="X28" s="6"/>
+      <c r="Y28" s="6"/>
+      <c r="Z28" s="6"/>
+      <c r="AA28" s="6"/>
+      <c r="AB28" s="6"/>
+      <c r="AC28" s="6"/>
+      <c r="AD28" s="6"/>
+      <c r="AE28" s="6"/>
+      <c r="AF28" s="6"/>
     </row>
     <row r="29" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B29" t="s">
@@ -1778,6 +2458,27 @@
       <c r="D29" t="s">
         <v>7</v>
       </c>
+      <c r="L29" s="6"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="6"/>
+      <c r="S29" s="6"/>
+      <c r="T29" s="6"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+      <c r="X29" s="6"/>
+      <c r="Y29" s="6"/>
+      <c r="Z29" s="6"/>
+      <c r="AA29" s="6"/>
+      <c r="AB29" s="6"/>
+      <c r="AC29" s="6"/>
+      <c r="AD29" s="6"/>
+      <c r="AE29" s="6"/>
+      <c r="AF29" s="6"/>
     </row>
     <row r="30" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B30" t="s">
@@ -1789,6 +2490,27 @@
       <c r="D30" t="s">
         <v>6</v>
       </c>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6"/>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="6"/>
+      <c r="S30" s="6"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6"/>
+      <c r="W30" s="6"/>
+      <c r="X30" s="6"/>
+      <c r="Y30" s="6"/>
+      <c r="Z30" s="6"/>
+      <c r="AA30" s="6"/>
+      <c r="AB30" s="6"/>
+      <c r="AC30" s="6"/>
+      <c r="AD30" s="6"/>
+      <c r="AE30" s="6"/>
+      <c r="AF30" s="6"/>
     </row>
     <row r="31" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B31" t="s">
@@ -1803,6 +2525,27 @@
       <c r="E31">
         <v>110</v>
       </c>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6"/>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="6"/>
+      <c r="S31" s="6"/>
+      <c r="T31" s="6"/>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+      <c r="X31" s="6"/>
+      <c r="Y31" s="6"/>
+      <c r="Z31" s="6"/>
+      <c r="AA31" s="6"/>
+      <c r="AB31" s="6"/>
+      <c r="AC31" s="6"/>
+      <c r="AD31" s="6"/>
+      <c r="AE31" s="6"/>
+      <c r="AF31" s="6"/>
     </row>
     <row r="32" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B32" t="s">
@@ -1814,8 +2557,29 @@
       <c r="D32" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L32" s="6"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="6"/>
+      <c r="S32" s="6"/>
+      <c r="T32" s="6"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+      <c r="X32" s="6"/>
+      <c r="Y32" s="6"/>
+      <c r="Z32" s="6"/>
+      <c r="AA32" s="6"/>
+      <c r="AB32" s="6"/>
+      <c r="AC32" s="6"/>
+      <c r="AD32" s="6"/>
+      <c r="AE32" s="6"/>
+      <c r="AF32" s="6"/>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B33" t="s">
         <v>29</v>
       </c>
@@ -1828,8 +2592,29 @@
       <c r="E33">
         <v>55</v>
       </c>
-    </row>
-    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6"/>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="6"/>
+      <c r="S33" s="6"/>
+      <c r="T33" s="6"/>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+      <c r="X33" s="6"/>
+      <c r="Y33" s="6"/>
+      <c r="Z33" s="6"/>
+      <c r="AA33" s="6"/>
+      <c r="AB33" s="6"/>
+      <c r="AC33" s="6"/>
+      <c r="AD33" s="6"/>
+      <c r="AE33" s="6"/>
+      <c r="AF33" s="6"/>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B34" t="s">
         <v>30</v>
       </c>
@@ -1839,8 +2624,29 @@
       <c r="D34" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L34" s="6"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="6"/>
+      <c r="S34" s="6"/>
+      <c r="T34" s="6"/>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+      <c r="X34" s="6"/>
+      <c r="Y34" s="6"/>
+      <c r="Z34" s="6"/>
+      <c r="AA34" s="6"/>
+      <c r="AB34" s="6"/>
+      <c r="AC34" s="6"/>
+      <c r="AD34" s="6"/>
+      <c r="AE34" s="6"/>
+      <c r="AF34" s="6"/>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B35" t="s">
         <v>30</v>
       </c>
@@ -1853,8 +2659,29 @@
       <c r="E35">
         <v>34</v>
       </c>
-    </row>
-    <row r="36" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6"/>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="6"/>
+      <c r="S35" s="6"/>
+      <c r="T35" s="6"/>
+      <c r="U35" s="6"/>
+      <c r="V35" s="6"/>
+      <c r="W35" s="6"/>
+      <c r="X35" s="6"/>
+      <c r="Y35" s="6"/>
+      <c r="Z35" s="6"/>
+      <c r="AA35" s="6"/>
+      <c r="AB35" s="6"/>
+      <c r="AC35" s="6"/>
+      <c r="AD35" s="6"/>
+      <c r="AE35" s="6"/>
+      <c r="AF35" s="6"/>
+    </row>
+    <row r="36" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B36" t="s">
         <v>31</v>
       </c>
@@ -1864,8 +2691,29 @@
       <c r="D36" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L36" s="6"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="6"/>
+      <c r="S36" s="6"/>
+      <c r="T36" s="6"/>
+      <c r="U36" s="6"/>
+      <c r="V36" s="6"/>
+      <c r="W36" s="6"/>
+      <c r="X36" s="6"/>
+      <c r="Y36" s="6"/>
+      <c r="Z36" s="6"/>
+      <c r="AA36" s="6"/>
+      <c r="AB36" s="6"/>
+      <c r="AC36" s="6"/>
+      <c r="AD36" s="6"/>
+      <c r="AE36" s="6"/>
+      <c r="AF36" s="6"/>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B37" t="s">
         <v>31</v>
       </c>
@@ -1878,8 +2726,29 @@
       <c r="E37">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6"/>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="6"/>
+      <c r="S37" s="6"/>
+      <c r="T37" s="6"/>
+      <c r="U37" s="6"/>
+      <c r="V37" s="6"/>
+      <c r="W37" s="6"/>
+      <c r="X37" s="6"/>
+      <c r="Y37" s="6"/>
+      <c r="Z37" s="6"/>
+      <c r="AA37" s="6"/>
+      <c r="AB37" s="6"/>
+      <c r="AC37" s="6"/>
+      <c r="AD37" s="6"/>
+      <c r="AE37" s="6"/>
+      <c r="AF37" s="6"/>
+    </row>
+    <row r="38" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B38" t="s">
         <v>32</v>
       </c>
@@ -1892,8 +2761,29 @@
       <c r="I38">
         <v>11130</v>
       </c>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L38" s="6"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6"/>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="6"/>
+      <c r="S38" s="6"/>
+      <c r="T38" s="6"/>
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
+      <c r="X38" s="6"/>
+      <c r="Y38" s="6"/>
+      <c r="Z38" s="6"/>
+      <c r="AA38" s="6"/>
+      <c r="AB38" s="6"/>
+      <c r="AC38" s="6"/>
+      <c r="AD38" s="6"/>
+      <c r="AE38" s="6"/>
+      <c r="AF38" s="6"/>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B39" t="s">
         <v>32</v>
       </c>
@@ -1903,8 +2793,29 @@
       <c r="D39" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6"/>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="6"/>
+      <c r="S39" s="6"/>
+      <c r="T39" s="6"/>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+      <c r="X39" s="6"/>
+      <c r="Y39" s="6"/>
+      <c r="Z39" s="6"/>
+      <c r="AA39" s="6"/>
+      <c r="AB39" s="6"/>
+      <c r="AC39" s="6"/>
+      <c r="AD39" s="6"/>
+      <c r="AE39" s="6"/>
+      <c r="AF39" s="6"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B40" t="s">
         <v>33</v>
       </c>
@@ -1917,8 +2828,29 @@
       <c r="E40">
         <v>1787.905</v>
       </c>
-    </row>
-    <row r="41" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L40" s="6"/>
+      <c r="M40" s="6"/>
+      <c r="N40" s="6"/>
+      <c r="O40" s="6"/>
+      <c r="P40" s="6"/>
+      <c r="Q40" s="6"/>
+      <c r="R40" s="6"/>
+      <c r="S40" s="6"/>
+      <c r="T40" s="6"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+      <c r="X40" s="6"/>
+      <c r="Y40" s="6"/>
+      <c r="Z40" s="6"/>
+      <c r="AA40" s="6"/>
+      <c r="AB40" s="6"/>
+      <c r="AC40" s="6"/>
+      <c r="AD40" s="6"/>
+      <c r="AE40" s="6"/>
+      <c r="AF40" s="6"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B41" t="s">
         <v>33</v>
       </c>
@@ -1928,8 +2860,29 @@
       <c r="D41" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="42" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L41" s="6"/>
+      <c r="M41" s="6"/>
+      <c r="N41" s="6"/>
+      <c r="O41" s="6"/>
+      <c r="P41" s="6"/>
+      <c r="Q41" s="6"/>
+      <c r="R41" s="6"/>
+      <c r="S41" s="6"/>
+      <c r="T41" s="6"/>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+      <c r="X41" s="6"/>
+      <c r="Y41" s="6"/>
+      <c r="Z41" s="6"/>
+      <c r="AA41" s="6"/>
+      <c r="AB41" s="6"/>
+      <c r="AC41" s="6"/>
+      <c r="AD41" s="6"/>
+      <c r="AE41" s="6"/>
+      <c r="AF41" s="6"/>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B42" t="s">
         <v>117</v>
       </c>
@@ -1942,8 +2895,29 @@
       <c r="E42">
         <v>1583.28</v>
       </c>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L42" s="6"/>
+      <c r="M42" s="6"/>
+      <c r="N42" s="6"/>
+      <c r="O42" s="6"/>
+      <c r="P42" s="6"/>
+      <c r="Q42" s="6"/>
+      <c r="R42" s="6"/>
+      <c r="S42" s="6"/>
+      <c r="T42" s="6"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+      <c r="X42" s="6"/>
+      <c r="Y42" s="6"/>
+      <c r="Z42" s="6"/>
+      <c r="AA42" s="6"/>
+      <c r="AB42" s="6"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="6"/>
+      <c r="AE42" s="6"/>
+      <c r="AF42" s="6"/>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B43" t="s">
         <v>117</v>
       </c>
@@ -1953,8 +2927,29 @@
       <c r="D43" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L43" s="6"/>
+      <c r="M43" s="6"/>
+      <c r="N43" s="6"/>
+      <c r="O43" s="6"/>
+      <c r="P43" s="6"/>
+      <c r="Q43" s="6"/>
+      <c r="R43" s="6"/>
+      <c r="S43" s="6"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+      <c r="X43" s="6"/>
+      <c r="Y43" s="6"/>
+      <c r="Z43" s="6"/>
+      <c r="AA43" s="6"/>
+      <c r="AB43" s="6"/>
+      <c r="AC43" s="6"/>
+      <c r="AD43" s="6"/>
+      <c r="AE43" s="6"/>
+      <c r="AF43" s="6"/>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B44" t="s">
         <v>34</v>
       </c>
@@ -1967,8 +2962,29 @@
       <c r="E44">
         <v>699.23500000000001</v>
       </c>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L44" s="6"/>
+      <c r="M44" s="6"/>
+      <c r="N44" s="6"/>
+      <c r="O44" s="6"/>
+      <c r="P44" s="6"/>
+      <c r="Q44" s="6"/>
+      <c r="R44" s="6"/>
+      <c r="S44" s="6"/>
+      <c r="T44" s="6"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+      <c r="X44" s="6"/>
+      <c r="Y44" s="6"/>
+      <c r="Z44" s="6"/>
+      <c r="AA44" s="6"/>
+      <c r="AB44" s="6"/>
+      <c r="AC44" s="6"/>
+      <c r="AD44" s="6"/>
+      <c r="AE44" s="6"/>
+      <c r="AF44" s="6"/>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B45" t="s">
         <v>34</v>
       </c>
@@ -1981,8 +2997,29 @@
       <c r="E45">
         <v>166.2</v>
       </c>
-    </row>
-    <row r="46" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L45" s="6"/>
+      <c r="M45" s="6"/>
+      <c r="N45" s="6"/>
+      <c r="O45" s="6"/>
+      <c r="P45" s="6"/>
+      <c r="Q45" s="6"/>
+      <c r="R45" s="6"/>
+      <c r="S45" s="6"/>
+      <c r="T45" s="6"/>
+      <c r="U45" s="6"/>
+      <c r="V45" s="6"/>
+      <c r="W45" s="6"/>
+      <c r="X45" s="6"/>
+      <c r="Y45" s="6"/>
+      <c r="Z45" s="6"/>
+      <c r="AA45" s="6"/>
+      <c r="AB45" s="6"/>
+      <c r="AC45" s="6"/>
+      <c r="AD45" s="6"/>
+      <c r="AE45" s="6"/>
+      <c r="AF45" s="6"/>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B46" t="s">
         <v>35</v>
       </c>
@@ -1995,8 +3032,29 @@
       <c r="E46">
         <v>820.2</v>
       </c>
-    </row>
-    <row r="47" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L46" s="6"/>
+      <c r="M46" s="6"/>
+      <c r="N46" s="6"/>
+      <c r="O46" s="6"/>
+      <c r="P46" s="6"/>
+      <c r="Q46" s="6"/>
+      <c r="R46" s="6"/>
+      <c r="S46" s="6"/>
+      <c r="T46" s="6"/>
+      <c r="U46" s="6"/>
+      <c r="V46" s="6"/>
+      <c r="W46" s="6"/>
+      <c r="X46" s="6"/>
+      <c r="Y46" s="6"/>
+      <c r="Z46" s="6"/>
+      <c r="AA46" s="6"/>
+      <c r="AB46" s="6"/>
+      <c r="AC46" s="6"/>
+      <c r="AD46" s="6"/>
+      <c r="AE46" s="6"/>
+      <c r="AF46" s="6"/>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B47" t="s">
         <v>35</v>
       </c>
@@ -2009,8 +3067,29 @@
       <c r="E47">
         <v>191.4</v>
       </c>
-    </row>
-    <row r="48" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="L47" s="6"/>
+      <c r="M47" s="6"/>
+      <c r="N47" s="6"/>
+      <c r="O47" s="6"/>
+      <c r="P47" s="6"/>
+      <c r="Q47" s="6"/>
+      <c r="R47" s="6"/>
+      <c r="S47" s="6"/>
+      <c r="T47" s="6"/>
+      <c r="U47" s="6"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="6"/>
+      <c r="X47" s="6"/>
+      <c r="Y47" s="6"/>
+      <c r="Z47" s="6"/>
+      <c r="AA47" s="6"/>
+      <c r="AB47" s="6"/>
+      <c r="AC47" s="6"/>
+      <c r="AD47" s="6"/>
+      <c r="AE47" s="6"/>
+      <c r="AF47" s="6"/>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.3">
       <c r="B48" t="s">
         <v>36</v>
       </c>
@@ -2023,6 +3102,27 @@
       <c r="E48">
         <v>165</v>
       </c>
+      <c r="L48" s="6"/>
+      <c r="M48" s="6"/>
+      <c r="N48" s="6"/>
+      <c r="O48" s="6"/>
+      <c r="P48" s="6"/>
+      <c r="Q48" s="6"/>
+      <c r="R48" s="6"/>
+      <c r="S48" s="6"/>
+      <c r="T48" s="6"/>
+      <c r="U48" s="6"/>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+      <c r="X48" s="6"/>
+      <c r="Y48" s="6"/>
+      <c r="Z48" s="6"/>
+      <c r="AA48" s="6"/>
+      <c r="AB48" s="6"/>
+      <c r="AC48" s="6"/>
+      <c r="AD48" s="6"/>
+      <c r="AE48" s="6"/>
+      <c r="AF48" s="6"/>
     </row>
     <row r="49" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B49" t="s">
@@ -2037,6 +3137,27 @@
       <c r="E49">
         <v>43.5</v>
       </c>
+      <c r="L49" s="6"/>
+      <c r="M49" s="6"/>
+      <c r="N49" s="6"/>
+      <c r="O49" s="6"/>
+      <c r="P49" s="6"/>
+      <c r="Q49" s="6"/>
+      <c r="R49" s="6"/>
+      <c r="S49" s="6"/>
+      <c r="T49" s="6"/>
+      <c r="U49" s="6"/>
+      <c r="V49" s="6"/>
+      <c r="W49" s="6"/>
+      <c r="X49" s="6"/>
+      <c r="Y49" s="6"/>
+      <c r="Z49" s="6"/>
+      <c r="AA49" s="6"/>
+      <c r="AB49" s="6"/>
+      <c r="AC49" s="6"/>
+      <c r="AD49" s="6"/>
+      <c r="AE49" s="6"/>
+      <c r="AF49" s="6"/>
     </row>
     <row r="50" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B50" t="s">
@@ -2048,6 +3169,27 @@
       <c r="D50" t="s">
         <v>6</v>
       </c>
+      <c r="L50" s="6"/>
+      <c r="M50" s="6"/>
+      <c r="N50" s="6"/>
+      <c r="O50" s="6"/>
+      <c r="P50" s="6"/>
+      <c r="Q50" s="6"/>
+      <c r="R50" s="6"/>
+      <c r="S50" s="6"/>
+      <c r="T50" s="6"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+      <c r="X50" s="6"/>
+      <c r="Y50" s="6"/>
+      <c r="Z50" s="6"/>
+      <c r="AA50" s="6"/>
+      <c r="AB50" s="6"/>
+      <c r="AC50" s="6"/>
+      <c r="AD50" s="6"/>
+      <c r="AE50" s="6"/>
+      <c r="AF50" s="6"/>
     </row>
     <row r="51" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B51" t="s">
@@ -2063,18 +3205,27 @@
         <v>201.5</v>
       </c>
       <c r="K51" s="4"/>
-      <c r="L51" s="4"/>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
-      <c r="P51" s="4"/>
-      <c r="Q51" s="4"/>
-      <c r="R51" s="4"/>
-      <c r="S51" s="4"/>
-      <c r="T51" s="4"/>
-      <c r="U51" s="4"/>
-      <c r="V51" s="4"/>
-      <c r="W51" s="4"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+      <c r="O51" s="6"/>
+      <c r="P51" s="6"/>
+      <c r="Q51" s="6"/>
+      <c r="R51" s="6"/>
+      <c r="S51" s="6"/>
+      <c r="T51" s="6"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+      <c r="X51" s="6"/>
+      <c r="Y51" s="6"/>
+      <c r="Z51" s="6"/>
+      <c r="AA51" s="6"/>
+      <c r="AB51" s="6"/>
+      <c r="AC51" s="6"/>
+      <c r="AD51" s="6"/>
+      <c r="AE51" s="6"/>
+      <c r="AF51" s="6"/>
     </row>
     <row r="52" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B52" s="5" t="s">
@@ -2099,22 +3250,31 @@
         <v>39</v>
       </c>
       <c r="K52" s="4"/>
-      <c r="L52" s="4"/>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
-      <c r="P52" s="4"/>
-      <c r="Q52" s="4"/>
-      <c r="R52" s="4">
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+      <c r="O52" s="6"/>
+      <c r="P52" s="6"/>
+      <c r="Q52" s="6"/>
+      <c r="R52" s="6">
         <v>75</v>
       </c>
-      <c r="S52" s="4">
+      <c r="S52" s="6">
         <v>325</v>
       </c>
-      <c r="T52" s="4"/>
-      <c r="U52" s="4"/>
-      <c r="V52" s="4"/>
-      <c r="W52" s="4"/>
+      <c r="T52" s="6"/>
+      <c r="U52" s="6"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
+      <c r="X52" s="6"/>
+      <c r="Y52" s="6"/>
+      <c r="Z52" s="6"/>
+      <c r="AA52" s="6"/>
+      <c r="AB52" s="6"/>
+      <c r="AC52" s="6"/>
+      <c r="AD52" s="6"/>
+      <c r="AE52" s="6"/>
+      <c r="AF52" s="6"/>
       <c r="AG52" t="s">
         <v>114</v>
       </c>
@@ -2136,18 +3296,27 @@
         <v>0</v>
       </c>
       <c r="K53" s="4"/>
-      <c r="L53" s="4"/>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
-      <c r="P53" s="4"/>
-      <c r="Q53" s="4"/>
-      <c r="R53" s="4"/>
-      <c r="S53" s="4"/>
-      <c r="T53" s="4"/>
-      <c r="U53" s="4"/>
-      <c r="V53" s="4"/>
-      <c r="W53" s="4"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+      <c r="O53" s="6"/>
+      <c r="P53" s="6"/>
+      <c r="Q53" s="6"/>
+      <c r="R53" s="6"/>
+      <c r="S53" s="6"/>
+      <c r="T53" s="6"/>
+      <c r="U53" s="6"/>
+      <c r="V53" s="6"/>
+      <c r="W53" s="6"/>
+      <c r="X53" s="6"/>
+      <c r="Y53" s="6"/>
+      <c r="Z53" s="6"/>
+      <c r="AA53" s="6"/>
+      <c r="AB53" s="6"/>
+      <c r="AC53" s="6"/>
+      <c r="AD53" s="6"/>
+      <c r="AE53" s="6"/>
+      <c r="AF53" s="6"/>
       <c r="AG53" t="s">
         <v>114</v>
       </c>
@@ -2175,22 +3344,31 @@
         <v>523</v>
       </c>
       <c r="K54" s="4"/>
-      <c r="L54" s="4"/>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
-      <c r="P54" s="4"/>
-      <c r="Q54" s="4"/>
-      <c r="R54" s="4"/>
-      <c r="S54" s="4"/>
-      <c r="T54" s="4">
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+      <c r="O54" s="6"/>
+      <c r="P54" s="6"/>
+      <c r="Q54" s="6"/>
+      <c r="R54" s="6"/>
+      <c r="S54" s="6"/>
+      <c r="T54" s="6">
         <v>35</v>
       </c>
-      <c r="U54" s="4">
+      <c r="U54" s="6">
         <v>122.7</v>
       </c>
-      <c r="V54" s="4"/>
-      <c r="W54" s="4"/>
+      <c r="V54" s="6"/>
+      <c r="W54" s="6"/>
+      <c r="X54" s="6"/>
+      <c r="Y54" s="6"/>
+      <c r="Z54" s="6"/>
+      <c r="AA54" s="6"/>
+      <c r="AB54" s="6"/>
+      <c r="AC54" s="6"/>
+      <c r="AD54" s="6"/>
+      <c r="AE54" s="6"/>
+      <c r="AF54" s="6"/>
       <c r="AG54" t="s">
         <v>114</v>
       </c>
@@ -2212,18 +3390,27 @@
         <v>0</v>
       </c>
       <c r="K55" s="4"/>
-      <c r="L55" s="4"/>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
-      <c r="P55" s="4"/>
-      <c r="Q55" s="4"/>
-      <c r="R55" s="4"/>
-      <c r="S55" s="4"/>
-      <c r="T55" s="4"/>
-      <c r="U55" s="4"/>
-      <c r="V55" s="4"/>
-      <c r="W55" s="4"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+      <c r="O55" s="6"/>
+      <c r="P55" s="6"/>
+      <c r="Q55" s="6"/>
+      <c r="R55" s="6"/>
+      <c r="S55" s="6"/>
+      <c r="T55" s="6"/>
+      <c r="U55" s="6"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
+      <c r="X55" s="6"/>
+      <c r="Y55" s="6"/>
+      <c r="Z55" s="6"/>
+      <c r="AA55" s="6"/>
+      <c r="AB55" s="6"/>
+      <c r="AC55" s="6"/>
+      <c r="AD55" s="6"/>
+      <c r="AE55" s="6"/>
+      <c r="AF55" s="6"/>
       <c r="AG55" t="s">
         <v>114</v>
       </c>
@@ -2251,22 +3438,31 @@
         <v>2126</v>
       </c>
       <c r="K56" s="4"/>
-      <c r="L56" s="4"/>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
-      <c r="P56" s="4"/>
-      <c r="Q56" s="4"/>
-      <c r="R56" s="4"/>
-      <c r="S56" s="4">
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+      <c r="O56" s="6"/>
+      <c r="P56" s="6"/>
+      <c r="Q56" s="6"/>
+      <c r="R56" s="6"/>
+      <c r="S56" s="6">
         <v>220</v>
       </c>
-      <c r="T56" s="4">
+      <c r="T56" s="6">
         <v>121.715</v>
       </c>
-      <c r="U56" s="4"/>
-      <c r="V56" s="4"/>
-      <c r="W56" s="4"/>
+      <c r="U56" s="6"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
+      <c r="X56" s="6"/>
+      <c r="Y56" s="6"/>
+      <c r="Z56" s="6"/>
+      <c r="AA56" s="6"/>
+      <c r="AB56" s="6"/>
+      <c r="AC56" s="6"/>
+      <c r="AD56" s="6"/>
+      <c r="AE56" s="6"/>
+      <c r="AF56" s="6"/>
       <c r="AG56" t="s">
         <v>114</v>
       </c>
@@ -2288,20 +3484,29 @@
         <v>13.17</v>
       </c>
       <c r="K57" s="4"/>
-      <c r="L57" s="4"/>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
-      <c r="P57" s="4"/>
-      <c r="Q57" s="4"/>
-      <c r="R57" s="4"/>
-      <c r="S57" s="4"/>
-      <c r="T57" s="4">
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+      <c r="O57" s="6"/>
+      <c r="P57" s="6"/>
+      <c r="Q57" s="6"/>
+      <c r="R57" s="6"/>
+      <c r="S57" s="6"/>
+      <c r="T57" s="6">
         <v>13.17</v>
       </c>
-      <c r="U57" s="4"/>
-      <c r="V57" s="4"/>
-      <c r="W57" s="4"/>
+      <c r="U57" s="6"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+      <c r="X57" s="6"/>
+      <c r="Y57" s="6"/>
+      <c r="Z57" s="6"/>
+      <c r="AA57" s="6"/>
+      <c r="AB57" s="6"/>
+      <c r="AC57" s="6"/>
+      <c r="AD57" s="6"/>
+      <c r="AE57" s="6"/>
+      <c r="AF57" s="6"/>
       <c r="AG57" t="s">
         <v>114</v>
       </c>
@@ -2326,20 +3531,29 @@
         <v>191</v>
       </c>
       <c r="K58" s="4"/>
-      <c r="L58" s="4"/>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
-      <c r="P58" s="4"/>
-      <c r="Q58" s="4"/>
-      <c r="R58" s="4"/>
-      <c r="S58" s="4"/>
-      <c r="T58" s="4">
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+      <c r="O58" s="6"/>
+      <c r="P58" s="6"/>
+      <c r="Q58" s="6"/>
+      <c r="R58" s="6"/>
+      <c r="S58" s="6"/>
+      <c r="T58" s="6">
         <v>43.015000000000001</v>
       </c>
-      <c r="U58" s="4"/>
-      <c r="V58" s="4"/>
-      <c r="W58" s="4"/>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+      <c r="X58" s="6"/>
+      <c r="Y58" s="6"/>
+      <c r="Z58" s="6"/>
+      <c r="AA58" s="6"/>
+      <c r="AB58" s="6"/>
+      <c r="AC58" s="6"/>
+      <c r="AD58" s="6"/>
+      <c r="AE58" s="6"/>
+      <c r="AF58" s="6"/>
       <c r="AG58" t="s">
         <v>114</v>
       </c>
@@ -2361,20 +3575,29 @@
         <v>51.05</v>
       </c>
       <c r="K59" s="4"/>
-      <c r="L59" s="4"/>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
-      <c r="P59" s="4"/>
-      <c r="Q59" s="4"/>
-      <c r="R59" s="4"/>
-      <c r="S59" s="4">
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+      <c r="O59" s="6"/>
+      <c r="P59" s="6"/>
+      <c r="Q59" s="6"/>
+      <c r="R59" s="6"/>
+      <c r="S59" s="6">
         <v>51.05</v>
       </c>
-      <c r="T59" s="4"/>
-      <c r="U59" s="4"/>
-      <c r="V59" s="4"/>
-      <c r="W59" s="4"/>
+      <c r="T59" s="6"/>
+      <c r="U59" s="6"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="6"/>
+      <c r="X59" s="6"/>
+      <c r="Y59" s="6"/>
+      <c r="Z59" s="6"/>
+      <c r="AA59" s="6"/>
+      <c r="AB59" s="6"/>
+      <c r="AC59" s="6"/>
+      <c r="AD59" s="6"/>
+      <c r="AE59" s="6"/>
+      <c r="AF59" s="6"/>
       <c r="AG59" t="s">
         <v>114</v>
       </c>
@@ -2408,20 +3631,29 @@
         <v>109</v>
       </c>
       <c r="K60" s="4"/>
-      <c r="L60" s="4"/>
-      <c r="M60" s="4"/>
-      <c r="N60" s="4"/>
-      <c r="O60" s="4"/>
-      <c r="P60" s="4"/>
-      <c r="Q60" s="4">
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
+      <c r="P60" s="6"/>
+      <c r="Q60" s="6">
         <v>288.26</v>
       </c>
-      <c r="R60" s="4"/>
-      <c r="S60" s="4"/>
-      <c r="T60" s="4"/>
-      <c r="U60" s="4"/>
-      <c r="V60" s="4"/>
-      <c r="W60" s="4"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+      <c r="X60" s="6"/>
+      <c r="Y60" s="6"/>
+      <c r="Z60" s="6"/>
+      <c r="AA60" s="6"/>
+      <c r="AB60" s="6"/>
+      <c r="AC60" s="6"/>
+      <c r="AD60" s="6"/>
+      <c r="AE60" s="6"/>
+      <c r="AF60" s="6"/>
       <c r="AG60" t="s">
         <v>114</v>
       </c>
@@ -2443,20 +3675,29 @@
         <v>32.85</v>
       </c>
       <c r="K61" s="4"/>
-      <c r="L61" s="4"/>
-      <c r="M61" s="4"/>
-      <c r="N61" s="4"/>
-      <c r="O61" s="4"/>
-      <c r="P61" s="4"/>
-      <c r="Q61" s="4">
+      <c r="L61" s="6"/>
+      <c r="M61" s="6"/>
+      <c r="N61" s="6"/>
+      <c r="O61" s="6"/>
+      <c r="P61" s="6"/>
+      <c r="Q61" s="6">
         <v>32.85</v>
       </c>
-      <c r="R61" s="4"/>
-      <c r="S61" s="4"/>
-      <c r="T61" s="4"/>
-      <c r="U61" s="4"/>
-      <c r="V61" s="4"/>
-      <c r="W61" s="4"/>
+      <c r="R61" s="6"/>
+      <c r="S61" s="6"/>
+      <c r="T61" s="6"/>
+      <c r="U61" s="6"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+      <c r="X61" s="6"/>
+      <c r="Y61" s="6"/>
+      <c r="Z61" s="6"/>
+      <c r="AA61" s="6"/>
+      <c r="AB61" s="6"/>
+      <c r="AC61" s="6"/>
+      <c r="AD61" s="6"/>
+      <c r="AE61" s="6"/>
+      <c r="AF61" s="6"/>
       <c r="AG61" t="s">
         <v>114</v>
       </c>
@@ -2484,20 +3725,29 @@
         <v>188</v>
       </c>
       <c r="K62" s="4"/>
-      <c r="L62" s="4"/>
-      <c r="M62" s="4"/>
-      <c r="N62" s="4"/>
-      <c r="O62" s="4"/>
-      <c r="P62" s="4"/>
-      <c r="Q62" s="4"/>
-      <c r="R62" s="4">
+      <c r="L62" s="6"/>
+      <c r="M62" s="6"/>
+      <c r="N62" s="6"/>
+      <c r="O62" s="6"/>
+      <c r="P62" s="6"/>
+      <c r="Q62" s="6"/>
+      <c r="R62" s="6">
         <v>223.29</v>
       </c>
-      <c r="S62" s="4"/>
-      <c r="T62" s="4"/>
-      <c r="U62" s="4"/>
-      <c r="V62" s="4"/>
-      <c r="W62" s="4"/>
+      <c r="S62" s="6"/>
+      <c r="T62" s="6"/>
+      <c r="U62" s="6"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+      <c r="X62" s="6"/>
+      <c r="Y62" s="6"/>
+      <c r="Z62" s="6"/>
+      <c r="AA62" s="6"/>
+      <c r="AB62" s="6"/>
+      <c r="AC62" s="6"/>
+      <c r="AD62" s="6"/>
+      <c r="AE62" s="6"/>
+      <c r="AF62" s="6"/>
       <c r="AG62" t="s">
         <v>114</v>
       </c>
@@ -2519,20 +3769,29 @@
         <v>26.66</v>
       </c>
       <c r="K63" s="4"/>
-      <c r="L63" s="4"/>
-      <c r="M63" s="4"/>
-      <c r="N63" s="4"/>
-      <c r="O63" s="4"/>
-      <c r="P63" s="4"/>
-      <c r="Q63" s="4">
+      <c r="L63" s="6"/>
+      <c r="M63" s="6"/>
+      <c r="N63" s="6"/>
+      <c r="O63" s="6"/>
+      <c r="P63" s="6"/>
+      <c r="Q63" s="6">
         <v>26.66</v>
       </c>
-      <c r="R63" s="4"/>
-      <c r="S63" s="4"/>
-      <c r="T63" s="4"/>
-      <c r="U63" s="4"/>
-      <c r="V63" s="4"/>
-      <c r="W63" s="4"/>
+      <c r="R63" s="6"/>
+      <c r="S63" s="6"/>
+      <c r="T63" s="6"/>
+      <c r="U63" s="6"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+      <c r="X63" s="6"/>
+      <c r="Y63" s="6"/>
+      <c r="Z63" s="6"/>
+      <c r="AA63" s="6"/>
+      <c r="AB63" s="6"/>
+      <c r="AC63" s="6"/>
+      <c r="AD63" s="6"/>
+      <c r="AE63" s="6"/>
+      <c r="AF63" s="6"/>
       <c r="AG63" t="s">
         <v>114</v>
       </c>
@@ -2560,20 +3819,31 @@
         <v>860</v>
       </c>
       <c r="K64" s="4"/>
-      <c r="L64" s="4"/>
-      <c r="M64" s="4"/>
-      <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
-      <c r="P64" s="4"/>
-      <c r="Q64" s="4"/>
-      <c r="R64" s="4"/>
-      <c r="S64" s="4"/>
-      <c r="T64" s="4">
+      <c r="L64" s="6"/>
+      <c r="M64" s="6"/>
+      <c r="N64" s="6"/>
+      <c r="O64" s="6"/>
+      <c r="P64" s="6"/>
+      <c r="Q64" s="6"/>
+      <c r="R64" s="6"/>
+      <c r="S64" s="6">
+        <v>59.73</v>
+      </c>
+      <c r="T64" s="6">
         <v>99.9</v>
       </c>
-      <c r="U64" s="4"/>
-      <c r="V64" s="4"/>
-      <c r="W64" s="4"/>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
+      <c r="X64" s="6"/>
+      <c r="Y64" s="6"/>
+      <c r="Z64" s="6"/>
+      <c r="AA64" s="6"/>
+      <c r="AB64" s="6"/>
+      <c r="AC64" s="6"/>
+      <c r="AD64" s="6"/>
+      <c r="AE64" s="6"/>
+      <c r="AF64" s="6"/>
       <c r="AG64" t="s">
         <v>114</v>
       </c>
@@ -2595,20 +3865,29 @@
         <v>31.4</v>
       </c>
       <c r="K65" s="4"/>
-      <c r="L65" s="4"/>
-      <c r="M65" s="4"/>
-      <c r="N65" s="4"/>
-      <c r="O65" s="4"/>
-      <c r="P65" s="4"/>
-      <c r="Q65" s="4">
-        <v>24</v>
-      </c>
-      <c r="R65" s="4"/>
-      <c r="S65" s="4"/>
-      <c r="T65" s="4"/>
-      <c r="U65" s="4"/>
-      <c r="V65" s="4"/>
-      <c r="W65" s="4"/>
+      <c r="L65" s="6"/>
+      <c r="M65" s="6"/>
+      <c r="N65" s="6"/>
+      <c r="O65" s="6"/>
+      <c r="P65" s="6"/>
+      <c r="Q65" s="6">
+        <v>31.4</v>
+      </c>
+      <c r="R65" s="6"/>
+      <c r="S65" s="6"/>
+      <c r="T65" s="6"/>
+      <c r="U65" s="6"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
+      <c r="X65" s="6"/>
+      <c r="Y65" s="6"/>
+      <c r="Z65" s="6"/>
+      <c r="AA65" s="6"/>
+      <c r="AB65" s="6"/>
+      <c r="AC65" s="6"/>
+      <c r="AD65" s="6"/>
+      <c r="AE65" s="6"/>
+      <c r="AF65" s="6"/>
       <c r="AG65" t="s">
         <v>114</v>
       </c>
@@ -2642,28 +3921,37 @@
         <v>72</v>
       </c>
       <c r="K66" s="4"/>
-      <c r="L66" s="4"/>
-      <c r="M66" s="4"/>
-      <c r="N66" s="4">
+      <c r="L66" s="6"/>
+      <c r="M66" s="6"/>
+      <c r="N66" s="6">
         <v>68</v>
       </c>
-      <c r="O66" s="4">
+      <c r="O66" s="6">
         <v>621.84500000000003</v>
       </c>
-      <c r="P66" s="4">
+      <c r="P66" s="6">
         <v>354.52499999999998</v>
       </c>
-      <c r="Q66" s="4">
+      <c r="Q66" s="6">
         <v>67.900000000000006</v>
       </c>
-      <c r="R66" s="4">
+      <c r="R66" s="6">
         <v>117.68</v>
       </c>
-      <c r="S66" s="4"/>
-      <c r="T66" s="4"/>
-      <c r="U66" s="4"/>
-      <c r="V66" s="4"/>
-      <c r="W66" s="4"/>
+      <c r="S66" s="6"/>
+      <c r="T66" s="6"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+      <c r="X66" s="6"/>
+      <c r="Y66" s="6"/>
+      <c r="Z66" s="6"/>
+      <c r="AA66" s="6"/>
+      <c r="AB66" s="6"/>
+      <c r="AC66" s="6"/>
+      <c r="AD66" s="6"/>
+      <c r="AE66" s="6"/>
+      <c r="AF66" s="6"/>
       <c r="AG66" t="s">
         <v>114</v>
       </c>
@@ -2685,18 +3973,27 @@
         <v>0</v>
       </c>
       <c r="K67" s="4"/>
-      <c r="L67" s="4"/>
-      <c r="M67" s="4"/>
-      <c r="N67" s="4"/>
-      <c r="O67" s="4"/>
-      <c r="P67" s="4"/>
-      <c r="Q67" s="4"/>
-      <c r="R67" s="4"/>
-      <c r="S67" s="4"/>
-      <c r="T67" s="4"/>
-      <c r="U67" s="4"/>
-      <c r="V67" s="4"/>
-      <c r="W67" s="4"/>
+      <c r="L67" s="6"/>
+      <c r="M67" s="6"/>
+      <c r="N67" s="6"/>
+      <c r="O67" s="6"/>
+      <c r="P67" s="6"/>
+      <c r="Q67" s="6"/>
+      <c r="R67" s="6"/>
+      <c r="S67" s="6"/>
+      <c r="T67" s="6"/>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+      <c r="X67" s="6"/>
+      <c r="Y67" s="6"/>
+      <c r="Z67" s="6"/>
+      <c r="AA67" s="6"/>
+      <c r="AB67" s="6"/>
+      <c r="AC67" s="6"/>
+      <c r="AD67" s="6"/>
+      <c r="AE67" s="6"/>
+      <c r="AF67" s="6"/>
       <c r="AG67" t="s">
         <v>114</v>
       </c>
@@ -2730,20 +4027,29 @@
         <v>338</v>
       </c>
       <c r="K68" s="4"/>
-      <c r="L68" s="4"/>
-      <c r="M68" s="4"/>
-      <c r="N68" s="4"/>
-      <c r="O68" s="4"/>
-      <c r="P68" s="4">
+      <c r="L68" s="6"/>
+      <c r="M68" s="6"/>
+      <c r="N68" s="6"/>
+      <c r="O68" s="6"/>
+      <c r="P68" s="6">
         <v>328.75</v>
       </c>
-      <c r="Q68" s="4"/>
-      <c r="R68" s="4"/>
-      <c r="S68" s="4"/>
-      <c r="T68" s="4"/>
-      <c r="U68" s="4"/>
-      <c r="V68" s="4"/>
-      <c r="W68" s="4"/>
+      <c r="Q68" s="6"/>
+      <c r="R68" s="6"/>
+      <c r="S68" s="6"/>
+      <c r="T68" s="6"/>
+      <c r="U68" s="6"/>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
+      <c r="X68" s="6"/>
+      <c r="Y68" s="6"/>
+      <c r="Z68" s="6"/>
+      <c r="AA68" s="6"/>
+      <c r="AB68" s="6"/>
+      <c r="AC68" s="6"/>
+      <c r="AD68" s="6"/>
+      <c r="AE68" s="6"/>
+      <c r="AF68" s="6"/>
       <c r="AG68" t="s">
         <v>114</v>
       </c>
@@ -2765,18 +4071,27 @@
         <v>0</v>
       </c>
       <c r="K69" s="4"/>
-      <c r="L69" s="4"/>
-      <c r="M69" s="4"/>
-      <c r="N69" s="4"/>
-      <c r="O69" s="4"/>
-      <c r="P69" s="4"/>
-      <c r="Q69" s="4"/>
-      <c r="R69" s="4"/>
-      <c r="S69" s="4"/>
-      <c r="T69" s="4"/>
-      <c r="U69" s="4"/>
-      <c r="V69" s="4"/>
-      <c r="W69" s="4"/>
+      <c r="L69" s="6"/>
+      <c r="M69" s="6"/>
+      <c r="N69" s="6"/>
+      <c r="O69" s="6"/>
+      <c r="P69" s="6"/>
+      <c r="Q69" s="6"/>
+      <c r="R69" s="6"/>
+      <c r="S69" s="6"/>
+      <c r="T69" s="6"/>
+      <c r="U69" s="6"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6"/>
+      <c r="X69" s="6"/>
+      <c r="Y69" s="6"/>
+      <c r="Z69" s="6"/>
+      <c r="AA69" s="6"/>
+      <c r="AB69" s="6"/>
+      <c r="AC69" s="6"/>
+      <c r="AD69" s="6"/>
+      <c r="AE69" s="6"/>
+      <c r="AF69" s="6"/>
       <c r="AG69" t="s">
         <v>114</v>
       </c>
@@ -2810,22 +4125,31 @@
         <v>901</v>
       </c>
       <c r="K70" s="4"/>
-      <c r="L70" s="4"/>
-      <c r="M70" s="4"/>
-      <c r="N70" s="4"/>
-      <c r="O70" s="4"/>
-      <c r="P70" s="4">
+      <c r="L70" s="6"/>
+      <c r="M70" s="6"/>
+      <c r="N70" s="6"/>
+      <c r="O70" s="6"/>
+      <c r="P70" s="6">
         <v>247.93</v>
       </c>
-      <c r="Q70" s="4">
+      <c r="Q70" s="6">
         <v>136.74</v>
       </c>
-      <c r="R70" s="4"/>
-      <c r="S70" s="4"/>
-      <c r="T70" s="4"/>
-      <c r="U70" s="4"/>
-      <c r="V70" s="4"/>
-      <c r="W70" s="4"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+      <c r="X70" s="6"/>
+      <c r="Y70" s="6"/>
+      <c r="Z70" s="6"/>
+      <c r="AA70" s="6"/>
+      <c r="AB70" s="6"/>
+      <c r="AC70" s="6"/>
+      <c r="AD70" s="6"/>
+      <c r="AE70" s="6"/>
+      <c r="AF70" s="6"/>
       <c r="AG70" t="s">
         <v>114</v>
       </c>
@@ -2847,20 +4171,29 @@
         <v>20.32</v>
       </c>
       <c r="K71" s="4"/>
-      <c r="L71" s="4"/>
-      <c r="M71" s="4"/>
-      <c r="N71" s="4"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4">
+      <c r="L71" s="6"/>
+      <c r="M71" s="6"/>
+      <c r="N71" s="6"/>
+      <c r="O71" s="6"/>
+      <c r="P71" s="6"/>
+      <c r="Q71" s="6">
         <v>20.32</v>
       </c>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
-      <c r="V71" s="4"/>
-      <c r="W71" s="4"/>
+      <c r="R71" s="6"/>
+      <c r="S71" s="6"/>
+      <c r="T71" s="6"/>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6"/>
+      <c r="X71" s="6"/>
+      <c r="Y71" s="6"/>
+      <c r="Z71" s="6"/>
+      <c r="AA71" s="6"/>
+      <c r="AB71" s="6"/>
+      <c r="AC71" s="6"/>
+      <c r="AD71" s="6"/>
+      <c r="AE71" s="6"/>
+      <c r="AF71" s="6"/>
       <c r="AG71" t="s">
         <v>114</v>
       </c>
@@ -2879,27 +4212,35 @@
         <v>207.5</v>
       </c>
       <c r="F72" s="5">
-        <v>485.52</v>
+        <v>197.8</v>
       </c>
       <c r="I72">
         <v>1801</v>
       </c>
       <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
-      <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
-      <c r="V72" s="4"/>
-      <c r="W72" s="4"/>
-      <c r="X72">
-        <v>485.52</v>
-      </c>
+      <c r="L72" s="6"/>
+      <c r="M72" s="6"/>
+      <c r="N72" s="6"/>
+      <c r="O72" s="6"/>
+      <c r="P72" s="6"/>
+      <c r="Q72" s="6"/>
+      <c r="R72" s="6"/>
+      <c r="S72" s="6"/>
+      <c r="T72" s="6"/>
+      <c r="U72" s="6"/>
+      <c r="V72" s="6"/>
+      <c r="W72" s="6"/>
+      <c r="X72" s="6">
+        <v>197.8</v>
+      </c>
+      <c r="Y72" s="6"/>
+      <c r="Z72" s="6"/>
+      <c r="AA72" s="6"/>
+      <c r="AB72" s="6"/>
+      <c r="AC72" s="6"/>
+      <c r="AD72" s="6"/>
+      <c r="AE72" s="6"/>
+      <c r="AF72" s="6"/>
       <c r="AG72" t="s">
         <v>114</v>
       </c>
@@ -2921,22 +4262,30 @@
         <v>10.73</v>
       </c>
       <c r="K73" s="4"/>
-      <c r="L73" s="4"/>
-      <c r="M73" s="4"/>
-      <c r="N73" s="4"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
-      <c r="V73" s="4"/>
-      <c r="W73" s="4"/>
-      <c r="X73">
+      <c r="L73" s="6"/>
+      <c r="M73" s="6"/>
+      <c r="N73" s="6"/>
+      <c r="O73" s="6"/>
+      <c r="P73" s="6"/>
+      <c r="Q73" s="6"/>
+      <c r="R73" s="6"/>
+      <c r="S73" s="6"/>
+      <c r="T73" s="6"/>
+      <c r="U73" s="6"/>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6"/>
+      <c r="X73" s="6">
         <f>6.22+4.51</f>
         <v>10.73</v>
       </c>
+      <c r="Y73" s="6"/>
+      <c r="Z73" s="6"/>
+      <c r="AA73" s="6"/>
+      <c r="AB73" s="6"/>
+      <c r="AC73" s="6"/>
+      <c r="AD73" s="6"/>
+      <c r="AE73" s="6"/>
+      <c r="AF73" s="6"/>
       <c r="AG73" t="s">
         <v>114</v>
       </c>
@@ -2961,20 +4310,29 @@
         <v>168</v>
       </c>
       <c r="K74" s="4"/>
-      <c r="L74" s="4"/>
-      <c r="M74" s="4"/>
-      <c r="N74" s="4"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
-      <c r="V74" s="4"/>
-      <c r="W74" s="4">
+      <c r="L74" s="6"/>
+      <c r="M74" s="6"/>
+      <c r="N74" s="6"/>
+      <c r="O74" s="6"/>
+      <c r="P74" s="6"/>
+      <c r="Q74" s="6"/>
+      <c r="R74" s="6"/>
+      <c r="S74" s="6"/>
+      <c r="T74" s="6"/>
+      <c r="U74" s="6"/>
+      <c r="V74" s="6"/>
+      <c r="W74" s="6">
         <v>545.34</v>
       </c>
+      <c r="X74" s="6"/>
+      <c r="Y74" s="6"/>
+      <c r="Z74" s="6"/>
+      <c r="AA74" s="6"/>
+      <c r="AB74" s="6"/>
+      <c r="AC74" s="6"/>
+      <c r="AD74" s="6"/>
+      <c r="AE74" s="6"/>
+      <c r="AF74" s="6"/>
       <c r="AG74" t="s">
         <v>114</v>
       </c>
@@ -2996,20 +4354,29 @@
         <v>12.02</v>
       </c>
       <c r="K75" s="4"/>
-      <c r="L75" s="4"/>
-      <c r="M75" s="4"/>
-      <c r="N75" s="4"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-      <c r="V75" s="4"/>
-      <c r="W75" s="4">
+      <c r="L75" s="6"/>
+      <c r="M75" s="6"/>
+      <c r="N75" s="6"/>
+      <c r="O75" s="6"/>
+      <c r="P75" s="6"/>
+      <c r="Q75" s="6"/>
+      <c r="R75" s="6"/>
+      <c r="S75" s="6"/>
+      <c r="T75" s="6"/>
+      <c r="U75" s="6"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6">
         <v>12.02</v>
       </c>
+      <c r="X75" s="6"/>
+      <c r="Y75" s="6"/>
+      <c r="Z75" s="6"/>
+      <c r="AA75" s="6"/>
+      <c r="AB75" s="6"/>
+      <c r="AC75" s="6"/>
+      <c r="AD75" s="6"/>
+      <c r="AE75" s="6"/>
+      <c r="AF75" s="6"/>
       <c r="AG75" t="s">
         <v>114</v>
       </c>
@@ -3036,12 +4403,29 @@
       <c r="J76">
         <v>1152</v>
       </c>
-      <c r="T76" s="4"/>
-      <c r="U76" s="4">
+      <c r="L76" s="6"/>
+      <c r="M76" s="6"/>
+      <c r="N76" s="6"/>
+      <c r="O76" s="6"/>
+      <c r="P76" s="6"/>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6">
         <v>384.37</v>
       </c>
-      <c r="V76" s="4"/>
-      <c r="W76" s="4"/>
+      <c r="V76" s="6"/>
+      <c r="W76" s="6"/>
+      <c r="X76" s="6"/>
+      <c r="Y76" s="6"/>
+      <c r="Z76" s="6"/>
+      <c r="AA76" s="6"/>
+      <c r="AB76" s="6"/>
+      <c r="AC76" s="6"/>
+      <c r="AD76" s="6"/>
+      <c r="AE76" s="6"/>
+      <c r="AF76" s="6"/>
       <c r="AG76" t="s">
         <v>114</v>
       </c>
@@ -3062,12 +4446,29 @@
       <c r="F77" s="5">
         <v>23.8</v>
       </c>
-      <c r="T77" s="4"/>
-      <c r="U77" s="4">
+      <c r="L77" s="6"/>
+      <c r="M77" s="6"/>
+      <c r="N77" s="6"/>
+      <c r="O77" s="6"/>
+      <c r="P77" s="6"/>
+      <c r="Q77" s="6"/>
+      <c r="R77" s="6"/>
+      <c r="S77" s="6"/>
+      <c r="T77" s="6"/>
+      <c r="U77" s="6">
         <v>23.8</v>
       </c>
-      <c r="V77" s="4"/>
-      <c r="W77" s="4"/>
+      <c r="V77" s="6"/>
+      <c r="W77" s="6"/>
+      <c r="X77" s="6"/>
+      <c r="Y77" s="6"/>
+      <c r="Z77" s="6"/>
+      <c r="AA77" s="6"/>
+      <c r="AB77" s="6"/>
+      <c r="AC77" s="6"/>
+      <c r="AD77" s="6"/>
+      <c r="AE77" s="6"/>
+      <c r="AF77" s="6"/>
       <c r="AG77" t="s">
         <v>114</v>
       </c>
@@ -3088,15 +4489,31 @@
       <c r="I78">
         <v>2885</v>
       </c>
-      <c r="T78" s="4"/>
-      <c r="U78" s="4"/>
-      <c r="V78" s="4">
+      <c r="L78" s="6"/>
+      <c r="M78" s="6"/>
+      <c r="N78" s="6"/>
+      <c r="O78" s="6"/>
+      <c r="P78" s="6"/>
+      <c r="Q78" s="6"/>
+      <c r="R78" s="6"/>
+      <c r="S78" s="6"/>
+      <c r="T78" s="6"/>
+      <c r="U78" s="6"/>
+      <c r="V78" s="6">
         <v>20.95</v>
       </c>
-      <c r="W78" s="4"/>
-      <c r="X78" s="4">
+      <c r="W78" s="6"/>
+      <c r="X78" s="6">
         <v>70.260000000000005</v>
       </c>
+      <c r="Y78" s="6"/>
+      <c r="Z78" s="6"/>
+      <c r="AA78" s="6"/>
+      <c r="AB78" s="6"/>
+      <c r="AC78" s="6"/>
+      <c r="AD78" s="6"/>
+      <c r="AE78" s="6"/>
+      <c r="AF78" s="6"/>
       <c r="AG78" t="s">
         <v>114</v>
       </c>
@@ -3117,15 +4534,31 @@
       <c r="F79" s="5">
         <v>10.06</v>
       </c>
-      <c r="T79" s="4"/>
-      <c r="U79" s="4"/>
-      <c r="V79" s="4">
+      <c r="L79" s="6"/>
+      <c r="M79" s="6"/>
+      <c r="N79" s="6"/>
+      <c r="O79" s="6"/>
+      <c r="P79" s="6"/>
+      <c r="Q79" s="6"/>
+      <c r="R79" s="6"/>
+      <c r="S79" s="6"/>
+      <c r="T79" s="6"/>
+      <c r="U79" s="6"/>
+      <c r="V79" s="6">
         <v>8.06</v>
       </c>
-      <c r="W79" s="4"/>
-      <c r="X79">
+      <c r="W79" s="6"/>
+      <c r="X79" s="6">
         <v>2</v>
       </c>
+      <c r="Y79" s="6"/>
+      <c r="Z79" s="6"/>
+      <c r="AA79" s="6"/>
+      <c r="AB79" s="6"/>
+      <c r="AC79" s="6"/>
+      <c r="AD79" s="6"/>
+      <c r="AE79" s="6"/>
+      <c r="AF79" s="6"/>
       <c r="AG79" t="s">
         <v>114</v>
       </c>
@@ -3143,15 +4576,32 @@
       <c r="F80" s="5">
         <v>230.72</v>
       </c>
-      <c r="T80" s="4"/>
-      <c r="U80" s="4"/>
-      <c r="V80" s="4">
+      <c r="L80" s="6"/>
+      <c r="M80" s="6"/>
+      <c r="N80" s="6"/>
+      <c r="O80" s="6"/>
+      <c r="P80" s="6"/>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
+      <c r="S80" s="6"/>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
+      <c r="V80" s="6">
         <f>230.02-55.56</f>
         <v>174.46</v>
       </c>
-      <c r="W80" s="4">
+      <c r="W80" s="6">
         <v>56.26</v>
       </c>
+      <c r="X80" s="6"/>
+      <c r="Y80" s="6"/>
+      <c r="Z80" s="6"/>
+      <c r="AA80" s="6"/>
+      <c r="AB80" s="6"/>
+      <c r="AC80" s="6"/>
+      <c r="AD80" s="6"/>
+      <c r="AE80" s="6"/>
+      <c r="AF80" s="6"/>
       <c r="AG80" t="s">
         <v>114</v>
       </c>
@@ -3169,10 +4619,27 @@
       <c r="E81">
         <v>210.02</v>
       </c>
-      <c r="T81" s="4"/>
-      <c r="U81" s="4"/>
-      <c r="V81" s="4"/>
-      <c r="W81" s="4"/>
+      <c r="L81" s="6"/>
+      <c r="M81" s="6"/>
+      <c r="N81" s="6"/>
+      <c r="O81" s="6"/>
+      <c r="P81" s="6"/>
+      <c r="Q81" s="6"/>
+      <c r="R81" s="6"/>
+      <c r="S81" s="6"/>
+      <c r="T81" s="6"/>
+      <c r="U81" s="6"/>
+      <c r="V81" s="6"/>
+      <c r="W81" s="6"/>
+      <c r="X81" s="6"/>
+      <c r="Y81" s="6"/>
+      <c r="Z81" s="6"/>
+      <c r="AA81" s="6"/>
+      <c r="AB81" s="6"/>
+      <c r="AC81" s="6"/>
+      <c r="AD81" s="6"/>
+      <c r="AE81" s="6"/>
+      <c r="AF81" s="6"/>
       <c r="AG81" t="s">
         <v>114</v>
       </c>
@@ -3190,12 +4657,29 @@
       <c r="F82" s="5">
         <v>35.5</v>
       </c>
-      <c r="T82" s="4"/>
-      <c r="U82" s="4"/>
-      <c r="V82" s="4">
+      <c r="L82" s="6"/>
+      <c r="M82" s="6"/>
+      <c r="N82" s="6"/>
+      <c r="O82" s="6"/>
+      <c r="P82" s="6"/>
+      <c r="Q82" s="6"/>
+      <c r="R82" s="6"/>
+      <c r="S82" s="6"/>
+      <c r="T82" s="6"/>
+      <c r="U82" s="6"/>
+      <c r="V82" s="6">
         <v>35.5</v>
       </c>
-      <c r="W82" s="4"/>
+      <c r="W82" s="6"/>
+      <c r="X82" s="6"/>
+      <c r="Y82" s="6"/>
+      <c r="Z82" s="6"/>
+      <c r="AA82" s="6"/>
+      <c r="AB82" s="6"/>
+      <c r="AC82" s="6"/>
+      <c r="AD82" s="6"/>
+      <c r="AE82" s="6"/>
+      <c r="AF82" s="6"/>
       <c r="AG82" t="s">
         <v>114</v>
       </c>
@@ -3213,10 +4697,27 @@
       <c r="E83">
         <v>57.5</v>
       </c>
-      <c r="T83" s="4"/>
-      <c r="U83" s="4"/>
-      <c r="V83" s="4"/>
-      <c r="W83" s="4"/>
+      <c r="L83" s="6"/>
+      <c r="M83" s="6"/>
+      <c r="N83" s="6"/>
+      <c r="O83" s="6"/>
+      <c r="P83" s="6"/>
+      <c r="Q83" s="6"/>
+      <c r="R83" s="6"/>
+      <c r="S83" s="6"/>
+      <c r="T83" s="6"/>
+      <c r="U83" s="6"/>
+      <c r="V83" s="6"/>
+      <c r="W83" s="6"/>
+      <c r="X83" s="6"/>
+      <c r="Y83" s="6"/>
+      <c r="Z83" s="6"/>
+      <c r="AA83" s="6"/>
+      <c r="AB83" s="6"/>
+      <c r="AC83" s="6"/>
+      <c r="AD83" s="6"/>
+      <c r="AE83" s="6"/>
+      <c r="AF83" s="6"/>
       <c r="AG83" t="s">
         <v>114</v>
       </c>
@@ -3234,12 +4735,29 @@
       <c r="F84" s="5">
         <v>36.979999999999997</v>
       </c>
-      <c r="T84" s="4"/>
-      <c r="U84" s="4"/>
-      <c r="V84" s="4">
+      <c r="L84" s="6"/>
+      <c r="M84" s="6"/>
+      <c r="N84" s="6"/>
+      <c r="O84" s="6"/>
+      <c r="P84" s="6"/>
+      <c r="Q84" s="6"/>
+      <c r="R84" s="6"/>
+      <c r="S84" s="6"/>
+      <c r="T84" s="6"/>
+      <c r="U84" s="6"/>
+      <c r="V84" s="6">
         <v>36.979999999999997</v>
       </c>
-      <c r="W84" s="4"/>
+      <c r="W84" s="6"/>
+      <c r="X84" s="6"/>
+      <c r="Y84" s="6"/>
+      <c r="Z84" s="6"/>
+      <c r="AA84" s="6"/>
+      <c r="AB84" s="6"/>
+      <c r="AC84" s="6"/>
+      <c r="AD84" s="6"/>
+      <c r="AE84" s="6"/>
+      <c r="AF84" s="6"/>
       <c r="AG84" t="s">
         <v>114</v>
       </c>
@@ -3257,10 +4775,27 @@
       <c r="E85">
         <v>56</v>
       </c>
-      <c r="T85" s="4"/>
-      <c r="U85" s="4"/>
-      <c r="V85" s="4"/>
-      <c r="W85" s="4"/>
+      <c r="L85" s="6"/>
+      <c r="M85" s="6"/>
+      <c r="N85" s="6"/>
+      <c r="O85" s="6"/>
+      <c r="P85" s="6"/>
+      <c r="Q85" s="6"/>
+      <c r="R85" s="6"/>
+      <c r="S85" s="6"/>
+      <c r="T85" s="6"/>
+      <c r="U85" s="6"/>
+      <c r="V85" s="6"/>
+      <c r="W85" s="6"/>
+      <c r="X85" s="6"/>
+      <c r="Y85" s="6"/>
+      <c r="Z85" s="6"/>
+      <c r="AA85" s="6"/>
+      <c r="AB85" s="6"/>
+      <c r="AC85" s="6"/>
+      <c r="AD85" s="6"/>
+      <c r="AE85" s="6"/>
+      <c r="AF85" s="6"/>
       <c r="AG85" t="s">
         <v>114</v>
       </c>
@@ -3281,12 +4816,29 @@
       <c r="J86">
         <v>628</v>
       </c>
-      <c r="T86" s="4"/>
-      <c r="U86" s="4"/>
-      <c r="V86" s="4">
+      <c r="L86" s="6"/>
+      <c r="M86" s="6"/>
+      <c r="N86" s="6"/>
+      <c r="O86" s="6"/>
+      <c r="P86" s="6"/>
+      <c r="Q86" s="6"/>
+      <c r="R86" s="6"/>
+      <c r="S86" s="6"/>
+      <c r="T86" s="6"/>
+      <c r="U86" s="6"/>
+      <c r="V86" s="6">
         <v>39.04</v>
       </c>
-      <c r="W86" s="4"/>
+      <c r="W86" s="6"/>
+      <c r="X86" s="6"/>
+      <c r="Y86" s="6"/>
+      <c r="Z86" s="6"/>
+      <c r="AA86" s="6"/>
+      <c r="AB86" s="6"/>
+      <c r="AC86" s="6"/>
+      <c r="AD86" s="6"/>
+      <c r="AE86" s="6"/>
+      <c r="AF86" s="6"/>
       <c r="AG86" t="s">
         <v>114</v>
       </c>
@@ -3304,10 +4856,27 @@
       <c r="E87">
         <v>39.5</v>
       </c>
-      <c r="T87" s="4"/>
-      <c r="U87" s="4"/>
-      <c r="V87" s="4"/>
-      <c r="W87" s="4"/>
+      <c r="L87" s="6"/>
+      <c r="M87" s="6"/>
+      <c r="N87" s="6"/>
+      <c r="O87" s="6"/>
+      <c r="P87" s="6"/>
+      <c r="Q87" s="6"/>
+      <c r="R87" s="6"/>
+      <c r="S87" s="6"/>
+      <c r="T87" s="6"/>
+      <c r="U87" s="6"/>
+      <c r="V87" s="6"/>
+      <c r="W87" s="6"/>
+      <c r="X87" s="6"/>
+      <c r="Y87" s="6"/>
+      <c r="Z87" s="6"/>
+      <c r="AA87" s="6"/>
+      <c r="AB87" s="6"/>
+      <c r="AC87" s="6"/>
+      <c r="AD87" s="6"/>
+      <c r="AE87" s="6"/>
+      <c r="AF87" s="6"/>
       <c r="AG87" t="s">
         <v>114</v>
       </c>
@@ -3325,12 +4894,29 @@
       <c r="F88" s="5">
         <v>34.42</v>
       </c>
-      <c r="T88" s="4"/>
-      <c r="U88" s="4"/>
-      <c r="V88" s="4">
+      <c r="L88" s="6"/>
+      <c r="M88" s="6"/>
+      <c r="N88" s="6"/>
+      <c r="O88" s="6"/>
+      <c r="P88" s="6"/>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="6"/>
+      <c r="T88" s="6"/>
+      <c r="U88" s="6"/>
+      <c r="V88" s="6">
         <v>34.42</v>
       </c>
-      <c r="W88" s="4"/>
+      <c r="W88" s="6"/>
+      <c r="X88" s="6"/>
+      <c r="Y88" s="6"/>
+      <c r="Z88" s="6"/>
+      <c r="AA88" s="6"/>
+      <c r="AB88" s="6"/>
+      <c r="AC88" s="6"/>
+      <c r="AD88" s="6"/>
+      <c r="AE88" s="6"/>
+      <c r="AF88" s="6"/>
       <c r="AG88" t="s">
         <v>114</v>
       </c>
@@ -3348,10 +4934,27 @@
       <c r="E89">
         <v>63.5</v>
       </c>
-      <c r="T89" s="4"/>
-      <c r="U89" s="4"/>
-      <c r="V89" s="4"/>
-      <c r="W89" s="4"/>
+      <c r="L89" s="6"/>
+      <c r="M89" s="6"/>
+      <c r="N89" s="6"/>
+      <c r="O89" s="6"/>
+      <c r="P89" s="6"/>
+      <c r="Q89" s="6"/>
+      <c r="R89" s="6"/>
+      <c r="S89" s="6"/>
+      <c r="T89" s="6"/>
+      <c r="U89" s="6"/>
+      <c r="V89" s="6"/>
+      <c r="W89" s="6"/>
+      <c r="X89" s="6"/>
+      <c r="Y89" s="6"/>
+      <c r="Z89" s="6"/>
+      <c r="AA89" s="6"/>
+      <c r="AB89" s="6"/>
+      <c r="AC89" s="6"/>
+      <c r="AD89" s="6"/>
+      <c r="AE89" s="6"/>
+      <c r="AF89" s="6"/>
       <c r="AG89" t="s">
         <v>114</v>
       </c>
@@ -3369,12 +4972,29 @@
       <c r="F90" s="5">
         <v>34.119999999999997</v>
       </c>
-      <c r="T90" s="4"/>
-      <c r="U90" s="4"/>
-      <c r="V90" s="4">
+      <c r="L90" s="6"/>
+      <c r="M90" s="6"/>
+      <c r="N90" s="6"/>
+      <c r="O90" s="6"/>
+      <c r="P90" s="6"/>
+      <c r="Q90" s="6"/>
+      <c r="R90" s="6"/>
+      <c r="S90" s="6"/>
+      <c r="T90" s="6"/>
+      <c r="U90" s="6"/>
+      <c r="V90" s="6">
         <v>34.119999999999997</v>
       </c>
-      <c r="W90" s="4"/>
+      <c r="W90" s="6"/>
+      <c r="X90" s="6"/>
+      <c r="Y90" s="6"/>
+      <c r="Z90" s="6"/>
+      <c r="AA90" s="6"/>
+      <c r="AB90" s="6"/>
+      <c r="AC90" s="6"/>
+      <c r="AD90" s="6"/>
+      <c r="AE90" s="6"/>
+      <c r="AF90" s="6"/>
       <c r="AG90" t="s">
         <v>114</v>
       </c>
@@ -3392,10 +5012,27 @@
       <c r="E91">
         <v>67.5</v>
       </c>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-      <c r="V91" s="4"/>
-      <c r="W91" s="4"/>
+      <c r="L91" s="6"/>
+      <c r="M91" s="6"/>
+      <c r="N91" s="6"/>
+      <c r="O91" s="6"/>
+      <c r="P91" s="6"/>
+      <c r="Q91" s="6"/>
+      <c r="R91" s="6"/>
+      <c r="S91" s="6"/>
+      <c r="T91" s="6"/>
+      <c r="U91" s="6"/>
+      <c r="V91" s="6"/>
+      <c r="W91" s="6"/>
+      <c r="X91" s="6"/>
+      <c r="Y91" s="6"/>
+      <c r="Z91" s="6"/>
+      <c r="AA91" s="6"/>
+      <c r="AB91" s="6"/>
+      <c r="AC91" s="6"/>
+      <c r="AD91" s="6"/>
+      <c r="AE91" s="6"/>
+      <c r="AF91" s="6"/>
       <c r="AG91" t="s">
         <v>114</v>
       </c>
@@ -3413,12 +5050,29 @@
       <c r="F92" s="5">
         <v>32.11</v>
       </c>
-      <c r="T92" s="4"/>
-      <c r="U92" s="4"/>
-      <c r="V92" s="4">
+      <c r="L92" s="6"/>
+      <c r="M92" s="6"/>
+      <c r="N92" s="6"/>
+      <c r="O92" s="6"/>
+      <c r="P92" s="6"/>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
+      <c r="V92" s="6">
         <v>32.11</v>
       </c>
-      <c r="W92" s="4"/>
+      <c r="W92" s="6"/>
+      <c r="X92" s="6"/>
+      <c r="Y92" s="6"/>
+      <c r="Z92" s="6"/>
+      <c r="AA92" s="6"/>
+      <c r="AB92" s="6"/>
+      <c r="AC92" s="6"/>
+      <c r="AD92" s="6"/>
+      <c r="AE92" s="6"/>
+      <c r="AF92" s="6"/>
       <c r="AG92" t="s">
         <v>114</v>
       </c>
@@ -3436,10 +5090,27 @@
       <c r="E93">
         <v>67.5</v>
       </c>
-      <c r="T93" s="4"/>
-      <c r="U93" s="4"/>
-      <c r="V93" s="4"/>
-      <c r="W93" s="4"/>
+      <c r="L93" s="6"/>
+      <c r="M93" s="6"/>
+      <c r="N93" s="6"/>
+      <c r="O93" s="6"/>
+      <c r="P93" s="6"/>
+      <c r="Q93" s="6"/>
+      <c r="R93" s="6"/>
+      <c r="S93" s="6"/>
+      <c r="T93" s="6"/>
+      <c r="U93" s="6"/>
+      <c r="V93" s="6"/>
+      <c r="W93" s="6"/>
+      <c r="X93" s="6"/>
+      <c r="Y93" s="6"/>
+      <c r="Z93" s="6"/>
+      <c r="AA93" s="6"/>
+      <c r="AB93" s="6"/>
+      <c r="AC93" s="6"/>
+      <c r="AD93" s="6"/>
+      <c r="AE93" s="6"/>
+      <c r="AF93" s="6"/>
       <c r="AG93" t="s">
         <v>114</v>
       </c>
@@ -3457,12 +5128,29 @@
       <c r="F94" s="5">
         <v>35.9</v>
       </c>
-      <c r="T94" s="4"/>
-      <c r="U94" s="4"/>
-      <c r="V94" s="4">
+      <c r="L94" s="6"/>
+      <c r="M94" s="6"/>
+      <c r="N94" s="6"/>
+      <c r="O94" s="6"/>
+      <c r="P94" s="6"/>
+      <c r="Q94" s="6"/>
+      <c r="R94" s="6"/>
+      <c r="S94" s="6"/>
+      <c r="T94" s="6"/>
+      <c r="U94" s="6"/>
+      <c r="V94" s="6">
         <v>35.9</v>
       </c>
-      <c r="W94" s="4"/>
+      <c r="W94" s="6"/>
+      <c r="X94" s="6"/>
+      <c r="Y94" s="6"/>
+      <c r="Z94" s="6"/>
+      <c r="AA94" s="6"/>
+      <c r="AB94" s="6"/>
+      <c r="AC94" s="6"/>
+      <c r="AD94" s="6"/>
+      <c r="AE94" s="6"/>
+      <c r="AF94" s="6"/>
       <c r="AG94" t="s">
         <v>114</v>
       </c>
@@ -3480,10 +5168,27 @@
       <c r="E95">
         <v>84.5</v>
       </c>
-      <c r="T95" s="4"/>
-      <c r="U95" s="4"/>
-      <c r="V95" s="4"/>
-      <c r="W95" s="4"/>
+      <c r="L95" s="6"/>
+      <c r="M95" s="6"/>
+      <c r="N95" s="6"/>
+      <c r="O95" s="6"/>
+      <c r="P95" s="6"/>
+      <c r="Q95" s="6"/>
+      <c r="R95" s="6"/>
+      <c r="S95" s="6"/>
+      <c r="T95" s="6"/>
+      <c r="U95" s="6"/>
+      <c r="V95" s="6"/>
+      <c r="W95" s="6"/>
+      <c r="X95" s="6"/>
+      <c r="Y95" s="6"/>
+      <c r="Z95" s="6"/>
+      <c r="AA95" s="6"/>
+      <c r="AB95" s="6"/>
+      <c r="AC95" s="6"/>
+      <c r="AD95" s="6"/>
+      <c r="AE95" s="6"/>
+      <c r="AF95" s="6"/>
       <c r="AG95" t="s">
         <v>114</v>
       </c>
@@ -3504,12 +5209,29 @@
       <c r="F96" s="5">
         <v>32.19</v>
       </c>
-      <c r="T96" s="4"/>
-      <c r="U96" s="4"/>
-      <c r="V96" s="4">
+      <c r="L96" s="6"/>
+      <c r="M96" s="6"/>
+      <c r="N96" s="6"/>
+      <c r="O96" s="6"/>
+      <c r="P96" s="6"/>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
+      <c r="V96" s="6">
         <v>32.19</v>
       </c>
-      <c r="W96" s="4"/>
+      <c r="W96" s="6"/>
+      <c r="X96" s="6"/>
+      <c r="Y96" s="6"/>
+      <c r="Z96" s="6"/>
+      <c r="AA96" s="6"/>
+      <c r="AB96" s="6"/>
+      <c r="AC96" s="6"/>
+      <c r="AD96" s="6"/>
+      <c r="AE96" s="6"/>
+      <c r="AF96" s="6"/>
       <c r="AG96" t="s">
         <v>114</v>
       </c>
@@ -3527,10 +5249,27 @@
       <c r="E97">
         <v>114.5</v>
       </c>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-      <c r="V97" s="4"/>
-      <c r="W97" s="4"/>
+      <c r="L97" s="6"/>
+      <c r="M97" s="6"/>
+      <c r="N97" s="6"/>
+      <c r="O97" s="6"/>
+      <c r="P97" s="6"/>
+      <c r="Q97" s="6"/>
+      <c r="R97" s="6"/>
+      <c r="S97" s="6"/>
+      <c r="T97" s="6"/>
+      <c r="U97" s="6"/>
+      <c r="V97" s="6"/>
+      <c r="W97" s="6"/>
+      <c r="X97" s="6"/>
+      <c r="Y97" s="6"/>
+      <c r="Z97" s="6"/>
+      <c r="AA97" s="6"/>
+      <c r="AB97" s="6"/>
+      <c r="AC97" s="6"/>
+      <c r="AD97" s="6"/>
+      <c r="AE97" s="6"/>
+      <c r="AF97" s="6"/>
       <c r="AG97" t="s">
         <v>114</v>
       </c>
@@ -3551,14 +5290,31 @@
       <c r="F98" s="5">
         <v>76.599999999999994</v>
       </c>
-      <c r="T98" s="4"/>
-      <c r="U98" s="4"/>
-      <c r="V98" s="4">
+      <c r="L98" s="6"/>
+      <c r="M98" s="6"/>
+      <c r="N98" s="6"/>
+      <c r="O98" s="6"/>
+      <c r="P98" s="6"/>
+      <c r="Q98" s="6"/>
+      <c r="R98" s="6"/>
+      <c r="S98" s="6"/>
+      <c r="T98" s="6"/>
+      <c r="U98" s="6"/>
+      <c r="V98" s="6">
         <v>37.72</v>
       </c>
-      <c r="W98" s="4">
+      <c r="W98" s="6">
         <v>38.880000000000003</v>
       </c>
+      <c r="X98" s="6"/>
+      <c r="Y98" s="6"/>
+      <c r="Z98" s="6"/>
+      <c r="AA98" s="6"/>
+      <c r="AB98" s="6"/>
+      <c r="AC98" s="6"/>
+      <c r="AD98" s="6"/>
+      <c r="AE98" s="6"/>
+      <c r="AF98" s="6"/>
       <c r="AG98" t="s">
         <v>114</v>
       </c>
@@ -3576,10 +5332,27 @@
       <c r="E99">
         <v>58.5</v>
       </c>
-      <c r="T99" s="4"/>
-      <c r="U99" s="4"/>
-      <c r="V99" s="4"/>
-      <c r="W99" s="4"/>
+      <c r="L99" s="6"/>
+      <c r="M99" s="6"/>
+      <c r="N99" s="6"/>
+      <c r="O99" s="6"/>
+      <c r="P99" s="6"/>
+      <c r="Q99" s="6"/>
+      <c r="R99" s="6"/>
+      <c r="S99" s="6"/>
+      <c r="T99" s="6"/>
+      <c r="U99" s="6"/>
+      <c r="V99" s="6"/>
+      <c r="W99" s="6"/>
+      <c r="X99" s="6"/>
+      <c r="Y99" s="6"/>
+      <c r="Z99" s="6"/>
+      <c r="AA99" s="6"/>
+      <c r="AB99" s="6"/>
+      <c r="AC99" s="6"/>
+      <c r="AD99" s="6"/>
+      <c r="AE99" s="6"/>
+      <c r="AF99" s="6"/>
       <c r="AG99" t="s">
         <v>114</v>
       </c>
@@ -3600,14 +5373,31 @@
       <c r="F100" s="5">
         <v>84.62</v>
       </c>
-      <c r="T100" s="4"/>
-      <c r="U100" s="4"/>
-      <c r="V100" s="4">
+      <c r="L100" s="6"/>
+      <c r="M100" s="6"/>
+      <c r="N100" s="6"/>
+      <c r="O100" s="6"/>
+      <c r="P100" s="6"/>
+      <c r="Q100" s="6"/>
+      <c r="R100" s="6"/>
+      <c r="S100" s="6"/>
+      <c r="T100" s="6"/>
+      <c r="U100" s="6"/>
+      <c r="V100" s="6">
         <v>36.840000000000003</v>
       </c>
-      <c r="W100" s="4">
+      <c r="W100" s="6">
         <v>47.78</v>
       </c>
+      <c r="X100" s="6"/>
+      <c r="Y100" s="6"/>
+      <c r="Z100" s="6"/>
+      <c r="AA100" s="6"/>
+      <c r="AB100" s="6"/>
+      <c r="AC100" s="6"/>
+      <c r="AD100" s="6"/>
+      <c r="AE100" s="6"/>
+      <c r="AF100" s="6"/>
       <c r="AG100" t="s">
         <v>114</v>
       </c>
@@ -3625,10 +5415,27 @@
       <c r="E101">
         <v>37.5</v>
       </c>
-      <c r="T101" s="4"/>
-      <c r="U101" s="4"/>
-      <c r="V101" s="4"/>
-      <c r="W101" s="4"/>
+      <c r="L101" s="6"/>
+      <c r="M101" s="6"/>
+      <c r="N101" s="6"/>
+      <c r="O101" s="6"/>
+      <c r="P101" s="6"/>
+      <c r="Q101" s="6"/>
+      <c r="R101" s="6"/>
+      <c r="S101" s="6"/>
+      <c r="T101" s="6"/>
+      <c r="U101" s="6"/>
+      <c r="V101" s="6"/>
+      <c r="W101" s="6"/>
+      <c r="X101" s="6"/>
+      <c r="Y101" s="6"/>
+      <c r="Z101" s="6"/>
+      <c r="AA101" s="6"/>
+      <c r="AB101" s="6"/>
+      <c r="AC101" s="6"/>
+      <c r="AD101" s="6"/>
+      <c r="AE101" s="6"/>
+      <c r="AF101" s="6"/>
       <c r="AG101" t="s">
         <v>114</v>
       </c>
@@ -3649,12 +5456,29 @@
       <c r="F102" s="5">
         <v>35.5</v>
       </c>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
-      <c r="V102" s="4">
+      <c r="L102" s="6"/>
+      <c r="M102" s="6"/>
+      <c r="N102" s="6"/>
+      <c r="O102" s="6"/>
+      <c r="P102" s="6"/>
+      <c r="Q102" s="6"/>
+      <c r="R102" s="6"/>
+      <c r="S102" s="6"/>
+      <c r="T102" s="6"/>
+      <c r="U102" s="6"/>
+      <c r="V102" s="6">
         <v>35.5</v>
       </c>
-      <c r="W102" s="4"/>
+      <c r="W102" s="6"/>
+      <c r="X102" s="6"/>
+      <c r="Y102" s="6"/>
+      <c r="Z102" s="6"/>
+      <c r="AA102" s="6"/>
+      <c r="AB102" s="6"/>
+      <c r="AC102" s="6"/>
+      <c r="AD102" s="6"/>
+      <c r="AE102" s="6"/>
+      <c r="AF102" s="6"/>
       <c r="AG102" t="s">
         <v>114</v>
       </c>
@@ -3672,10 +5496,27 @@
       <c r="E103">
         <v>32.5</v>
       </c>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
-      <c r="V103" s="4"/>
-      <c r="W103" s="4"/>
+      <c r="L103" s="6"/>
+      <c r="M103" s="6"/>
+      <c r="N103" s="6"/>
+      <c r="O103" s="6"/>
+      <c r="P103" s="6"/>
+      <c r="Q103" s="6"/>
+      <c r="R103" s="6"/>
+      <c r="S103" s="6"/>
+      <c r="T103" s="6"/>
+      <c r="U103" s="6"/>
+      <c r="V103" s="6"/>
+      <c r="W103" s="6"/>
+      <c r="X103" s="6"/>
+      <c r="Y103" s="6"/>
+      <c r="Z103" s="6"/>
+      <c r="AA103" s="6"/>
+      <c r="AB103" s="6"/>
+      <c r="AC103" s="6"/>
+      <c r="AD103" s="6"/>
+      <c r="AE103" s="6"/>
+      <c r="AF103" s="6"/>
       <c r="AG103" t="s">
         <v>114</v>
       </c>
@@ -3696,12 +5537,29 @@
       <c r="F104" s="5">
         <v>34.380000000000003</v>
       </c>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
-      <c r="V104" s="4">
+      <c r="L104" s="6"/>
+      <c r="M104" s="6"/>
+      <c r="N104" s="6"/>
+      <c r="O104" s="6"/>
+      <c r="P104" s="6"/>
+      <c r="Q104" s="6"/>
+      <c r="R104" s="6"/>
+      <c r="S104" s="6"/>
+      <c r="T104" s="6"/>
+      <c r="U104" s="6"/>
+      <c r="V104" s="6">
         <v>34.380000000000003</v>
       </c>
-      <c r="W104" s="4"/>
+      <c r="W104" s="6"/>
+      <c r="X104" s="6"/>
+      <c r="Y104" s="6"/>
+      <c r="Z104" s="6"/>
+      <c r="AA104" s="6"/>
+      <c r="AB104" s="6"/>
+      <c r="AC104" s="6"/>
+      <c r="AD104" s="6"/>
+      <c r="AE104" s="6"/>
+      <c r="AF104" s="6"/>
       <c r="AG104" t="s">
         <v>114</v>
       </c>
@@ -3719,10 +5577,27 @@
       <c r="E105">
         <v>5.5</v>
       </c>
-      <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
-      <c r="V105" s="4"/>
-      <c r="W105" s="4"/>
+      <c r="L105" s="6"/>
+      <c r="M105" s="6"/>
+      <c r="N105" s="6"/>
+      <c r="O105" s="6"/>
+      <c r="P105" s="6"/>
+      <c r="Q105" s="6"/>
+      <c r="R105" s="6"/>
+      <c r="S105" s="6"/>
+      <c r="T105" s="6"/>
+      <c r="U105" s="6"/>
+      <c r="V105" s="6"/>
+      <c r="W105" s="6"/>
+      <c r="X105" s="6"/>
+      <c r="Y105" s="6"/>
+      <c r="Z105" s="6"/>
+      <c r="AA105" s="6"/>
+      <c r="AB105" s="6"/>
+      <c r="AC105" s="6"/>
+      <c r="AD105" s="6"/>
+      <c r="AE105" s="6"/>
+      <c r="AF105" s="6"/>
       <c r="AG105" t="s">
         <v>114</v>
       </c>
@@ -3743,14 +5618,31 @@
       <c r="F106" s="5">
         <v>167.19</v>
       </c>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
-      <c r="V106" s="4">
+      <c r="L106" s="6"/>
+      <c r="M106" s="6"/>
+      <c r="N106" s="6"/>
+      <c r="O106" s="6"/>
+      <c r="P106" s="6"/>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
+      <c r="V106" s="6">
         <v>43.97</v>
       </c>
-      <c r="W106" s="4">
+      <c r="W106" s="6">
         <v>123.22</v>
       </c>
+      <c r="X106" s="6"/>
+      <c r="Y106" s="6"/>
+      <c r="Z106" s="6"/>
+      <c r="AA106" s="6"/>
+      <c r="AB106" s="6"/>
+      <c r="AC106" s="6"/>
+      <c r="AD106" s="6"/>
+      <c r="AE106" s="6"/>
+      <c r="AF106" s="6"/>
       <c r="AG106" t="s">
         <v>114</v>
       </c>
@@ -3768,10 +5660,27 @@
       <c r="E107">
         <v>2</v>
       </c>
-      <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
-      <c r="V107" s="4"/>
-      <c r="W107" s="4"/>
+      <c r="L107" s="6"/>
+      <c r="M107" s="6"/>
+      <c r="N107" s="6"/>
+      <c r="O107" s="6"/>
+      <c r="P107" s="6"/>
+      <c r="Q107" s="6"/>
+      <c r="R107" s="6"/>
+      <c r="S107" s="6"/>
+      <c r="T107" s="6"/>
+      <c r="U107" s="6"/>
+      <c r="V107" s="6"/>
+      <c r="W107" s="6"/>
+      <c r="X107" s="6"/>
+      <c r="Y107" s="6"/>
+      <c r="Z107" s="6"/>
+      <c r="AA107" s="6"/>
+      <c r="AB107" s="6"/>
+      <c r="AC107" s="6"/>
+      <c r="AD107" s="6"/>
+      <c r="AE107" s="6"/>
+      <c r="AF107" s="6"/>
       <c r="AG107" t="s">
         <v>114</v>
       </c>
@@ -3795,12 +5704,29 @@
       <c r="J108">
         <v>531</v>
       </c>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
-      <c r="V108" s="4"/>
-      <c r="W108" s="4">
+      <c r="L108" s="6"/>
+      <c r="M108" s="6"/>
+      <c r="N108" s="6"/>
+      <c r="O108" s="6"/>
+      <c r="P108" s="6"/>
+      <c r="Q108" s="6"/>
+      <c r="R108" s="6"/>
+      <c r="S108" s="6"/>
+      <c r="T108" s="6"/>
+      <c r="U108" s="6"/>
+      <c r="V108" s="6"/>
+      <c r="W108" s="6">
         <v>189</v>
       </c>
+      <c r="X108" s="6"/>
+      <c r="Y108" s="6"/>
+      <c r="Z108" s="6"/>
+      <c r="AA108" s="6"/>
+      <c r="AB108" s="6"/>
+      <c r="AC108" s="6"/>
+      <c r="AD108" s="6"/>
+      <c r="AE108" s="6"/>
+      <c r="AF108" s="6"/>
       <c r="AG108" t="s">
         <v>114</v>
       </c>
@@ -3821,9 +5747,29 @@
       <c r="F109" s="5">
         <v>70.930000000000007</v>
       </c>
-      <c r="W109">
+      <c r="L109" s="6"/>
+      <c r="M109" s="6"/>
+      <c r="N109" s="6"/>
+      <c r="O109" s="6"/>
+      <c r="P109" s="6"/>
+      <c r="Q109" s="6"/>
+      <c r="R109" s="6"/>
+      <c r="S109" s="6"/>
+      <c r="T109" s="6"/>
+      <c r="U109" s="6"/>
+      <c r="V109" s="6"/>
+      <c r="W109" s="6">
         <v>70.930000000000007</v>
       </c>
+      <c r="X109" s="6"/>
+      <c r="Y109" s="6"/>
+      <c r="Z109" s="6"/>
+      <c r="AA109" s="6"/>
+      <c r="AB109" s="6"/>
+      <c r="AC109" s="6"/>
+      <c r="AD109" s="6"/>
+      <c r="AE109" s="6"/>
+      <c r="AF109" s="6"/>
       <c r="AG109" t="s">
         <v>114</v>
       </c>
@@ -3847,12 +5793,31 @@
       <c r="I110">
         <v>223</v>
       </c>
-      <c r="V110">
+      <c r="L110" s="6"/>
+      <c r="M110" s="6"/>
+      <c r="N110" s="6"/>
+      <c r="O110" s="6"/>
+      <c r="P110" s="6"/>
+      <c r="Q110" s="6"/>
+      <c r="R110" s="6"/>
+      <c r="S110" s="6"/>
+      <c r="T110" s="6"/>
+      <c r="U110" s="6"/>
+      <c r="V110" s="6">
         <v>329.56</v>
       </c>
-      <c r="W110" s="4">
+      <c r="W110" s="6">
         <v>34.29</v>
       </c>
+      <c r="X110" s="6"/>
+      <c r="Y110" s="6"/>
+      <c r="Z110" s="6"/>
+      <c r="AA110" s="6"/>
+      <c r="AB110" s="6"/>
+      <c r="AC110" s="6"/>
+      <c r="AD110" s="6"/>
+      <c r="AE110" s="6"/>
+      <c r="AF110" s="6"/>
       <c r="AG110" t="s">
         <v>114</v>
       </c>
@@ -3873,9 +5838,29 @@
       <c r="F111" s="5">
         <v>19.84</v>
       </c>
-      <c r="X111">
+      <c r="L111" s="6"/>
+      <c r="M111" s="6"/>
+      <c r="N111" s="6"/>
+      <c r="O111" s="6"/>
+      <c r="P111" s="6"/>
+      <c r="Q111" s="6"/>
+      <c r="R111" s="6"/>
+      <c r="S111" s="6"/>
+      <c r="T111" s="6"/>
+      <c r="U111" s="6"/>
+      <c r="V111" s="6"/>
+      <c r="W111" s="6"/>
+      <c r="X111" s="6">
         <v>19.84</v>
       </c>
+      <c r="Y111" s="6"/>
+      <c r="Z111" s="6"/>
+      <c r="AA111" s="6"/>
+      <c r="AB111" s="6"/>
+      <c r="AC111" s="6"/>
+      <c r="AD111" s="6"/>
+      <c r="AE111" s="6"/>
+      <c r="AF111" s="6"/>
       <c r="AG111" t="s">
         <v>114</v>
       </c>
@@ -3896,12 +5881,31 @@
       <c r="F112" s="5">
         <v>89.05</v>
       </c>
-      <c r="V112">
+      <c r="L112" s="6"/>
+      <c r="M112" s="6"/>
+      <c r="N112" s="6"/>
+      <c r="O112" s="6"/>
+      <c r="P112" s="6"/>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
+      <c r="V112" s="6">
         <v>32.99</v>
       </c>
-      <c r="W112">
+      <c r="W112" s="6">
         <v>56.06</v>
       </c>
+      <c r="X112" s="6"/>
+      <c r="Y112" s="6"/>
+      <c r="Z112" s="6"/>
+      <c r="AA112" s="6"/>
+      <c r="AB112" s="6"/>
+      <c r="AC112" s="6"/>
+      <c r="AD112" s="6"/>
+      <c r="AE112" s="6"/>
+      <c r="AF112" s="6"/>
       <c r="AG112" t="s">
         <v>114</v>
       </c>
@@ -3919,6 +5923,27 @@
       <c r="E113">
         <v>2</v>
       </c>
+      <c r="L113" s="6"/>
+      <c r="M113" s="6"/>
+      <c r="N113" s="6"/>
+      <c r="O113" s="6"/>
+      <c r="P113" s="6"/>
+      <c r="Q113" s="6"/>
+      <c r="R113" s="6"/>
+      <c r="S113" s="6"/>
+      <c r="T113" s="6"/>
+      <c r="U113" s="6"/>
+      <c r="V113" s="6"/>
+      <c r="W113" s="6"/>
+      <c r="X113" s="6"/>
+      <c r="Y113" s="6"/>
+      <c r="Z113" s="6"/>
+      <c r="AA113" s="6"/>
+      <c r="AB113" s="6"/>
+      <c r="AC113" s="6"/>
+      <c r="AD113" s="6"/>
+      <c r="AE113" s="6"/>
+      <c r="AF113" s="6"/>
       <c r="AG113" t="s">
         <v>114</v>
       </c>
@@ -3939,9 +5964,29 @@
       <c r="F114" s="5">
         <v>35.479999999999997</v>
       </c>
-      <c r="V114">
+      <c r="L114" s="6"/>
+      <c r="M114" s="6"/>
+      <c r="N114" s="6"/>
+      <c r="O114" s="6"/>
+      <c r="P114" s="6"/>
+      <c r="Q114" s="6"/>
+      <c r="R114" s="6"/>
+      <c r="S114" s="6"/>
+      <c r="T114" s="6"/>
+      <c r="U114" s="6"/>
+      <c r="V114" s="6">
         <v>35.479999999999997</v>
       </c>
+      <c r="W114" s="6"/>
+      <c r="X114" s="6"/>
+      <c r="Y114" s="6"/>
+      <c r="Z114" s="6"/>
+      <c r="AA114" s="6"/>
+      <c r="AB114" s="6"/>
+      <c r="AC114" s="6"/>
+      <c r="AD114" s="6"/>
+      <c r="AE114" s="6"/>
+      <c r="AF114" s="6"/>
       <c r="AG114" t="s">
         <v>114</v>
       </c>
@@ -3959,6 +6004,27 @@
       <c r="E115">
         <v>26</v>
       </c>
+      <c r="L115" s="6"/>
+      <c r="M115" s="6"/>
+      <c r="N115" s="6"/>
+      <c r="O115" s="6"/>
+      <c r="P115" s="6"/>
+      <c r="Q115" s="6"/>
+      <c r="R115" s="6"/>
+      <c r="S115" s="6"/>
+      <c r="T115" s="6"/>
+      <c r="U115" s="6"/>
+      <c r="V115" s="6"/>
+      <c r="W115" s="6"/>
+      <c r="X115" s="6"/>
+      <c r="Y115" s="6"/>
+      <c r="Z115" s="6"/>
+      <c r="AA115" s="6"/>
+      <c r="AB115" s="6"/>
+      <c r="AC115" s="6"/>
+      <c r="AD115" s="6"/>
+      <c r="AE115" s="6"/>
+      <c r="AF115" s="6"/>
       <c r="AG115" t="s">
         <v>114</v>
       </c>
@@ -3979,12 +6045,31 @@
       <c r="F116" s="5">
         <v>206.17</v>
       </c>
-      <c r="V116">
+      <c r="L116" s="6"/>
+      <c r="M116" s="6"/>
+      <c r="N116" s="6"/>
+      <c r="O116" s="6"/>
+      <c r="P116" s="6"/>
+      <c r="Q116" s="6"/>
+      <c r="R116" s="6"/>
+      <c r="S116" s="6"/>
+      <c r="T116" s="6"/>
+      <c r="U116" s="6"/>
+      <c r="V116" s="6">
         <v>129.66999999999999</v>
       </c>
-      <c r="W116">
+      <c r="W116" s="6">
         <v>76.5</v>
       </c>
+      <c r="X116" s="6"/>
+      <c r="Y116" s="6"/>
+      <c r="Z116" s="6"/>
+      <c r="AA116" s="6"/>
+      <c r="AB116" s="6"/>
+      <c r="AC116" s="6"/>
+      <c r="AD116" s="6"/>
+      <c r="AE116" s="6"/>
+      <c r="AF116" s="6"/>
       <c r="AG116" t="s">
         <v>114</v>
       </c>
@@ -4002,6 +6087,27 @@
       <c r="E117">
         <v>86</v>
       </c>
+      <c r="L117" s="6"/>
+      <c r="M117" s="6"/>
+      <c r="N117" s="6"/>
+      <c r="O117" s="6"/>
+      <c r="P117" s="6"/>
+      <c r="Q117" s="6"/>
+      <c r="R117" s="6"/>
+      <c r="S117" s="6"/>
+      <c r="T117" s="6"/>
+      <c r="U117" s="6"/>
+      <c r="V117" s="6"/>
+      <c r="W117" s="6"/>
+      <c r="X117" s="6"/>
+      <c r="Y117" s="6"/>
+      <c r="Z117" s="6"/>
+      <c r="AA117" s="6"/>
+      <c r="AB117" s="6"/>
+      <c r="AC117" s="6"/>
+      <c r="AD117" s="6"/>
+      <c r="AE117" s="6"/>
+      <c r="AF117" s="6"/>
       <c r="AG117" t="s">
         <v>114</v>
       </c>
@@ -4022,12 +6128,31 @@
       <c r="F118" s="5">
         <v>97.16</v>
       </c>
-      <c r="V118">
+      <c r="L118" s="6"/>
+      <c r="M118" s="6"/>
+      <c r="N118" s="6"/>
+      <c r="O118" s="6"/>
+      <c r="P118" s="6"/>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
+      <c r="V118" s="6">
         <v>68.16</v>
       </c>
-      <c r="W118">
+      <c r="W118" s="6">
         <v>29</v>
       </c>
+      <c r="X118" s="6"/>
+      <c r="Y118" s="6"/>
+      <c r="Z118" s="6"/>
+      <c r="AA118" s="6"/>
+      <c r="AB118" s="6"/>
+      <c r="AC118" s="6"/>
+      <c r="AD118" s="6"/>
+      <c r="AE118" s="6"/>
+      <c r="AF118" s="6"/>
       <c r="AG118" t="s">
         <v>114</v>
       </c>
@@ -4045,6 +6170,27 @@
       <c r="E119">
         <v>40.5</v>
       </c>
+      <c r="L119" s="6"/>
+      <c r="M119" s="6"/>
+      <c r="N119" s="6"/>
+      <c r="O119" s="6"/>
+      <c r="P119" s="6"/>
+      <c r="Q119" s="6"/>
+      <c r="R119" s="6"/>
+      <c r="S119" s="6"/>
+      <c r="T119" s="6"/>
+      <c r="U119" s="6"/>
+      <c r="V119" s="6"/>
+      <c r="W119" s="6"/>
+      <c r="X119" s="6"/>
+      <c r="Y119" s="6"/>
+      <c r="Z119" s="6"/>
+      <c r="AA119" s="6"/>
+      <c r="AB119" s="6"/>
+      <c r="AC119" s="6"/>
+      <c r="AD119" s="6"/>
+      <c r="AE119" s="6"/>
+      <c r="AF119" s="6"/>
       <c r="AG119" t="s">
         <v>114</v>
       </c>
@@ -4065,9 +6211,29 @@
       <c r="F120" s="5">
         <v>35.42</v>
       </c>
-      <c r="V120">
+      <c r="L120" s="6"/>
+      <c r="M120" s="6"/>
+      <c r="N120" s="6"/>
+      <c r="O120" s="6"/>
+      <c r="P120" s="6"/>
+      <c r="Q120" s="6"/>
+      <c r="R120" s="6"/>
+      <c r="S120" s="6"/>
+      <c r="T120" s="6"/>
+      <c r="U120" s="6"/>
+      <c r="V120" s="6">
         <v>35.42</v>
       </c>
+      <c r="W120" s="6"/>
+      <c r="X120" s="6"/>
+      <c r="Y120" s="6"/>
+      <c r="Z120" s="6"/>
+      <c r="AA120" s="6"/>
+      <c r="AB120" s="6"/>
+      <c r="AC120" s="6"/>
+      <c r="AD120" s="6"/>
+      <c r="AE120" s="6"/>
+      <c r="AF120" s="6"/>
       <c r="AG120" t="s">
         <v>114</v>
       </c>
@@ -4085,6 +6251,27 @@
       <c r="E121">
         <v>2</v>
       </c>
+      <c r="L121" s="6"/>
+      <c r="M121" s="6"/>
+      <c r="N121" s="6"/>
+      <c r="O121" s="6"/>
+      <c r="P121" s="6"/>
+      <c r="Q121" s="6"/>
+      <c r="R121" s="6"/>
+      <c r="S121" s="6"/>
+      <c r="T121" s="6"/>
+      <c r="U121" s="6"/>
+      <c r="V121" s="6"/>
+      <c r="W121" s="6"/>
+      <c r="X121" s="6"/>
+      <c r="Y121" s="6"/>
+      <c r="Z121" s="6"/>
+      <c r="AA121" s="6"/>
+      <c r="AB121" s="6"/>
+      <c r="AC121" s="6"/>
+      <c r="AD121" s="6"/>
+      <c r="AE121" s="6"/>
+      <c r="AF121" s="6"/>
       <c r="AG121" t="s">
         <v>114</v>
       </c>
@@ -4105,9 +6292,29 @@
       <c r="F122" s="5">
         <v>34.409999999999997</v>
       </c>
-      <c r="V122">
+      <c r="L122" s="6"/>
+      <c r="M122" s="6"/>
+      <c r="N122" s="6"/>
+      <c r="O122" s="6"/>
+      <c r="P122" s="6"/>
+      <c r="Q122" s="6"/>
+      <c r="R122" s="6"/>
+      <c r="S122" s="6"/>
+      <c r="T122" s="6"/>
+      <c r="U122" s="6"/>
+      <c r="V122" s="6">
         <v>34.409999999999997</v>
       </c>
+      <c r="W122" s="6"/>
+      <c r="X122" s="6"/>
+      <c r="Y122" s="6"/>
+      <c r="Z122" s="6"/>
+      <c r="AA122" s="6"/>
+      <c r="AB122" s="6"/>
+      <c r="AC122" s="6"/>
+      <c r="AD122" s="6"/>
+      <c r="AE122" s="6"/>
+      <c r="AF122" s="6"/>
       <c r="AG122" t="s">
         <v>114</v>
       </c>
@@ -4125,6 +6332,27 @@
       <c r="E123">
         <v>2</v>
       </c>
+      <c r="L123" s="6"/>
+      <c r="M123" s="6"/>
+      <c r="N123" s="6"/>
+      <c r="O123" s="6"/>
+      <c r="P123" s="6"/>
+      <c r="Q123" s="6"/>
+      <c r="R123" s="6"/>
+      <c r="S123" s="6"/>
+      <c r="T123" s="6"/>
+      <c r="U123" s="6"/>
+      <c r="V123" s="6"/>
+      <c r="W123" s="6"/>
+      <c r="X123" s="6"/>
+      <c r="Y123" s="6"/>
+      <c r="Z123" s="6"/>
+      <c r="AA123" s="6"/>
+      <c r="AB123" s="6"/>
+      <c r="AC123" s="6"/>
+      <c r="AD123" s="6"/>
+      <c r="AE123" s="6"/>
+      <c r="AF123" s="6"/>
       <c r="AG123" t="s">
         <v>114</v>
       </c>
@@ -4145,9 +6373,29 @@
       <c r="F124" s="5">
         <v>47.44</v>
       </c>
-      <c r="V124">
+      <c r="L124" s="6"/>
+      <c r="M124" s="6"/>
+      <c r="N124" s="6"/>
+      <c r="O124" s="6"/>
+      <c r="P124" s="6"/>
+      <c r="Q124" s="6"/>
+      <c r="R124" s="6"/>
+      <c r="S124" s="6"/>
+      <c r="T124" s="6"/>
+      <c r="U124" s="6"/>
+      <c r="V124" s="6">
         <v>47.44</v>
       </c>
+      <c r="W124" s="6"/>
+      <c r="X124" s="6"/>
+      <c r="Y124" s="6"/>
+      <c r="Z124" s="6"/>
+      <c r="AA124" s="6"/>
+      <c r="AB124" s="6"/>
+      <c r="AC124" s="6"/>
+      <c r="AD124" s="6"/>
+      <c r="AE124" s="6"/>
+      <c r="AF124" s="6"/>
       <c r="AG124" t="s">
         <v>114</v>
       </c>
@@ -4165,6 +6413,27 @@
       <c r="E125">
         <v>9.5</v>
       </c>
+      <c r="L125" s="6"/>
+      <c r="M125" s="6"/>
+      <c r="N125" s="6"/>
+      <c r="O125" s="6"/>
+      <c r="P125" s="6"/>
+      <c r="Q125" s="6"/>
+      <c r="R125" s="6"/>
+      <c r="S125" s="6"/>
+      <c r="T125" s="6"/>
+      <c r="U125" s="6"/>
+      <c r="V125" s="6"/>
+      <c r="W125" s="6"/>
+      <c r="X125" s="6"/>
+      <c r="Y125" s="6"/>
+      <c r="Z125" s="6"/>
+      <c r="AA125" s="6"/>
+      <c r="AB125" s="6"/>
+      <c r="AC125" s="6"/>
+      <c r="AD125" s="6"/>
+      <c r="AE125" s="6"/>
+      <c r="AF125" s="6"/>
       <c r="AG125" t="s">
         <v>114</v>
       </c>
@@ -4185,12 +6454,31 @@
       <c r="F126" s="5">
         <v>255.86</v>
       </c>
-      <c r="V126">
+      <c r="L126" s="6"/>
+      <c r="M126" s="6"/>
+      <c r="N126" s="6"/>
+      <c r="O126" s="6"/>
+      <c r="P126" s="6"/>
+      <c r="Q126" s="6"/>
+      <c r="R126" s="6"/>
+      <c r="S126" s="6"/>
+      <c r="T126" s="6"/>
+      <c r="U126" s="6"/>
+      <c r="V126" s="6">
         <v>67.05</v>
       </c>
-      <c r="X126">
+      <c r="W126" s="6"/>
+      <c r="X126" s="6">
         <v>188.81</v>
       </c>
+      <c r="Y126" s="6"/>
+      <c r="Z126" s="6"/>
+      <c r="AA126" s="6"/>
+      <c r="AB126" s="6"/>
+      <c r="AC126" s="6"/>
+      <c r="AD126" s="6"/>
+      <c r="AE126" s="6"/>
+      <c r="AF126" s="6"/>
       <c r="AG126" t="s">
         <v>114</v>
       </c>
@@ -4211,6 +6499,27 @@
       <c r="F127" s="5">
         <v>0</v>
       </c>
+      <c r="L127" s="6"/>
+      <c r="M127" s="6"/>
+      <c r="N127" s="6"/>
+      <c r="O127" s="6"/>
+      <c r="P127" s="6"/>
+      <c r="Q127" s="6"/>
+      <c r="R127" s="6"/>
+      <c r="S127" s="6"/>
+      <c r="T127" s="6"/>
+      <c r="U127" s="6"/>
+      <c r="V127" s="6"/>
+      <c r="W127" s="6"/>
+      <c r="X127" s="6"/>
+      <c r="Y127" s="6"/>
+      <c r="Z127" s="6"/>
+      <c r="AA127" s="6"/>
+      <c r="AB127" s="6"/>
+      <c r="AC127" s="6"/>
+      <c r="AD127" s="6"/>
+      <c r="AE127" s="6"/>
+      <c r="AF127" s="6"/>
       <c r="AG127" t="s">
         <v>114</v>
       </c>
@@ -4243,12 +6552,31 @@
       <c r="J128">
         <v>2397</v>
       </c>
-      <c r="S128">
+      <c r="L128" s="6"/>
+      <c r="M128" s="6"/>
+      <c r="N128" s="6"/>
+      <c r="O128" s="6"/>
+      <c r="P128" s="6"/>
+      <c r="Q128" s="6"/>
+      <c r="R128" s="6"/>
+      <c r="S128" s="6">
         <v>162.16499999999999</v>
       </c>
-      <c r="T128">
+      <c r="T128" s="6">
         <v>283.32499999999999</v>
       </c>
+      <c r="U128" s="6"/>
+      <c r="V128" s="6"/>
+      <c r="W128" s="6"/>
+      <c r="X128" s="6"/>
+      <c r="Y128" s="6"/>
+      <c r="Z128" s="6"/>
+      <c r="AA128" s="6"/>
+      <c r="AB128" s="6"/>
+      <c r="AC128" s="6"/>
+      <c r="AD128" s="6"/>
+      <c r="AE128" s="6"/>
+      <c r="AF128" s="6"/>
       <c r="AG128" t="s">
         <v>114</v>
       </c>
@@ -4269,9 +6597,29 @@
       <c r="F129" s="5">
         <v>75.599999999999994</v>
       </c>
-      <c r="T129">
+      <c r="L129" s="6"/>
+      <c r="M129" s="6"/>
+      <c r="N129" s="6"/>
+      <c r="O129" s="6"/>
+      <c r="P129" s="6"/>
+      <c r="Q129" s="6"/>
+      <c r="R129" s="6"/>
+      <c r="S129" s="6"/>
+      <c r="T129" s="6">
         <v>75.599999999999994</v>
       </c>
+      <c r="U129" s="6"/>
+      <c r="V129" s="6"/>
+      <c r="W129" s="6"/>
+      <c r="X129" s="6"/>
+      <c r="Y129" s="6"/>
+      <c r="Z129" s="6"/>
+      <c r="AA129" s="6"/>
+      <c r="AB129" s="6"/>
+      <c r="AC129" s="6"/>
+      <c r="AD129" s="6"/>
+      <c r="AE129" s="6"/>
+      <c r="AF129" s="6"/>
       <c r="AG129" t="s">
         <v>114</v>
       </c>
@@ -4295,9 +6643,29 @@
       <c r="I130">
         <v>788</v>
       </c>
-      <c r="T130">
+      <c r="L130" s="6"/>
+      <c r="M130" s="6"/>
+      <c r="N130" s="6"/>
+      <c r="O130" s="6"/>
+      <c r="P130" s="6"/>
+      <c r="Q130" s="6"/>
+      <c r="R130" s="6"/>
+      <c r="S130" s="6"/>
+      <c r="T130" s="6">
         <v>629.14</v>
       </c>
+      <c r="U130" s="6"/>
+      <c r="V130" s="6"/>
+      <c r="W130" s="6"/>
+      <c r="X130" s="6"/>
+      <c r="Y130" s="6"/>
+      <c r="Z130" s="6"/>
+      <c r="AA130" s="6"/>
+      <c r="AB130" s="6"/>
+      <c r="AC130" s="6"/>
+      <c r="AD130" s="6"/>
+      <c r="AE130" s="6"/>
+      <c r="AF130" s="6"/>
       <c r="AG130" t="s">
         <v>114</v>
       </c>
@@ -4318,9 +6686,29 @@
       <c r="F131" s="5">
         <v>37.89</v>
       </c>
-      <c r="T131">
+      <c r="L131" s="6"/>
+      <c r="M131" s="6"/>
+      <c r="N131" s="6"/>
+      <c r="O131" s="6"/>
+      <c r="P131" s="6"/>
+      <c r="Q131" s="6"/>
+      <c r="R131" s="6"/>
+      <c r="S131" s="6"/>
+      <c r="T131" s="6">
         <v>37.89</v>
       </c>
+      <c r="U131" s="6"/>
+      <c r="V131" s="6"/>
+      <c r="W131" s="6"/>
+      <c r="X131" s="6"/>
+      <c r="Y131" s="6"/>
+      <c r="Z131" s="6"/>
+      <c r="AA131" s="6"/>
+      <c r="AB131" s="6"/>
+      <c r="AC131" s="6"/>
+      <c r="AD131" s="6"/>
+      <c r="AE131" s="6"/>
+      <c r="AF131" s="6"/>
       <c r="AG131" t="s">
         <v>114</v>
       </c>
@@ -4344,9 +6732,29 @@
       <c r="I132">
         <v>654</v>
       </c>
-      <c r="T132">
+      <c r="L132" s="6"/>
+      <c r="M132" s="6"/>
+      <c r="N132" s="6"/>
+      <c r="O132" s="6"/>
+      <c r="P132" s="6"/>
+      <c r="Q132" s="6"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="6"/>
+      <c r="T132" s="6">
         <v>108.02</v>
       </c>
+      <c r="U132" s="6"/>
+      <c r="V132" s="6"/>
+      <c r="W132" s="6"/>
+      <c r="X132" s="6"/>
+      <c r="Y132" s="6"/>
+      <c r="Z132" s="6"/>
+      <c r="AA132" s="6"/>
+      <c r="AB132" s="6"/>
+      <c r="AC132" s="6"/>
+      <c r="AD132" s="6"/>
+      <c r="AE132" s="6"/>
+      <c r="AF132" s="6"/>
       <c r="AG132" t="s">
         <v>114</v>
       </c>
@@ -4367,9 +6775,29 @@
       <c r="F133" s="5">
         <v>1.55</v>
       </c>
-      <c r="T133">
+      <c r="L133" s="6"/>
+      <c r="M133" s="6"/>
+      <c r="N133" s="6"/>
+      <c r="O133" s="6"/>
+      <c r="P133" s="6"/>
+      <c r="Q133" s="6"/>
+      <c r="R133" s="6"/>
+      <c r="S133" s="6"/>
+      <c r="T133" s="6">
         <v>1.55</v>
       </c>
+      <c r="U133" s="6"/>
+      <c r="V133" s="6"/>
+      <c r="W133" s="6"/>
+      <c r="X133" s="6"/>
+      <c r="Y133" s="6"/>
+      <c r="Z133" s="6"/>
+      <c r="AA133" s="6"/>
+      <c r="AB133" s="6"/>
+      <c r="AC133" s="6"/>
+      <c r="AD133" s="6"/>
+      <c r="AE133" s="6"/>
+      <c r="AF133" s="6"/>
       <c r="AG133" t="s">
         <v>114</v>
       </c>
@@ -4396,9 +6824,29 @@
       <c r="J134">
         <v>393</v>
       </c>
-      <c r="R134">
+      <c r="L134" s="6"/>
+      <c r="M134" s="6"/>
+      <c r="N134" s="6"/>
+      <c r="O134" s="6"/>
+      <c r="P134" s="6"/>
+      <c r="Q134" s="6"/>
+      <c r="R134" s="6">
         <v>296.60000000000002</v>
       </c>
+      <c r="S134" s="6"/>
+      <c r="T134" s="6"/>
+      <c r="U134" s="6"/>
+      <c r="V134" s="6"/>
+      <c r="W134" s="6"/>
+      <c r="X134" s="6"/>
+      <c r="Y134" s="6"/>
+      <c r="Z134" s="6"/>
+      <c r="AA134" s="6"/>
+      <c r="AB134" s="6"/>
+      <c r="AC134" s="6"/>
+      <c r="AD134" s="6"/>
+      <c r="AE134" s="6"/>
+      <c r="AF134" s="6"/>
       <c r="AG134" t="s">
         <v>114</v>
       </c>
@@ -4419,6 +6867,27 @@
       <c r="F135" s="5">
         <v>0</v>
       </c>
+      <c r="L135" s="6"/>
+      <c r="M135" s="6"/>
+      <c r="N135" s="6"/>
+      <c r="O135" s="6"/>
+      <c r="P135" s="6"/>
+      <c r="Q135" s="6"/>
+      <c r="R135" s="6"/>
+      <c r="S135" s="6"/>
+      <c r="T135" s="6"/>
+      <c r="U135" s="6"/>
+      <c r="V135" s="6"/>
+      <c r="W135" s="6"/>
+      <c r="X135" s="6"/>
+      <c r="Y135" s="6"/>
+      <c r="Z135" s="6"/>
+      <c r="AA135" s="6"/>
+      <c r="AB135" s="6"/>
+      <c r="AC135" s="6"/>
+      <c r="AD135" s="6"/>
+      <c r="AE135" s="6"/>
+      <c r="AF135" s="6"/>
       <c r="AG135" t="s">
         <v>114</v>
       </c>
@@ -4442,15 +6911,33 @@
       <c r="I136">
         <v>118</v>
       </c>
-      <c r="R136">
+      <c r="L136" s="6"/>
+      <c r="M136" s="6"/>
+      <c r="N136" s="6"/>
+      <c r="O136" s="6"/>
+      <c r="P136" s="6"/>
+      <c r="Q136" s="6"/>
+      <c r="R136" s="6">
         <v>102.5</v>
       </c>
-      <c r="U136">
+      <c r="S136" s="6"/>
+      <c r="T136" s="6"/>
+      <c r="U136" s="6">
         <v>28.8</v>
       </c>
-      <c r="V136">
+      <c r="V136" s="6">
         <v>73</v>
       </c>
+      <c r="W136" s="6"/>
+      <c r="X136" s="6"/>
+      <c r="Y136" s="6"/>
+      <c r="Z136" s="6"/>
+      <c r="AA136" s="6"/>
+      <c r="AB136" s="6"/>
+      <c r="AC136" s="6"/>
+      <c r="AD136" s="6"/>
+      <c r="AE136" s="6"/>
+      <c r="AF136" s="6"/>
       <c r="AG136" t="s">
         <v>115</v>
       </c>
@@ -4471,12 +6958,31 @@
       <c r="F137" s="5">
         <v>48</v>
       </c>
-      <c r="R137">
+      <c r="L137" s="6"/>
+      <c r="M137" s="6"/>
+      <c r="N137" s="6"/>
+      <c r="O137" s="6"/>
+      <c r="P137" s="6"/>
+      <c r="Q137" s="6"/>
+      <c r="R137" s="6">
         <v>16</v>
       </c>
-      <c r="V137">
+      <c r="S137" s="6"/>
+      <c r="T137" s="6"/>
+      <c r="U137" s="6"/>
+      <c r="V137" s="6">
         <v>32</v>
       </c>
+      <c r="W137" s="6"/>
+      <c r="X137" s="6"/>
+      <c r="Y137" s="6"/>
+      <c r="Z137" s="6"/>
+      <c r="AA137" s="6"/>
+      <c r="AB137" s="6"/>
+      <c r="AC137" s="6"/>
+      <c r="AD137" s="6"/>
+      <c r="AE137" s="6"/>
+      <c r="AF137" s="6"/>
       <c r="AG137" t="s">
         <v>115</v>
       </c>
@@ -4500,9 +7006,29 @@
       <c r="I138">
         <v>2295</v>
       </c>
-      <c r="X138" s="6">
+      <c r="L138" s="6"/>
+      <c r="M138" s="6"/>
+      <c r="N138" s="6"/>
+      <c r="O138" s="6"/>
+      <c r="P138" s="6"/>
+      <c r="Q138" s="6"/>
+      <c r="R138" s="6"/>
+      <c r="S138" s="6"/>
+      <c r="T138" s="6"/>
+      <c r="U138" s="6"/>
+      <c r="V138" s="6"/>
+      <c r="W138" s="6"/>
+      <c r="X138" s="7">
         <v>220.59</v>
       </c>
+      <c r="Y138" s="6"/>
+      <c r="Z138" s="6"/>
+      <c r="AA138" s="6"/>
+      <c r="AB138" s="6"/>
+      <c r="AC138" s="6"/>
+      <c r="AD138" s="6"/>
+      <c r="AE138" s="6"/>
+      <c r="AF138" s="6"/>
       <c r="AG138" t="s">
         <v>114</v>
       </c>
@@ -4520,6 +7046,27 @@
       <c r="E139">
         <v>130</v>
       </c>
+      <c r="L139" s="6"/>
+      <c r="M139" s="6"/>
+      <c r="N139" s="6"/>
+      <c r="O139" s="6"/>
+      <c r="P139" s="6"/>
+      <c r="Q139" s="6"/>
+      <c r="R139" s="6"/>
+      <c r="S139" s="6"/>
+      <c r="T139" s="6"/>
+      <c r="U139" s="6"/>
+      <c r="V139" s="6"/>
+      <c r="W139" s="6"/>
+      <c r="X139" s="6"/>
+      <c r="Y139" s="6"/>
+      <c r="Z139" s="6"/>
+      <c r="AA139" s="6"/>
+      <c r="AB139" s="6"/>
+      <c r="AC139" s="6"/>
+      <c r="AD139" s="6"/>
+      <c r="AE139" s="6"/>
+      <c r="AF139" s="6"/>
       <c r="AG139" t="s">
         <v>114</v>
       </c>
@@ -4540,6 +7087,27 @@
       <c r="I140">
         <v>220</v>
       </c>
+      <c r="L140" s="6"/>
+      <c r="M140" s="6"/>
+      <c r="N140" s="6"/>
+      <c r="O140" s="6"/>
+      <c r="P140" s="6"/>
+      <c r="Q140" s="6"/>
+      <c r="R140" s="6"/>
+      <c r="S140" s="6"/>
+      <c r="T140" s="6"/>
+      <c r="U140" s="6"/>
+      <c r="V140" s="6"/>
+      <c r="W140" s="6"/>
+      <c r="X140" s="6"/>
+      <c r="Y140" s="6"/>
+      <c r="Z140" s="6"/>
+      <c r="AA140" s="6"/>
+      <c r="AB140" s="6"/>
+      <c r="AC140" s="6"/>
+      <c r="AD140" s="6"/>
+      <c r="AE140" s="6"/>
+      <c r="AF140" s="6"/>
     </row>
     <row r="141" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B141" t="s">
@@ -4554,6 +7122,27 @@
       <c r="E141">
         <v>415.5</v>
       </c>
+      <c r="L141" s="6"/>
+      <c r="M141" s="6"/>
+      <c r="N141" s="6"/>
+      <c r="O141" s="6"/>
+      <c r="P141" s="6"/>
+      <c r="Q141" s="6"/>
+      <c r="R141" s="6"/>
+      <c r="S141" s="6"/>
+      <c r="T141" s="6"/>
+      <c r="U141" s="6"/>
+      <c r="V141" s="6"/>
+      <c r="W141" s="6"/>
+      <c r="X141" s="6"/>
+      <c r="Y141" s="6"/>
+      <c r="Z141" s="6"/>
+      <c r="AA141" s="6"/>
+      <c r="AB141" s="6"/>
+      <c r="AC141" s="6"/>
+      <c r="AD141" s="6"/>
+      <c r="AE141" s="6"/>
+      <c r="AF141" s="6"/>
     </row>
     <row r="142" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B142" t="s">
@@ -4568,6 +7157,27 @@
       <c r="E142">
         <v>28.85</v>
       </c>
+      <c r="L142" s="6"/>
+      <c r="M142" s="6"/>
+      <c r="N142" s="6"/>
+      <c r="O142" s="6"/>
+      <c r="P142" s="6"/>
+      <c r="Q142" s="6"/>
+      <c r="R142" s="6"/>
+      <c r="S142" s="6"/>
+      <c r="T142" s="6"/>
+      <c r="U142" s="6"/>
+      <c r="V142" s="6"/>
+      <c r="W142" s="6"/>
+      <c r="X142" s="6"/>
+      <c r="Y142" s="6"/>
+      <c r="Z142" s="6"/>
+      <c r="AA142" s="6"/>
+      <c r="AB142" s="6"/>
+      <c r="AC142" s="6"/>
+      <c r="AD142" s="6"/>
+      <c r="AE142" s="6"/>
+      <c r="AF142" s="6"/>
     </row>
     <row r="143" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B143" t="s">
@@ -4582,6 +7192,27 @@
       <c r="E143">
         <v>138.24</v>
       </c>
+      <c r="L143" s="6"/>
+      <c r="M143" s="6"/>
+      <c r="N143" s="6"/>
+      <c r="O143" s="6"/>
+      <c r="P143" s="6"/>
+      <c r="Q143" s="6"/>
+      <c r="R143" s="6"/>
+      <c r="S143" s="6"/>
+      <c r="T143" s="6"/>
+      <c r="U143" s="6"/>
+      <c r="V143" s="6"/>
+      <c r="W143" s="6"/>
+      <c r="X143" s="6"/>
+      <c r="Y143" s="6"/>
+      <c r="Z143" s="6"/>
+      <c r="AA143" s="6"/>
+      <c r="AB143" s="6"/>
+      <c r="AC143" s="6"/>
+      <c r="AD143" s="6"/>
+      <c r="AE143" s="6"/>
+      <c r="AF143" s="6"/>
     </row>
     <row r="144" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B144" t="s">
@@ -4602,6 +7233,27 @@
       <c r="I144">
         <v>94</v>
       </c>
+      <c r="L144" s="6"/>
+      <c r="M144" s="6"/>
+      <c r="N144" s="6"/>
+      <c r="O144" s="6"/>
+      <c r="P144" s="6"/>
+      <c r="Q144" s="6"/>
+      <c r="R144" s="6"/>
+      <c r="S144" s="6"/>
+      <c r="T144" s="6"/>
+      <c r="U144" s="6"/>
+      <c r="V144" s="6"/>
+      <c r="W144" s="6"/>
+      <c r="X144" s="6"/>
+      <c r="Y144" s="6"/>
+      <c r="Z144" s="6"/>
+      <c r="AA144" s="6"/>
+      <c r="AB144" s="6"/>
+      <c r="AC144" s="6"/>
+      <c r="AD144" s="6"/>
+      <c r="AE144" s="6"/>
+      <c r="AF144" s="6"/>
       <c r="AG144" t="s">
         <v>115</v>
       </c>
@@ -4622,9 +7274,29 @@
       <c r="F145" s="5">
         <v>9</v>
       </c>
-      <c r="U145">
+      <c r="L145" s="6"/>
+      <c r="M145" s="6"/>
+      <c r="N145" s="6"/>
+      <c r="O145" s="6"/>
+      <c r="P145" s="6"/>
+      <c r="Q145" s="6"/>
+      <c r="R145" s="6"/>
+      <c r="S145" s="6"/>
+      <c r="T145" s="6"/>
+      <c r="U145" s="6">
         <v>9</v>
       </c>
+      <c r="V145" s="6"/>
+      <c r="W145" s="6"/>
+      <c r="X145" s="6"/>
+      <c r="Y145" s="6"/>
+      <c r="Z145" s="6"/>
+      <c r="AA145" s="6"/>
+      <c r="AB145" s="6"/>
+      <c r="AC145" s="6"/>
+      <c r="AD145" s="6"/>
+      <c r="AE145" s="6"/>
+      <c r="AF145" s="6"/>
       <c r="AG145" t="s">
         <v>115</v>
       </c>
@@ -4639,6 +7311,27 @@
       <c r="D146" t="s">
         <v>6</v>
       </c>
+      <c r="L146" s="6"/>
+      <c r="M146" s="6"/>
+      <c r="N146" s="6"/>
+      <c r="O146" s="6"/>
+      <c r="P146" s="6"/>
+      <c r="Q146" s="6"/>
+      <c r="R146" s="6"/>
+      <c r="S146" s="6"/>
+      <c r="T146" s="6"/>
+      <c r="U146" s="6"/>
+      <c r="V146" s="6"/>
+      <c r="W146" s="6"/>
+      <c r="X146" s="6"/>
+      <c r="Y146" s="6"/>
+      <c r="Z146" s="6"/>
+      <c r="AA146" s="6"/>
+      <c r="AB146" s="6"/>
+      <c r="AC146" s="6"/>
+      <c r="AD146" s="6"/>
+      <c r="AE146" s="6"/>
+      <c r="AF146" s="6"/>
     </row>
     <row r="147" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B147" t="s">
@@ -4653,6 +7346,27 @@
       <c r="E147">
         <v>109.8</v>
       </c>
+      <c r="L147" s="6"/>
+      <c r="M147" s="6"/>
+      <c r="N147" s="6"/>
+      <c r="O147" s="6"/>
+      <c r="P147" s="6"/>
+      <c r="Q147" s="6"/>
+      <c r="R147" s="6"/>
+      <c r="S147" s="6"/>
+      <c r="T147" s="6"/>
+      <c r="U147" s="6"/>
+      <c r="V147" s="6"/>
+      <c r="W147" s="6"/>
+      <c r="X147" s="6"/>
+      <c r="Y147" s="6"/>
+      <c r="Z147" s="6"/>
+      <c r="AA147" s="6"/>
+      <c r="AB147" s="6"/>
+      <c r="AC147" s="6"/>
+      <c r="AD147" s="6"/>
+      <c r="AE147" s="6"/>
+      <c r="AF147" s="6"/>
     </row>
     <row r="148" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B148" t="s">
@@ -4664,6 +7378,27 @@
       <c r="D148" t="s">
         <v>6</v>
       </c>
+      <c r="L148" s="6"/>
+      <c r="M148" s="6"/>
+      <c r="N148" s="6"/>
+      <c r="O148" s="6"/>
+      <c r="P148" s="6"/>
+      <c r="Q148" s="6"/>
+      <c r="R148" s="6"/>
+      <c r="S148" s="6"/>
+      <c r="T148" s="6"/>
+      <c r="U148" s="6"/>
+      <c r="V148" s="6"/>
+      <c r="W148" s="6"/>
+      <c r="X148" s="6"/>
+      <c r="Y148" s="6"/>
+      <c r="Z148" s="6"/>
+      <c r="AA148" s="6"/>
+      <c r="AB148" s="6"/>
+      <c r="AC148" s="6"/>
+      <c r="AD148" s="6"/>
+      <c r="AE148" s="6"/>
+      <c r="AF148" s="6"/>
     </row>
     <row r="149" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B149" t="s">
@@ -4678,6 +7413,27 @@
       <c r="E149">
         <v>220.48</v>
       </c>
+      <c r="L149" s="6"/>
+      <c r="M149" s="6"/>
+      <c r="N149" s="6"/>
+      <c r="O149" s="6"/>
+      <c r="P149" s="6"/>
+      <c r="Q149" s="6"/>
+      <c r="R149" s="6"/>
+      <c r="S149" s="6"/>
+      <c r="T149" s="6"/>
+      <c r="U149" s="6"/>
+      <c r="V149" s="6"/>
+      <c r="W149" s="6"/>
+      <c r="X149" s="6"/>
+      <c r="Y149" s="6"/>
+      <c r="Z149" s="6"/>
+      <c r="AA149" s="6"/>
+      <c r="AB149" s="6"/>
+      <c r="AC149" s="6"/>
+      <c r="AD149" s="6"/>
+      <c r="AE149" s="6"/>
+      <c r="AF149" s="6"/>
     </row>
     <row r="150" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B150" t="s">
@@ -4692,6 +7448,27 @@
       <c r="I150">
         <v>32</v>
       </c>
+      <c r="L150" s="6"/>
+      <c r="M150" s="6"/>
+      <c r="N150" s="6"/>
+      <c r="O150" s="6"/>
+      <c r="P150" s="6"/>
+      <c r="Q150" s="6"/>
+      <c r="R150" s="6"/>
+      <c r="S150" s="6"/>
+      <c r="T150" s="6"/>
+      <c r="U150" s="6"/>
+      <c r="V150" s="6"/>
+      <c r="W150" s="6"/>
+      <c r="X150" s="6"/>
+      <c r="Y150" s="6"/>
+      <c r="Z150" s="6"/>
+      <c r="AA150" s="6"/>
+      <c r="AB150" s="6"/>
+      <c r="AC150" s="6"/>
+      <c r="AD150" s="6"/>
+      <c r="AE150" s="6"/>
+      <c r="AF150" s="6"/>
     </row>
     <row r="151" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B151" t="s">
@@ -4706,6 +7483,27 @@
       <c r="E151">
         <v>59.5</v>
       </c>
+      <c r="L151" s="6"/>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6"/>
+      <c r="O151" s="6"/>
+      <c r="P151" s="6"/>
+      <c r="Q151" s="6"/>
+      <c r="R151" s="6"/>
+      <c r="S151" s="6"/>
+      <c r="T151" s="6"/>
+      <c r="U151" s="6"/>
+      <c r="V151" s="6"/>
+      <c r="W151" s="6"/>
+      <c r="X151" s="6"/>
+      <c r="Y151" s="6"/>
+      <c r="Z151" s="6"/>
+      <c r="AA151" s="6"/>
+      <c r="AB151" s="6"/>
+      <c r="AC151" s="6"/>
+      <c r="AD151" s="6"/>
+      <c r="AE151" s="6"/>
+      <c r="AF151" s="6"/>
     </row>
     <row r="152" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B152" t="s">
@@ -4720,6 +7518,27 @@
       <c r="I152">
         <v>1180</v>
       </c>
+      <c r="L152" s="6"/>
+      <c r="M152" s="6"/>
+      <c r="N152" s="6"/>
+      <c r="O152" s="6"/>
+      <c r="P152" s="6"/>
+      <c r="Q152" s="6"/>
+      <c r="R152" s="6"/>
+      <c r="S152" s="6"/>
+      <c r="T152" s="6"/>
+      <c r="U152" s="6"/>
+      <c r="V152" s="6"/>
+      <c r="W152" s="6"/>
+      <c r="X152" s="6"/>
+      <c r="Y152" s="6"/>
+      <c r="Z152" s="6"/>
+      <c r="AA152" s="6"/>
+      <c r="AB152" s="6"/>
+      <c r="AC152" s="6"/>
+      <c r="AD152" s="6"/>
+      <c r="AE152" s="6"/>
+      <c r="AF152" s="6"/>
     </row>
     <row r="153" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B153" t="s">
@@ -4734,6 +7553,27 @@
       <c r="E153">
         <v>382.5</v>
       </c>
+      <c r="L153" s="6"/>
+      <c r="M153" s="6"/>
+      <c r="N153" s="6"/>
+      <c r="O153" s="6"/>
+      <c r="P153" s="6"/>
+      <c r="Q153" s="6"/>
+      <c r="R153" s="6"/>
+      <c r="S153" s="6"/>
+      <c r="T153" s="6"/>
+      <c r="U153" s="6"/>
+      <c r="V153" s="6"/>
+      <c r="W153" s="6"/>
+      <c r="X153" s="6"/>
+      <c r="Y153" s="6"/>
+      <c r="Z153" s="6"/>
+      <c r="AA153" s="6"/>
+      <c r="AB153" s="6"/>
+      <c r="AC153" s="6"/>
+      <c r="AD153" s="6"/>
+      <c r="AE153" s="6"/>
+      <c r="AF153" s="6"/>
     </row>
     <row r="154" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B154" t="s">
@@ -4748,6 +7588,27 @@
       <c r="E154">
         <v>418.5</v>
       </c>
+      <c r="L154" s="6"/>
+      <c r="M154" s="6"/>
+      <c r="N154" s="6"/>
+      <c r="O154" s="6"/>
+      <c r="P154" s="6"/>
+      <c r="Q154" s="6"/>
+      <c r="R154" s="6"/>
+      <c r="S154" s="6"/>
+      <c r="T154" s="6"/>
+      <c r="U154" s="6"/>
+      <c r="V154" s="6"/>
+      <c r="W154" s="6"/>
+      <c r="X154" s="6"/>
+      <c r="Y154" s="6"/>
+      <c r="Z154" s="6"/>
+      <c r="AA154" s="6"/>
+      <c r="AB154" s="6"/>
+      <c r="AC154" s="6"/>
+      <c r="AD154" s="6"/>
+      <c r="AE154" s="6"/>
+      <c r="AF154" s="6"/>
     </row>
     <row r="155" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B155" t="s">
@@ -4762,6 +7623,27 @@
       <c r="E155">
         <v>441.5</v>
       </c>
+      <c r="L155" s="6"/>
+      <c r="M155" s="6"/>
+      <c r="N155" s="6"/>
+      <c r="O155" s="6"/>
+      <c r="P155" s="6"/>
+      <c r="Q155" s="6"/>
+      <c r="R155" s="6"/>
+      <c r="S155" s="6"/>
+      <c r="T155" s="6"/>
+      <c r="U155" s="6"/>
+      <c r="V155" s="6"/>
+      <c r="W155" s="6"/>
+      <c r="X155" s="6"/>
+      <c r="Y155" s="6"/>
+      <c r="Z155" s="6"/>
+      <c r="AA155" s="6"/>
+      <c r="AB155" s="6"/>
+      <c r="AC155" s="6"/>
+      <c r="AD155" s="6"/>
+      <c r="AE155" s="6"/>
+      <c r="AF155" s="6"/>
     </row>
     <row r="156" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="s">
@@ -4791,17 +7673,35 @@
       <c r="J156">
         <v>1901</v>
       </c>
-      <c r="U156">
+      <c r="L156" s="6"/>
+      <c r="M156" s="6"/>
+      <c r="N156" s="6"/>
+      <c r="O156" s="6"/>
+      <c r="P156" s="6"/>
+      <c r="Q156" s="6"/>
+      <c r="R156" s="6"/>
+      <c r="S156" s="6"/>
+      <c r="T156" s="6"/>
+      <c r="U156" s="6">
         <f>528.5-68.36</f>
         <v>460.14</v>
       </c>
-      <c r="V156">
+      <c r="V156" s="6">
         <f>52.4-0.15</f>
         <v>52.25</v>
       </c>
-      <c r="X156">
+      <c r="W156" s="6"/>
+      <c r="X156" s="6">
         <v>70.239999999999995</v>
       </c>
+      <c r="Y156" s="6"/>
+      <c r="Z156" s="6"/>
+      <c r="AA156" s="6"/>
+      <c r="AB156" s="6"/>
+      <c r="AC156" s="6"/>
+      <c r="AD156" s="6"/>
+      <c r="AE156" s="6"/>
+      <c r="AF156" s="6"/>
       <c r="AG156" t="s">
         <v>115</v>
       </c>
@@ -4822,15 +7722,33 @@
       <c r="F157" s="5">
         <v>91.31</v>
       </c>
-      <c r="U157">
+      <c r="L157" s="6"/>
+      <c r="M157" s="6"/>
+      <c r="N157" s="6"/>
+      <c r="O157" s="6"/>
+      <c r="P157" s="6"/>
+      <c r="Q157" s="6"/>
+      <c r="R157" s="6"/>
+      <c r="S157" s="6"/>
+      <c r="T157" s="6"/>
+      <c r="U157" s="6">
         <v>42.7</v>
       </c>
-      <c r="W157">
+      <c r="V157" s="6"/>
+      <c r="W157" s="6">
         <v>39.799999999999997</v>
       </c>
-      <c r="X157">
+      <c r="X157" s="6">
         <v>8.81</v>
       </c>
+      <c r="Y157" s="6"/>
+      <c r="Z157" s="6"/>
+      <c r="AA157" s="6"/>
+      <c r="AB157" s="6"/>
+      <c r="AC157" s="6"/>
+      <c r="AD157" s="6"/>
+      <c r="AE157" s="6"/>
+      <c r="AF157" s="6"/>
       <c r="AG157" t="s">
         <v>115</v>
       </c>
@@ -4863,13 +7781,32 @@
       <c r="J158">
         <v>822</v>
       </c>
-      <c r="U158">
+      <c r="L158" s="6"/>
+      <c r="M158" s="6"/>
+      <c r="N158" s="6"/>
+      <c r="O158" s="6"/>
+      <c r="P158" s="6"/>
+      <c r="Q158" s="6"/>
+      <c r="R158" s="6"/>
+      <c r="S158" s="6"/>
+      <c r="T158" s="6"/>
+      <c r="U158" s="6">
         <f>67.2+51</f>
         <v>118.2</v>
       </c>
-      <c r="V158">
+      <c r="V158" s="6">
         <v>256.5</v>
       </c>
+      <c r="W158" s="6"/>
+      <c r="X158" s="6"/>
+      <c r="Y158" s="6"/>
+      <c r="Z158" s="6"/>
+      <c r="AA158" s="6"/>
+      <c r="AB158" s="6"/>
+      <c r="AC158" s="6"/>
+      <c r="AD158" s="6"/>
+      <c r="AE158" s="6"/>
+      <c r="AF158" s="6"/>
       <c r="AG158" t="s">
         <v>115</v>
       </c>
@@ -4890,9 +7827,29 @@
       <c r="F159" s="5">
         <v>65.599999999999994</v>
       </c>
-      <c r="W159">
+      <c r="L159" s="6"/>
+      <c r="M159" s="6"/>
+      <c r="N159" s="6"/>
+      <c r="O159" s="6"/>
+      <c r="P159" s="6"/>
+      <c r="Q159" s="6"/>
+      <c r="R159" s="6"/>
+      <c r="S159" s="6"/>
+      <c r="T159" s="6"/>
+      <c r="U159" s="6"/>
+      <c r="V159" s="6"/>
+      <c r="W159" s="6">
         <v>65.599999999999994</v>
       </c>
+      <c r="X159" s="6"/>
+      <c r="Y159" s="6"/>
+      <c r="Z159" s="6"/>
+      <c r="AA159" s="6"/>
+      <c r="AB159" s="6"/>
+      <c r="AC159" s="6"/>
+      <c r="AD159" s="6"/>
+      <c r="AE159" s="6"/>
+      <c r="AF159" s="6"/>
       <c r="AG159" t="s">
         <v>115</v>
       </c>
@@ -4919,9 +7876,29 @@
       <c r="I160">
         <v>597</v>
       </c>
-      <c r="V160">
+      <c r="L160" s="6"/>
+      <c r="M160" s="6"/>
+      <c r="N160" s="6"/>
+      <c r="O160" s="6"/>
+      <c r="P160" s="6"/>
+      <c r="Q160" s="6"/>
+      <c r="R160" s="6"/>
+      <c r="S160" s="6"/>
+      <c r="T160" s="6"/>
+      <c r="U160" s="6"/>
+      <c r="V160" s="6">
         <v>207.4</v>
       </c>
+      <c r="W160" s="6"/>
+      <c r="X160" s="6"/>
+      <c r="Y160" s="6"/>
+      <c r="Z160" s="6"/>
+      <c r="AA160" s="6"/>
+      <c r="AB160" s="6"/>
+      <c r="AC160" s="6"/>
+      <c r="AD160" s="6"/>
+      <c r="AE160" s="6"/>
+      <c r="AF160" s="6"/>
       <c r="AG160" t="s">
         <v>115</v>
       </c>
@@ -4942,9 +7919,29 @@
       <c r="F161" s="5">
         <v>2</v>
       </c>
-      <c r="W161">
+      <c r="L161" s="6"/>
+      <c r="M161" s="6"/>
+      <c r="N161" s="6"/>
+      <c r="O161" s="6"/>
+      <c r="P161" s="6"/>
+      <c r="Q161" s="6"/>
+      <c r="R161" s="6"/>
+      <c r="S161" s="6"/>
+      <c r="T161" s="6"/>
+      <c r="U161" s="6"/>
+      <c r="V161" s="6"/>
+      <c r="W161" s="6">
         <v>2</v>
       </c>
+      <c r="X161" s="6"/>
+      <c r="Y161" s="6"/>
+      <c r="Z161" s="6"/>
+      <c r="AA161" s="6"/>
+      <c r="AB161" s="6"/>
+      <c r="AC161" s="6"/>
+      <c r="AD161" s="6"/>
+      <c r="AE161" s="6"/>
+      <c r="AF161" s="6"/>
       <c r="AG161" t="s">
         <v>115</v>
       </c>
@@ -4965,6 +7962,27 @@
       <c r="I162">
         <v>785</v>
       </c>
+      <c r="L162" s="6"/>
+      <c r="M162" s="6"/>
+      <c r="N162" s="6"/>
+      <c r="O162" s="6"/>
+      <c r="P162" s="6"/>
+      <c r="Q162" s="6"/>
+      <c r="R162" s="6"/>
+      <c r="S162" s="6"/>
+      <c r="T162" s="6"/>
+      <c r="U162" s="6"/>
+      <c r="V162" s="6"/>
+      <c r="W162" s="6"/>
+      <c r="X162" s="6"/>
+      <c r="Y162" s="6"/>
+      <c r="Z162" s="6"/>
+      <c r="AA162" s="6"/>
+      <c r="AB162" s="6"/>
+      <c r="AC162" s="6"/>
+      <c r="AD162" s="6"/>
+      <c r="AE162" s="6"/>
+      <c r="AF162" s="6"/>
     </row>
     <row r="163" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B163" t="s">
@@ -4979,6 +7997,27 @@
       <c r="E163">
         <v>894.97</v>
       </c>
+      <c r="L163" s="6"/>
+      <c r="M163" s="6"/>
+      <c r="N163" s="6"/>
+      <c r="O163" s="6"/>
+      <c r="P163" s="6"/>
+      <c r="Q163" s="6"/>
+      <c r="R163" s="6"/>
+      <c r="S163" s="6"/>
+      <c r="T163" s="6"/>
+      <c r="U163" s="6"/>
+      <c r="V163" s="6"/>
+      <c r="W163" s="6"/>
+      <c r="X163" s="6"/>
+      <c r="Y163" s="6"/>
+      <c r="Z163" s="6"/>
+      <c r="AA163" s="6"/>
+      <c r="AB163" s="6"/>
+      <c r="AC163" s="6"/>
+      <c r="AD163" s="6"/>
+      <c r="AE163" s="6"/>
+      <c r="AF163" s="6"/>
     </row>
     <row r="164" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B164" t="s">
@@ -4990,6 +8029,27 @@
       <c r="D164" t="s">
         <v>6</v>
       </c>
+      <c r="L164" s="6"/>
+      <c r="M164" s="6"/>
+      <c r="N164" s="6"/>
+      <c r="O164" s="6"/>
+      <c r="P164" s="6"/>
+      <c r="Q164" s="6"/>
+      <c r="R164" s="6"/>
+      <c r="S164" s="6"/>
+      <c r="T164" s="6"/>
+      <c r="U164" s="6"/>
+      <c r="V164" s="6"/>
+      <c r="W164" s="6"/>
+      <c r="X164" s="6"/>
+      <c r="Y164" s="6"/>
+      <c r="Z164" s="6"/>
+      <c r="AA164" s="6"/>
+      <c r="AB164" s="6"/>
+      <c r="AC164" s="6"/>
+      <c r="AD164" s="6"/>
+      <c r="AE164" s="6"/>
+      <c r="AF164" s="6"/>
     </row>
     <row r="165" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B165" t="s">
@@ -5004,6 +8064,27 @@
       <c r="E165">
         <v>747</v>
       </c>
+      <c r="L165" s="6"/>
+      <c r="M165" s="6"/>
+      <c r="N165" s="6"/>
+      <c r="O165" s="6"/>
+      <c r="P165" s="6"/>
+      <c r="Q165" s="6"/>
+      <c r="R165" s="6"/>
+      <c r="S165" s="6"/>
+      <c r="T165" s="6"/>
+      <c r="U165" s="6"/>
+      <c r="V165" s="6"/>
+      <c r="W165" s="6"/>
+      <c r="X165" s="6"/>
+      <c r="Y165" s="6"/>
+      <c r="Z165" s="6"/>
+      <c r="AA165" s="6"/>
+      <c r="AB165" s="6"/>
+      <c r="AC165" s="6"/>
+      <c r="AD165" s="6"/>
+      <c r="AE165" s="6"/>
+      <c r="AF165" s="6"/>
     </row>
     <row r="166" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B166" s="5" t="s">
@@ -5024,9 +8105,29 @@
       <c r="I166">
         <v>288</v>
       </c>
-      <c r="X166">
+      <c r="L166" s="6"/>
+      <c r="M166" s="6"/>
+      <c r="N166" s="6"/>
+      <c r="O166" s="6"/>
+      <c r="P166" s="6"/>
+      <c r="Q166" s="6"/>
+      <c r="R166" s="6"/>
+      <c r="S166" s="6"/>
+      <c r="T166" s="6"/>
+      <c r="U166" s="6"/>
+      <c r="V166" s="6"/>
+      <c r="W166" s="6"/>
+      <c r="X166" s="6">
         <v>76.400000000000006</v>
       </c>
+      <c r="Y166" s="6"/>
+      <c r="Z166" s="6"/>
+      <c r="AA166" s="6"/>
+      <c r="AB166" s="6"/>
+      <c r="AC166" s="6"/>
+      <c r="AD166" s="6"/>
+      <c r="AE166" s="6"/>
+      <c r="AF166" s="6"/>
       <c r="AG166" t="s">
         <v>115</v>
       </c>
@@ -5044,6 +8145,27 @@
       <c r="E167">
         <v>59.6</v>
       </c>
+      <c r="L167" s="6"/>
+      <c r="M167" s="6"/>
+      <c r="N167" s="6"/>
+      <c r="O167" s="6"/>
+      <c r="P167" s="6"/>
+      <c r="Q167" s="6"/>
+      <c r="R167" s="6"/>
+      <c r="S167" s="6"/>
+      <c r="T167" s="6"/>
+      <c r="U167" s="6"/>
+      <c r="V167" s="6"/>
+      <c r="W167" s="6"/>
+      <c r="X167" s="6"/>
+      <c r="Y167" s="6"/>
+      <c r="Z167" s="6"/>
+      <c r="AA167" s="6"/>
+      <c r="AB167" s="6"/>
+      <c r="AC167" s="6"/>
+      <c r="AD167" s="6"/>
+      <c r="AE167" s="6"/>
+      <c r="AF167" s="6"/>
       <c r="AG167" t="s">
         <v>115</v>
       </c>
@@ -5067,13 +8189,32 @@
       <c r="I168">
         <v>415</v>
       </c>
-      <c r="W168">
+      <c r="L168" s="6"/>
+      <c r="M168" s="6"/>
+      <c r="N168" s="6"/>
+      <c r="O168" s="6"/>
+      <c r="P168" s="6"/>
+      <c r="Q168" s="6"/>
+      <c r="R168" s="6"/>
+      <c r="S168" s="6"/>
+      <c r="T168" s="6"/>
+      <c r="U168" s="6"/>
+      <c r="V168" s="6"/>
+      <c r="W168" s="6">
         <v>81.8</v>
       </c>
-      <c r="X168">
+      <c r="X168" s="6">
         <f>42+158.17+61.95+0.21</f>
         <v>262.33</v>
       </c>
+      <c r="Y168" s="6"/>
+      <c r="Z168" s="6"/>
+      <c r="AA168" s="6"/>
+      <c r="AB168" s="6"/>
+      <c r="AC168" s="6"/>
+      <c r="AD168" s="6"/>
+      <c r="AE168" s="6"/>
+      <c r="AF168" s="6"/>
       <c r="AG168" t="s">
         <v>115</v>
       </c>
@@ -5094,10 +8235,30 @@
       <c r="F169" s="5">
         <v>40.9</v>
       </c>
-      <c r="X169">
+      <c r="L169" s="6"/>
+      <c r="M169" s="6"/>
+      <c r="N169" s="6"/>
+      <c r="O169" s="6"/>
+      <c r="P169" s="6"/>
+      <c r="Q169" s="6"/>
+      <c r="R169" s="6"/>
+      <c r="S169" s="6"/>
+      <c r="T169" s="6"/>
+      <c r="U169" s="6"/>
+      <c r="V169" s="6"/>
+      <c r="W169" s="6"/>
+      <c r="X169" s="6">
         <f>11.35+17.44+12.11</f>
         <v>40.9</v>
       </c>
+      <c r="Y169" s="6"/>
+      <c r="Z169" s="6"/>
+      <c r="AA169" s="6"/>
+      <c r="AB169" s="6"/>
+      <c r="AC169" s="6"/>
+      <c r="AD169" s="6"/>
+      <c r="AE169" s="6"/>
+      <c r="AF169" s="6"/>
       <c r="AG169" t="s">
         <v>115</v>
       </c>
@@ -5118,6 +8279,27 @@
       <c r="I170">
         <v>141</v>
       </c>
+      <c r="L170" s="6"/>
+      <c r="M170" s="6"/>
+      <c r="N170" s="6"/>
+      <c r="O170" s="6"/>
+      <c r="P170" s="6"/>
+      <c r="Q170" s="6"/>
+      <c r="R170" s="6"/>
+      <c r="S170" s="6"/>
+      <c r="T170" s="6"/>
+      <c r="U170" s="6"/>
+      <c r="V170" s="6"/>
+      <c r="W170" s="6"/>
+      <c r="X170" s="6"/>
+      <c r="Y170" s="6"/>
+      <c r="Z170" s="6"/>
+      <c r="AA170" s="6"/>
+      <c r="AB170" s="6"/>
+      <c r="AC170" s="6"/>
+      <c r="AD170" s="6"/>
+      <c r="AE170" s="6"/>
+      <c r="AF170" s="6"/>
     </row>
     <row r="171" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B171" t="s">
@@ -5132,6 +8314,27 @@
       <c r="E171">
         <v>28</v>
       </c>
+      <c r="L171" s="6"/>
+      <c r="M171" s="6"/>
+      <c r="N171" s="6"/>
+      <c r="O171" s="6"/>
+      <c r="P171" s="6"/>
+      <c r="Q171" s="6"/>
+      <c r="R171" s="6"/>
+      <c r="S171" s="6"/>
+      <c r="T171" s="6"/>
+      <c r="U171" s="6"/>
+      <c r="V171" s="6"/>
+      <c r="W171" s="6"/>
+      <c r="X171" s="6"/>
+      <c r="Y171" s="6"/>
+      <c r="Z171" s="6"/>
+      <c r="AA171" s="6"/>
+      <c r="AB171" s="6"/>
+      <c r="AC171" s="6"/>
+      <c r="AD171" s="6"/>
+      <c r="AE171" s="6"/>
+      <c r="AF171" s="6"/>
     </row>
     <row r="172" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B172" t="s">
@@ -5143,6 +8346,27 @@
       <c r="D172" t="s">
         <v>6</v>
       </c>
+      <c r="L172" s="6"/>
+      <c r="M172" s="6"/>
+      <c r="N172" s="6"/>
+      <c r="O172" s="6"/>
+      <c r="P172" s="6"/>
+      <c r="Q172" s="6"/>
+      <c r="R172" s="6"/>
+      <c r="S172" s="6"/>
+      <c r="T172" s="6"/>
+      <c r="U172" s="6"/>
+      <c r="V172" s="6"/>
+      <c r="W172" s="6"/>
+      <c r="X172" s="6"/>
+      <c r="Y172" s="6"/>
+      <c r="Z172" s="6"/>
+      <c r="AA172" s="6"/>
+      <c r="AB172" s="6"/>
+      <c r="AC172" s="6"/>
+      <c r="AD172" s="6"/>
+      <c r="AE172" s="6"/>
+      <c r="AF172" s="6"/>
     </row>
     <row r="173" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B173" t="s">
@@ -5157,6 +8381,27 @@
       <c r="E173">
         <v>125</v>
       </c>
+      <c r="L173" s="6"/>
+      <c r="M173" s="6"/>
+      <c r="N173" s="6"/>
+      <c r="O173" s="6"/>
+      <c r="P173" s="6"/>
+      <c r="Q173" s="6"/>
+      <c r="R173" s="6"/>
+      <c r="S173" s="6"/>
+      <c r="T173" s="6"/>
+      <c r="U173" s="6"/>
+      <c r="V173" s="6"/>
+      <c r="W173" s="6"/>
+      <c r="X173" s="6"/>
+      <c r="Y173" s="6"/>
+      <c r="Z173" s="6"/>
+      <c r="AA173" s="6"/>
+      <c r="AB173" s="6"/>
+      <c r="AC173" s="6"/>
+      <c r="AD173" s="6"/>
+      <c r="AE173" s="6"/>
+      <c r="AF173" s="6"/>
     </row>
     <row r="174" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B174" t="s">
@@ -5174,6 +8419,27 @@
       <c r="I174">
         <v>134</v>
       </c>
+      <c r="L174" s="6"/>
+      <c r="M174" s="6"/>
+      <c r="N174" s="6"/>
+      <c r="O174" s="6"/>
+      <c r="P174" s="6"/>
+      <c r="Q174" s="6"/>
+      <c r="R174" s="6"/>
+      <c r="S174" s="6"/>
+      <c r="T174" s="6"/>
+      <c r="U174" s="6"/>
+      <c r="V174" s="6"/>
+      <c r="W174" s="6"/>
+      <c r="X174" s="6"/>
+      <c r="Y174" s="6"/>
+      <c r="Z174" s="6"/>
+      <c r="AA174" s="6"/>
+      <c r="AB174" s="6"/>
+      <c r="AC174" s="6"/>
+      <c r="AD174" s="6"/>
+      <c r="AE174" s="6"/>
+      <c r="AF174" s="6"/>
     </row>
     <row r="175" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B175" t="s">
@@ -5188,6 +8454,27 @@
       <c r="E175">
         <v>15.2</v>
       </c>
+      <c r="L175" s="6"/>
+      <c r="M175" s="6"/>
+      <c r="N175" s="6"/>
+      <c r="O175" s="6"/>
+      <c r="P175" s="6"/>
+      <c r="Q175" s="6"/>
+      <c r="R175" s="6"/>
+      <c r="S175" s="6"/>
+      <c r="T175" s="6"/>
+      <c r="U175" s="6"/>
+      <c r="V175" s="6"/>
+      <c r="W175" s="6"/>
+      <c r="X175" s="6"/>
+      <c r="Y175" s="6"/>
+      <c r="Z175" s="6"/>
+      <c r="AA175" s="6"/>
+      <c r="AB175" s="6"/>
+      <c r="AC175" s="6"/>
+      <c r="AD175" s="6"/>
+      <c r="AE175" s="6"/>
+      <c r="AF175" s="6"/>
     </row>
     <row r="176" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B176" t="s">
@@ -5199,6 +8486,27 @@
       <c r="D176" t="s">
         <v>6</v>
       </c>
+      <c r="L176" s="6"/>
+      <c r="M176" s="6"/>
+      <c r="N176" s="6"/>
+      <c r="O176" s="6"/>
+      <c r="P176" s="6"/>
+      <c r="Q176" s="6"/>
+      <c r="R176" s="6"/>
+      <c r="S176" s="6"/>
+      <c r="T176" s="6"/>
+      <c r="U176" s="6"/>
+      <c r="V176" s="6"/>
+      <c r="W176" s="6"/>
+      <c r="X176" s="6"/>
+      <c r="Y176" s="6"/>
+      <c r="Z176" s="6"/>
+      <c r="AA176" s="6"/>
+      <c r="AB176" s="6"/>
+      <c r="AC176" s="6"/>
+      <c r="AD176" s="6"/>
+      <c r="AE176" s="6"/>
+      <c r="AF176" s="6"/>
     </row>
     <row r="177" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B177" t="s">
@@ -5213,6 +8521,27 @@
       <c r="E177">
         <v>1021.03</v>
       </c>
+      <c r="L177" s="6"/>
+      <c r="M177" s="6"/>
+      <c r="N177" s="6"/>
+      <c r="O177" s="6"/>
+      <c r="P177" s="6"/>
+      <c r="Q177" s="6"/>
+      <c r="R177" s="6"/>
+      <c r="S177" s="6"/>
+      <c r="T177" s="6"/>
+      <c r="U177" s="6"/>
+      <c r="V177" s="6"/>
+      <c r="W177" s="6"/>
+      <c r="X177" s="6"/>
+      <c r="Y177" s="6"/>
+      <c r="Z177" s="6"/>
+      <c r="AA177" s="6"/>
+      <c r="AB177" s="6"/>
+      <c r="AC177" s="6"/>
+      <c r="AD177" s="6"/>
+      <c r="AE177" s="6"/>
+      <c r="AF177" s="6"/>
     </row>
     <row r="178" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B178" s="5" t="s">
@@ -5233,13 +8562,32 @@
       <c r="I178">
         <v>37</v>
       </c>
-      <c r="W178">
+      <c r="L178" s="6"/>
+      <c r="M178" s="6"/>
+      <c r="N178" s="6"/>
+      <c r="O178" s="6"/>
+      <c r="P178" s="6"/>
+      <c r="Q178" s="6"/>
+      <c r="R178" s="6"/>
+      <c r="S178" s="6"/>
+      <c r="T178" s="6"/>
+      <c r="U178" s="6"/>
+      <c r="V178" s="6"/>
+      <c r="W178" s="6">
         <v>78.180000000000007</v>
       </c>
-      <c r="X178">
+      <c r="X178" s="6">
         <f>18.75+12+36.95</f>
         <v>67.7</v>
       </c>
+      <c r="Y178" s="6"/>
+      <c r="Z178" s="6"/>
+      <c r="AA178" s="6"/>
+      <c r="AB178" s="6"/>
+      <c r="AC178" s="6"/>
+      <c r="AD178" s="6"/>
+      <c r="AE178" s="6"/>
+      <c r="AF178" s="6"/>
       <c r="AG178" t="s">
         <v>114</v>
       </c>
@@ -5260,10 +8608,30 @@
       <c r="F179" s="5">
         <v>55.83</v>
       </c>
-      <c r="X179">
+      <c r="L179" s="6"/>
+      <c r="M179" s="6"/>
+      <c r="N179" s="6"/>
+      <c r="O179" s="6"/>
+      <c r="P179" s="6"/>
+      <c r="Q179" s="6"/>
+      <c r="R179" s="6"/>
+      <c r="S179" s="6"/>
+      <c r="T179" s="6"/>
+      <c r="U179" s="6"/>
+      <c r="V179" s="6"/>
+      <c r="W179" s="6"/>
+      <c r="X179" s="6">
         <f>34.75+6.11+14.97</f>
         <v>55.83</v>
       </c>
+      <c r="Y179" s="6"/>
+      <c r="Z179" s="6"/>
+      <c r="AA179" s="6"/>
+      <c r="AB179" s="6"/>
+      <c r="AC179" s="6"/>
+      <c r="AD179" s="6"/>
+      <c r="AE179" s="6"/>
+      <c r="AF179" s="6"/>
       <c r="AG179" t="s">
         <v>114</v>
       </c>
@@ -5278,6 +8646,27 @@
       <c r="D180" t="s">
         <v>6</v>
       </c>
+      <c r="L180" s="6"/>
+      <c r="M180" s="6"/>
+      <c r="N180" s="6"/>
+      <c r="O180" s="6"/>
+      <c r="P180" s="6"/>
+      <c r="Q180" s="6"/>
+      <c r="R180" s="6"/>
+      <c r="S180" s="6"/>
+      <c r="T180" s="6"/>
+      <c r="U180" s="6"/>
+      <c r="V180" s="6"/>
+      <c r="W180" s="6"/>
+      <c r="X180" s="6"/>
+      <c r="Y180" s="6"/>
+      <c r="Z180" s="6"/>
+      <c r="AA180" s="6"/>
+      <c r="AB180" s="6"/>
+      <c r="AC180" s="6"/>
+      <c r="AD180" s="6"/>
+      <c r="AE180" s="6"/>
+      <c r="AF180" s="6"/>
     </row>
     <row r="181" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B181" t="s">
@@ -5292,6 +8681,27 @@
       <c r="E181">
         <v>226.5</v>
       </c>
+      <c r="L181" s="6"/>
+      <c r="M181" s="6"/>
+      <c r="N181" s="6"/>
+      <c r="O181" s="6"/>
+      <c r="P181" s="6"/>
+      <c r="Q181" s="6"/>
+      <c r="R181" s="6"/>
+      <c r="S181" s="6"/>
+      <c r="T181" s="6"/>
+      <c r="U181" s="6"/>
+      <c r="V181" s="6"/>
+      <c r="W181" s="6"/>
+      <c r="X181" s="6"/>
+      <c r="Y181" s="6"/>
+      <c r="Z181" s="6"/>
+      <c r="AA181" s="6"/>
+      <c r="AB181" s="6"/>
+      <c r="AC181" s="6"/>
+      <c r="AD181" s="6"/>
+      <c r="AE181" s="6"/>
+      <c r="AF181" s="6"/>
     </row>
     <row r="182" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B182" t="s">
@@ -5309,6 +8719,27 @@
       <c r="I182">
         <v>87</v>
       </c>
+      <c r="L182" s="6"/>
+      <c r="M182" s="6"/>
+      <c r="N182" s="6"/>
+      <c r="O182" s="6"/>
+      <c r="P182" s="6"/>
+      <c r="Q182" s="6"/>
+      <c r="R182" s="6"/>
+      <c r="S182" s="6"/>
+      <c r="T182" s="6"/>
+      <c r="U182" s="6"/>
+      <c r="V182" s="6"/>
+      <c r="W182" s="6"/>
+      <c r="X182" s="6"/>
+      <c r="Y182" s="6"/>
+      <c r="Z182" s="6"/>
+      <c r="AA182" s="6"/>
+      <c r="AB182" s="6"/>
+      <c r="AC182" s="6"/>
+      <c r="AD182" s="6"/>
+      <c r="AE182" s="6"/>
+      <c r="AF182" s="6"/>
     </row>
     <row r="183" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B183" t="s">
@@ -5323,6 +8754,27 @@
       <c r="E183">
         <v>244.5</v>
       </c>
+      <c r="L183" s="6"/>
+      <c r="M183" s="6"/>
+      <c r="N183" s="6"/>
+      <c r="O183" s="6"/>
+      <c r="P183" s="6"/>
+      <c r="Q183" s="6"/>
+      <c r="R183" s="6"/>
+      <c r="S183" s="6"/>
+      <c r="T183" s="6"/>
+      <c r="U183" s="6"/>
+      <c r="V183" s="6"/>
+      <c r="W183" s="6"/>
+      <c r="X183" s="6"/>
+      <c r="Y183" s="6"/>
+      <c r="Z183" s="6"/>
+      <c r="AA183" s="6"/>
+      <c r="AB183" s="6"/>
+      <c r="AC183" s="6"/>
+      <c r="AD183" s="6"/>
+      <c r="AE183" s="6"/>
+      <c r="AF183" s="6"/>
     </row>
     <row r="184" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B184" t="s">
@@ -5334,6 +8786,27 @@
       <c r="D184" t="s">
         <v>6</v>
       </c>
+      <c r="L184" s="6"/>
+      <c r="M184" s="6"/>
+      <c r="N184" s="6"/>
+      <c r="O184" s="6"/>
+      <c r="P184" s="6"/>
+      <c r="Q184" s="6"/>
+      <c r="R184" s="6"/>
+      <c r="S184" s="6"/>
+      <c r="T184" s="6"/>
+      <c r="U184" s="6"/>
+      <c r="V184" s="6"/>
+      <c r="W184" s="6"/>
+      <c r="X184" s="6"/>
+      <c r="Y184" s="6"/>
+      <c r="Z184" s="6"/>
+      <c r="AA184" s="6"/>
+      <c r="AB184" s="6"/>
+      <c r="AC184" s="6"/>
+      <c r="AD184" s="6"/>
+      <c r="AE184" s="6"/>
+      <c r="AF184" s="6"/>
     </row>
     <row r="185" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B185" t="s">
@@ -5348,6 +8821,27 @@
       <c r="E185">
         <v>338.5</v>
       </c>
+      <c r="L185" s="6"/>
+      <c r="M185" s="6"/>
+      <c r="N185" s="6"/>
+      <c r="O185" s="6"/>
+      <c r="P185" s="6"/>
+      <c r="Q185" s="6"/>
+      <c r="R185" s="6"/>
+      <c r="S185" s="6"/>
+      <c r="T185" s="6"/>
+      <c r="U185" s="6"/>
+      <c r="V185" s="6"/>
+      <c r="W185" s="6"/>
+      <c r="X185" s="6"/>
+      <c r="Y185" s="6"/>
+      <c r="Z185" s="6"/>
+      <c r="AA185" s="6"/>
+      <c r="AB185" s="6"/>
+      <c r="AC185" s="6"/>
+      <c r="AD185" s="6"/>
+      <c r="AE185" s="6"/>
+      <c r="AF185" s="6"/>
     </row>
     <row r="186" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B186" t="s">
@@ -5359,6 +8853,27 @@
       <c r="D186" t="s">
         <v>6</v>
       </c>
+      <c r="L186" s="6"/>
+      <c r="M186" s="6"/>
+      <c r="N186" s="6"/>
+      <c r="O186" s="6"/>
+      <c r="P186" s="6"/>
+      <c r="Q186" s="6"/>
+      <c r="R186" s="6"/>
+      <c r="S186" s="6"/>
+      <c r="T186" s="6"/>
+      <c r="U186" s="6"/>
+      <c r="V186" s="6"/>
+      <c r="W186" s="6"/>
+      <c r="X186" s="6"/>
+      <c r="Y186" s="6"/>
+      <c r="Z186" s="6"/>
+      <c r="AA186" s="6"/>
+      <c r="AB186" s="6"/>
+      <c r="AC186" s="6"/>
+      <c r="AD186" s="6"/>
+      <c r="AE186" s="6"/>
+      <c r="AF186" s="6"/>
     </row>
     <row r="187" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B187" t="s">
@@ -5373,6 +8888,27 @@
       <c r="E187">
         <v>238</v>
       </c>
+      <c r="L187" s="6"/>
+      <c r="M187" s="6"/>
+      <c r="N187" s="6"/>
+      <c r="O187" s="6"/>
+      <c r="P187" s="6"/>
+      <c r="Q187" s="6"/>
+      <c r="R187" s="6"/>
+      <c r="S187" s="6"/>
+      <c r="T187" s="6"/>
+      <c r="U187" s="6"/>
+      <c r="V187" s="6"/>
+      <c r="W187" s="6"/>
+      <c r="X187" s="6"/>
+      <c r="Y187" s="6"/>
+      <c r="Z187" s="6"/>
+      <c r="AA187" s="6"/>
+      <c r="AB187" s="6"/>
+      <c r="AC187" s="6"/>
+      <c r="AD187" s="6"/>
+      <c r="AE187" s="6"/>
+      <c r="AF187" s="6"/>
     </row>
     <row r="188" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B188" t="s">
@@ -5384,6 +8920,27 @@
       <c r="D188" t="s">
         <v>6</v>
       </c>
+      <c r="L188" s="6"/>
+      <c r="M188" s="6"/>
+      <c r="N188" s="6"/>
+      <c r="O188" s="6"/>
+      <c r="P188" s="6"/>
+      <c r="Q188" s="6"/>
+      <c r="R188" s="6"/>
+      <c r="S188" s="6"/>
+      <c r="T188" s="6"/>
+      <c r="U188" s="6"/>
+      <c r="V188" s="6"/>
+      <c r="W188" s="6"/>
+      <c r="X188" s="6"/>
+      <c r="Y188" s="6"/>
+      <c r="Z188" s="6"/>
+      <c r="AA188" s="6"/>
+      <c r="AB188" s="6"/>
+      <c r="AC188" s="6"/>
+      <c r="AD188" s="6"/>
+      <c r="AE188" s="6"/>
+      <c r="AF188" s="6"/>
     </row>
     <row r="189" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B189" t="s">
@@ -5398,6 +8955,27 @@
       <c r="E189">
         <v>69</v>
       </c>
+      <c r="L189" s="6"/>
+      <c r="M189" s="6"/>
+      <c r="N189" s="6"/>
+      <c r="O189" s="6"/>
+      <c r="P189" s="6"/>
+      <c r="Q189" s="6"/>
+      <c r="R189" s="6"/>
+      <c r="S189" s="6"/>
+      <c r="T189" s="6"/>
+      <c r="U189" s="6"/>
+      <c r="V189" s="6"/>
+      <c r="W189" s="6"/>
+      <c r="X189" s="6"/>
+      <c r="Y189" s="6"/>
+      <c r="Z189" s="6"/>
+      <c r="AA189" s="6"/>
+      <c r="AB189" s="6"/>
+      <c r="AC189" s="6"/>
+      <c r="AD189" s="6"/>
+      <c r="AE189" s="6"/>
+      <c r="AF189" s="6"/>
     </row>
     <row r="190" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B190" t="s">
@@ -5409,6 +8987,27 @@
       <c r="D190" t="s">
         <v>6</v>
       </c>
+      <c r="L190" s="6"/>
+      <c r="M190" s="6"/>
+      <c r="N190" s="6"/>
+      <c r="O190" s="6"/>
+      <c r="P190" s="6"/>
+      <c r="Q190" s="6"/>
+      <c r="R190" s="6"/>
+      <c r="S190" s="6"/>
+      <c r="T190" s="6"/>
+      <c r="U190" s="6"/>
+      <c r="V190" s="6"/>
+      <c r="W190" s="6"/>
+      <c r="X190" s="6"/>
+      <c r="Y190" s="6"/>
+      <c r="Z190" s="6"/>
+      <c r="AA190" s="6"/>
+      <c r="AB190" s="6"/>
+      <c r="AC190" s="6"/>
+      <c r="AD190" s="6"/>
+      <c r="AE190" s="6"/>
+      <c r="AF190" s="6"/>
     </row>
     <row r="191" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B191" t="s">
@@ -5423,6 +9022,27 @@
       <c r="E191">
         <v>140</v>
       </c>
+      <c r="L191" s="6"/>
+      <c r="M191" s="6"/>
+      <c r="N191" s="6"/>
+      <c r="O191" s="6"/>
+      <c r="P191" s="6"/>
+      <c r="Q191" s="6"/>
+      <c r="R191" s="6"/>
+      <c r="S191" s="6"/>
+      <c r="T191" s="6"/>
+      <c r="U191" s="6"/>
+      <c r="V191" s="6"/>
+      <c r="W191" s="6"/>
+      <c r="X191" s="6"/>
+      <c r="Y191" s="6"/>
+      <c r="Z191" s="6"/>
+      <c r="AA191" s="6"/>
+      <c r="AB191" s="6"/>
+      <c r="AC191" s="6"/>
+      <c r="AD191" s="6"/>
+      <c r="AE191" s="6"/>
+      <c r="AF191" s="6"/>
     </row>
     <row r="192" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B192" t="s">
@@ -5434,6 +9054,27 @@
       <c r="D192" t="s">
         <v>6</v>
       </c>
+      <c r="L192" s="6"/>
+      <c r="M192" s="6"/>
+      <c r="N192" s="6"/>
+      <c r="O192" s="6"/>
+      <c r="P192" s="6"/>
+      <c r="Q192" s="6"/>
+      <c r="R192" s="6"/>
+      <c r="S192" s="6"/>
+      <c r="T192" s="6"/>
+      <c r="U192" s="6"/>
+      <c r="V192" s="6"/>
+      <c r="W192" s="6"/>
+      <c r="X192" s="6"/>
+      <c r="Y192" s="6"/>
+      <c r="Z192" s="6"/>
+      <c r="AA192" s="6"/>
+      <c r="AB192" s="6"/>
+      <c r="AC192" s="6"/>
+      <c r="AD192" s="6"/>
+      <c r="AE192" s="6"/>
+      <c r="AF192" s="6"/>
       <c r="AG192" t="s">
         <v>115</v>
       </c>
@@ -5451,6 +9092,27 @@
       <c r="E193">
         <v>858.5</v>
       </c>
+      <c r="L193" s="6"/>
+      <c r="M193" s="6"/>
+      <c r="N193" s="6"/>
+      <c r="O193" s="6"/>
+      <c r="P193" s="6"/>
+      <c r="Q193" s="6"/>
+      <c r="R193" s="6"/>
+      <c r="S193" s="6"/>
+      <c r="T193" s="6"/>
+      <c r="U193" s="6"/>
+      <c r="V193" s="6"/>
+      <c r="W193" s="6"/>
+      <c r="X193" s="6"/>
+      <c r="Y193" s="6"/>
+      <c r="Z193" s="6"/>
+      <c r="AA193" s="6"/>
+      <c r="AB193" s="6"/>
+      <c r="AC193" s="6"/>
+      <c r="AD193" s="6"/>
+      <c r="AE193" s="6"/>
+      <c r="AF193" s="6"/>
     </row>
     <row r="194" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B194" t="s">
@@ -5462,6 +9124,27 @@
       <c r="D194" t="s">
         <v>6</v>
       </c>
+      <c r="L194" s="6"/>
+      <c r="M194" s="6"/>
+      <c r="N194" s="6"/>
+      <c r="O194" s="6"/>
+      <c r="P194" s="6"/>
+      <c r="Q194" s="6"/>
+      <c r="R194" s="6"/>
+      <c r="S194" s="6"/>
+      <c r="T194" s="6"/>
+      <c r="U194" s="6"/>
+      <c r="V194" s="6"/>
+      <c r="W194" s="6"/>
+      <c r="X194" s="6"/>
+      <c r="Y194" s="6"/>
+      <c r="Z194" s="6"/>
+      <c r="AA194" s="6"/>
+      <c r="AB194" s="6"/>
+      <c r="AC194" s="6"/>
+      <c r="AD194" s="6"/>
+      <c r="AE194" s="6"/>
+      <c r="AF194" s="6"/>
     </row>
     <row r="195" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B195" t="s">
@@ -5476,6 +9159,27 @@
       <c r="E195">
         <v>168</v>
       </c>
+      <c r="L195" s="6"/>
+      <c r="M195" s="6"/>
+      <c r="N195" s="6"/>
+      <c r="O195" s="6"/>
+      <c r="P195" s="6"/>
+      <c r="Q195" s="6"/>
+      <c r="R195" s="6"/>
+      <c r="S195" s="6"/>
+      <c r="T195" s="6"/>
+      <c r="U195" s="6"/>
+      <c r="V195" s="6"/>
+      <c r="W195" s="6"/>
+      <c r="X195" s="6"/>
+      <c r="Y195" s="6"/>
+      <c r="Z195" s="6"/>
+      <c r="AA195" s="6"/>
+      <c r="AB195" s="6"/>
+      <c r="AC195" s="6"/>
+      <c r="AD195" s="6"/>
+      <c r="AE195" s="6"/>
+      <c r="AF195" s="6"/>
     </row>
     <row r="196" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B196" t="s">
@@ -5487,6 +9191,27 @@
       <c r="D196" t="s">
         <v>6</v>
       </c>
+      <c r="L196" s="6"/>
+      <c r="M196" s="6"/>
+      <c r="N196" s="6"/>
+      <c r="O196" s="6"/>
+      <c r="P196" s="6"/>
+      <c r="Q196" s="6"/>
+      <c r="R196" s="6"/>
+      <c r="S196" s="6"/>
+      <c r="T196" s="6"/>
+      <c r="U196" s="6"/>
+      <c r="V196" s="6"/>
+      <c r="W196" s="6"/>
+      <c r="X196" s="6"/>
+      <c r="Y196" s="6"/>
+      <c r="Z196" s="6"/>
+      <c r="AA196" s="6"/>
+      <c r="AB196" s="6"/>
+      <c r="AC196" s="6"/>
+      <c r="AD196" s="6"/>
+      <c r="AE196" s="6"/>
+      <c r="AF196" s="6"/>
     </row>
     <row r="197" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B197" t="s">
@@ -5501,6 +9226,27 @@
       <c r="E197">
         <v>180</v>
       </c>
+      <c r="L197" s="6"/>
+      <c r="M197" s="6"/>
+      <c r="N197" s="6"/>
+      <c r="O197" s="6"/>
+      <c r="P197" s="6"/>
+      <c r="Q197" s="6"/>
+      <c r="R197" s="6"/>
+      <c r="S197" s="6"/>
+      <c r="T197" s="6"/>
+      <c r="U197" s="6"/>
+      <c r="V197" s="6"/>
+      <c r="W197" s="6"/>
+      <c r="X197" s="6"/>
+      <c r="Y197" s="6"/>
+      <c r="Z197" s="6"/>
+      <c r="AA197" s="6"/>
+      <c r="AB197" s="6"/>
+      <c r="AC197" s="6"/>
+      <c r="AD197" s="6"/>
+      <c r="AE197" s="6"/>
+      <c r="AF197" s="6"/>
     </row>
     <row r="198" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B198" t="s">
@@ -5515,6 +9261,27 @@
       <c r="I198">
         <v>182</v>
       </c>
+      <c r="L198" s="6"/>
+      <c r="M198" s="6"/>
+      <c r="N198" s="6"/>
+      <c r="O198" s="6"/>
+      <c r="P198" s="6"/>
+      <c r="Q198" s="6"/>
+      <c r="R198" s="6"/>
+      <c r="S198" s="6"/>
+      <c r="T198" s="6"/>
+      <c r="U198" s="6"/>
+      <c r="V198" s="6"/>
+      <c r="W198" s="6"/>
+      <c r="X198" s="6"/>
+      <c r="Y198" s="6"/>
+      <c r="Z198" s="6"/>
+      <c r="AA198" s="6"/>
+      <c r="AB198" s="6"/>
+      <c r="AC198" s="6"/>
+      <c r="AD198" s="6"/>
+      <c r="AE198" s="6"/>
+      <c r="AF198" s="6"/>
     </row>
     <row r="199" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B199" t="s">
@@ -5529,6 +9296,27 @@
       <c r="E199">
         <v>238.52</v>
       </c>
+      <c r="L199" s="6"/>
+      <c r="M199" s="6"/>
+      <c r="N199" s="6"/>
+      <c r="O199" s="6"/>
+      <c r="P199" s="6"/>
+      <c r="Q199" s="6"/>
+      <c r="R199" s="6"/>
+      <c r="S199" s="6"/>
+      <c r="T199" s="6"/>
+      <c r="U199" s="6"/>
+      <c r="V199" s="6"/>
+      <c r="W199" s="6"/>
+      <c r="X199" s="6"/>
+      <c r="Y199" s="6"/>
+      <c r="Z199" s="6"/>
+      <c r="AA199" s="6"/>
+      <c r="AB199" s="6"/>
+      <c r="AC199" s="6"/>
+      <c r="AD199" s="6"/>
+      <c r="AE199" s="6"/>
+      <c r="AF199" s="6"/>
     </row>
     <row r="200" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B200" t="s">
@@ -5540,6 +9328,27 @@
       <c r="D200" t="s">
         <v>6</v>
       </c>
+      <c r="L200" s="6"/>
+      <c r="M200" s="6"/>
+      <c r="N200" s="6"/>
+      <c r="O200" s="6"/>
+      <c r="P200" s="6"/>
+      <c r="Q200" s="6"/>
+      <c r="R200" s="6"/>
+      <c r="S200" s="6"/>
+      <c r="T200" s="6"/>
+      <c r="U200" s="6"/>
+      <c r="V200" s="6"/>
+      <c r="W200" s="6"/>
+      <c r="X200" s="6"/>
+      <c r="Y200" s="6"/>
+      <c r="Z200" s="6"/>
+      <c r="AA200" s="6"/>
+      <c r="AB200" s="6"/>
+      <c r="AC200" s="6"/>
+      <c r="AD200" s="6"/>
+      <c r="AE200" s="6"/>
+      <c r="AF200" s="6"/>
     </row>
     <row r="201" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B201" t="s">
@@ -5554,6 +9363,27 @@
       <c r="E201">
         <v>229.5</v>
       </c>
+      <c r="L201" s="6"/>
+      <c r="M201" s="6"/>
+      <c r="N201" s="6"/>
+      <c r="O201" s="6"/>
+      <c r="P201" s="6"/>
+      <c r="Q201" s="6"/>
+      <c r="R201" s="6"/>
+      <c r="S201" s="6"/>
+      <c r="T201" s="6"/>
+      <c r="U201" s="6"/>
+      <c r="V201" s="6"/>
+      <c r="W201" s="6"/>
+      <c r="X201" s="6"/>
+      <c r="Y201" s="6"/>
+      <c r="Z201" s="6"/>
+      <c r="AA201" s="6"/>
+      <c r="AB201" s="6"/>
+      <c r="AC201" s="6"/>
+      <c r="AD201" s="6"/>
+      <c r="AE201" s="6"/>
+      <c r="AF201" s="6"/>
     </row>
     <row r="202" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B202" t="s">
@@ -5565,6 +9395,27 @@
       <c r="D202" t="s">
         <v>6</v>
       </c>
+      <c r="L202" s="6"/>
+      <c r="M202" s="6"/>
+      <c r="N202" s="6"/>
+      <c r="O202" s="6"/>
+      <c r="P202" s="6"/>
+      <c r="Q202" s="6"/>
+      <c r="R202" s="6"/>
+      <c r="S202" s="6"/>
+      <c r="T202" s="6"/>
+      <c r="U202" s="6"/>
+      <c r="V202" s="6"/>
+      <c r="W202" s="6"/>
+      <c r="X202" s="6"/>
+      <c r="Y202" s="6"/>
+      <c r="Z202" s="6"/>
+      <c r="AA202" s="6"/>
+      <c r="AB202" s="6"/>
+      <c r="AC202" s="6"/>
+      <c r="AD202" s="6"/>
+      <c r="AE202" s="6"/>
+      <c r="AF202" s="6"/>
     </row>
     <row r="203" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B203" t="s">
@@ -5579,6 +9430,27 @@
       <c r="E203">
         <v>1566.27</v>
       </c>
+      <c r="L203" s="6"/>
+      <c r="M203" s="6"/>
+      <c r="N203" s="6"/>
+      <c r="O203" s="6"/>
+      <c r="P203" s="6"/>
+      <c r="Q203" s="6"/>
+      <c r="R203" s="6"/>
+      <c r="S203" s="6"/>
+      <c r="T203" s="6"/>
+      <c r="U203" s="6"/>
+      <c r="V203" s="6"/>
+      <c r="W203" s="6"/>
+      <c r="X203" s="6"/>
+      <c r="Y203" s="6"/>
+      <c r="Z203" s="6"/>
+      <c r="AA203" s="6"/>
+      <c r="AB203" s="6"/>
+      <c r="AC203" s="6"/>
+      <c r="AD203" s="6"/>
+      <c r="AE203" s="6"/>
+      <c r="AF203" s="6"/>
     </row>
     <row r="204" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B204" t="s">
@@ -5590,6 +9462,27 @@
       <c r="D204" t="s">
         <v>6</v>
       </c>
+      <c r="L204" s="6"/>
+      <c r="M204" s="6"/>
+      <c r="N204" s="6"/>
+      <c r="O204" s="6"/>
+      <c r="P204" s="6"/>
+      <c r="Q204" s="6"/>
+      <c r="R204" s="6"/>
+      <c r="S204" s="6"/>
+      <c r="T204" s="6"/>
+      <c r="U204" s="6"/>
+      <c r="V204" s="6"/>
+      <c r="W204" s="6"/>
+      <c r="X204" s="6"/>
+      <c r="Y204" s="6"/>
+      <c r="Z204" s="6"/>
+      <c r="AA204" s="6"/>
+      <c r="AB204" s="6"/>
+      <c r="AC204" s="6"/>
+      <c r="AD204" s="6"/>
+      <c r="AE204" s="6"/>
+      <c r="AF204" s="6"/>
     </row>
     <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
@@ -5604,6 +9497,27 @@
       <c r="E205">
         <v>95</v>
       </c>
+      <c r="L205" s="6"/>
+      <c r="M205" s="6"/>
+      <c r="N205" s="6"/>
+      <c r="O205" s="6"/>
+      <c r="P205" s="6"/>
+      <c r="Q205" s="6"/>
+      <c r="R205" s="6"/>
+      <c r="S205" s="6"/>
+      <c r="T205" s="6"/>
+      <c r="U205" s="6"/>
+      <c r="V205" s="6"/>
+      <c r="W205" s="6"/>
+      <c r="X205" s="6"/>
+      <c r="Y205" s="6"/>
+      <c r="Z205" s="6"/>
+      <c r="AA205" s="6"/>
+      <c r="AB205" s="6"/>
+      <c r="AC205" s="6"/>
+      <c r="AD205" s="6"/>
+      <c r="AE205" s="6"/>
+      <c r="AF205" s="6"/>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="s">
@@ -5621,9 +9535,29 @@
       <c r="F206" s="5">
         <v>34.57</v>
       </c>
-      <c r="V206">
+      <c r="L206" s="6"/>
+      <c r="M206" s="6"/>
+      <c r="N206" s="6"/>
+      <c r="O206" s="6"/>
+      <c r="P206" s="6"/>
+      <c r="Q206" s="6"/>
+      <c r="R206" s="6"/>
+      <c r="S206" s="6"/>
+      <c r="T206" s="6"/>
+      <c r="U206" s="6"/>
+      <c r="V206" s="6">
         <v>34.57</v>
       </c>
+      <c r="W206" s="6"/>
+      <c r="X206" s="6"/>
+      <c r="Y206" s="6"/>
+      <c r="Z206" s="6"/>
+      <c r="AA206" s="6"/>
+      <c r="AB206" s="6"/>
+      <c r="AC206" s="6"/>
+      <c r="AD206" s="6"/>
+      <c r="AE206" s="6"/>
+      <c r="AF206" s="6"/>
       <c r="AG206" t="s">
         <v>114</v>
       </c>
@@ -5641,6 +9575,27 @@
       <c r="E207">
         <v>158</v>
       </c>
+      <c r="L207" s="6"/>
+      <c r="M207" s="6"/>
+      <c r="N207" s="6"/>
+      <c r="O207" s="6"/>
+      <c r="P207" s="6"/>
+      <c r="Q207" s="6"/>
+      <c r="R207" s="6"/>
+      <c r="S207" s="6"/>
+      <c r="T207" s="6"/>
+      <c r="U207" s="6"/>
+      <c r="V207" s="6"/>
+      <c r="W207" s="6"/>
+      <c r="X207" s="6"/>
+      <c r="Y207" s="6"/>
+      <c r="Z207" s="6"/>
+      <c r="AA207" s="6"/>
+      <c r="AB207" s="6"/>
+      <c r="AC207" s="6"/>
+      <c r="AD207" s="6"/>
+      <c r="AE207" s="6"/>
+      <c r="AF207" s="6"/>
       <c r="AG207" t="s">
         <v>114</v>
       </c>
@@ -5667,9 +9622,29 @@
       <c r="J208">
         <v>27</v>
       </c>
-      <c r="S208">
+      <c r="L208" s="6"/>
+      <c r="M208" s="6"/>
+      <c r="N208" s="6"/>
+      <c r="O208" s="6"/>
+      <c r="P208" s="6"/>
+      <c r="Q208" s="6"/>
+      <c r="R208" s="6"/>
+      <c r="S208" s="6">
         <v>300.68</v>
       </c>
+      <c r="T208" s="6"/>
+      <c r="U208" s="6"/>
+      <c r="V208" s="6"/>
+      <c r="W208" s="6"/>
+      <c r="X208" s="6"/>
+      <c r="Y208" s="6"/>
+      <c r="Z208" s="6"/>
+      <c r="AA208" s="6"/>
+      <c r="AB208" s="6"/>
+      <c r="AC208" s="6"/>
+      <c r="AD208" s="6"/>
+      <c r="AE208" s="6"/>
+      <c r="AF208" s="6"/>
       <c r="AG208" t="s">
         <v>114</v>
       </c>
@@ -5690,15 +9665,33 @@
       <c r="F209" s="5">
         <v>337.46</v>
       </c>
-      <c r="Q209">
+      <c r="L209" s="6"/>
+      <c r="M209" s="6"/>
+      <c r="N209" s="6"/>
+      <c r="O209" s="6"/>
+      <c r="P209" s="6"/>
+      <c r="Q209" s="6">
         <v>127.69</v>
       </c>
-      <c r="W209">
+      <c r="R209" s="6"/>
+      <c r="S209" s="6"/>
+      <c r="T209" s="6"/>
+      <c r="U209" s="6"/>
+      <c r="V209" s="6"/>
+      <c r="W209" s="6">
         <v>42</v>
       </c>
-      <c r="X209">
+      <c r="X209" s="6">
         <v>167.77</v>
       </c>
+      <c r="Y209" s="6"/>
+      <c r="Z209" s="6"/>
+      <c r="AA209" s="6"/>
+      <c r="AB209" s="6"/>
+      <c r="AC209" s="6"/>
+      <c r="AD209" s="6"/>
+      <c r="AE209" s="6"/>
+      <c r="AF209" s="6"/>
       <c r="AG209" t="s">
         <v>114</v>
       </c>
@@ -5716,6 +9709,27 @@
       <c r="E210">
         <v>100.2</v>
       </c>
+      <c r="L210" s="6"/>
+      <c r="M210" s="6"/>
+      <c r="N210" s="6"/>
+      <c r="O210" s="6"/>
+      <c r="P210" s="6"/>
+      <c r="Q210" s="6"/>
+      <c r="R210" s="6"/>
+      <c r="S210" s="6"/>
+      <c r="T210" s="6"/>
+      <c r="U210" s="6"/>
+      <c r="V210" s="6"/>
+      <c r="W210" s="6"/>
+      <c r="X210" s="6"/>
+      <c r="Y210" s="6"/>
+      <c r="Z210" s="6"/>
+      <c r="AA210" s="6"/>
+      <c r="AB210" s="6"/>
+      <c r="AC210" s="6"/>
+      <c r="AD210" s="6"/>
+      <c r="AE210" s="6"/>
+      <c r="AF210" s="6"/>
     </row>
     <row r="211" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B211" t="s">
@@ -5730,6 +9744,27 @@
       <c r="E211">
         <v>253.5</v>
       </c>
+      <c r="L211" s="6"/>
+      <c r="M211" s="6"/>
+      <c r="N211" s="6"/>
+      <c r="O211" s="6"/>
+      <c r="P211" s="6"/>
+      <c r="Q211" s="6"/>
+      <c r="R211" s="6"/>
+      <c r="S211" s="6"/>
+      <c r="T211" s="6"/>
+      <c r="U211" s="6"/>
+      <c r="V211" s="6"/>
+      <c r="W211" s="6"/>
+      <c r="X211" s="6"/>
+      <c r="Y211" s="6"/>
+      <c r="Z211" s="6"/>
+      <c r="AA211" s="6"/>
+      <c r="AB211" s="6"/>
+      <c r="AC211" s="6"/>
+      <c r="AD211" s="6"/>
+      <c r="AE211" s="6"/>
+      <c r="AF211" s="6"/>
     </row>
     <row r="212" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B212" t="s">
@@ -5744,6 +9779,27 @@
       <c r="E212">
         <v>89.9</v>
       </c>
+      <c r="L212" s="6"/>
+      <c r="M212" s="6"/>
+      <c r="N212" s="6"/>
+      <c r="O212" s="6"/>
+      <c r="P212" s="6"/>
+      <c r="Q212" s="6"/>
+      <c r="R212" s="6"/>
+      <c r="S212" s="6"/>
+      <c r="T212" s="6"/>
+      <c r="U212" s="6"/>
+      <c r="V212" s="6"/>
+      <c r="W212" s="6"/>
+      <c r="X212" s="6"/>
+      <c r="Y212" s="6"/>
+      <c r="Z212" s="6"/>
+      <c r="AA212" s="6"/>
+      <c r="AB212" s="6"/>
+      <c r="AC212" s="6"/>
+      <c r="AD212" s="6"/>
+      <c r="AE212" s="6"/>
+      <c r="AF212" s="6"/>
     </row>
     <row r="213" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B213" t="s">
@@ -5758,6 +9814,27 @@
       <c r="E213">
         <v>322.2</v>
       </c>
+      <c r="L213" s="6"/>
+      <c r="M213" s="6"/>
+      <c r="N213" s="6"/>
+      <c r="O213" s="6"/>
+      <c r="P213" s="6"/>
+      <c r="Q213" s="6"/>
+      <c r="R213" s="6"/>
+      <c r="S213" s="6"/>
+      <c r="T213" s="6"/>
+      <c r="U213" s="6"/>
+      <c r="V213" s="6"/>
+      <c r="W213" s="6"/>
+      <c r="X213" s="6"/>
+      <c r="Y213" s="6"/>
+      <c r="Z213" s="6"/>
+      <c r="AA213" s="6"/>
+      <c r="AB213" s="6"/>
+      <c r="AC213" s="6"/>
+      <c r="AD213" s="6"/>
+      <c r="AE213" s="6"/>
+      <c r="AF213" s="6"/>
     </row>
     <row r="214" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B214" t="s">
@@ -5769,6 +9846,27 @@
       <c r="D214" t="s">
         <v>6</v>
       </c>
+      <c r="L214" s="6"/>
+      <c r="M214" s="6"/>
+      <c r="N214" s="6"/>
+      <c r="O214" s="6"/>
+      <c r="P214" s="6"/>
+      <c r="Q214" s="6"/>
+      <c r="R214" s="6"/>
+      <c r="S214" s="6"/>
+      <c r="T214" s="6"/>
+      <c r="U214" s="6"/>
+      <c r="V214" s="6"/>
+      <c r="W214" s="6"/>
+      <c r="X214" s="6"/>
+      <c r="Y214" s="6"/>
+      <c r="Z214" s="6"/>
+      <c r="AA214" s="6"/>
+      <c r="AB214" s="6"/>
+      <c r="AC214" s="6"/>
+      <c r="AD214" s="6"/>
+      <c r="AE214" s="6"/>
+      <c r="AF214" s="6"/>
     </row>
     <row r="215" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B215" t="s">
@@ -5783,6 +9881,27 @@
       <c r="E215">
         <v>129.80000000000001</v>
       </c>
+      <c r="L215" s="6"/>
+      <c r="M215" s="6"/>
+      <c r="N215" s="6"/>
+      <c r="O215" s="6"/>
+      <c r="P215" s="6"/>
+      <c r="Q215" s="6"/>
+      <c r="R215" s="6"/>
+      <c r="S215" s="6"/>
+      <c r="T215" s="6"/>
+      <c r="U215" s="6"/>
+      <c r="V215" s="6"/>
+      <c r="W215" s="6"/>
+      <c r="X215" s="6"/>
+      <c r="Y215" s="6"/>
+      <c r="Z215" s="6"/>
+      <c r="AA215" s="6"/>
+      <c r="AB215" s="6"/>
+      <c r="AC215" s="6"/>
+      <c r="AD215" s="6"/>
+      <c r="AE215" s="6"/>
+      <c r="AF215" s="6"/>
     </row>
     <row r="216" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B216" t="s">
@@ -5794,6 +9913,27 @@
       <c r="D216" t="s">
         <v>6</v>
       </c>
+      <c r="L216" s="6"/>
+      <c r="M216" s="6"/>
+      <c r="N216" s="6"/>
+      <c r="O216" s="6"/>
+      <c r="P216" s="6"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="6"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="6"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="6"/>
+      <c r="AB216" s="6"/>
+      <c r="AC216" s="6"/>
+      <c r="AD216" s="6"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="6"/>
     </row>
     <row r="217" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B217" t="s">
@@ -5808,6 +9948,27 @@
       <c r="E217">
         <v>205</v>
       </c>
+      <c r="L217" s="6"/>
+      <c r="M217" s="6"/>
+      <c r="N217" s="6"/>
+      <c r="O217" s="6"/>
+      <c r="P217" s="6"/>
+      <c r="Q217" s="6"/>
+      <c r="R217" s="6"/>
+      <c r="S217" s="6"/>
+      <c r="T217" s="6"/>
+      <c r="U217" s="6"/>
+      <c r="V217" s="6"/>
+      <c r="W217" s="6"/>
+      <c r="X217" s="6"/>
+      <c r="Y217" s="6"/>
+      <c r="Z217" s="6"/>
+      <c r="AA217" s="6"/>
+      <c r="AB217" s="6"/>
+      <c r="AC217" s="6"/>
+      <c r="AD217" s="6"/>
+      <c r="AE217" s="6"/>
+      <c r="AF217" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>

--- a/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEE97603-A5C3-4271-951A-6B91FEF1BAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBF2523-B246-4AA1-AD38-80CDB183820F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -446,18 +446,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -472,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -488,7 +482,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1612,7 +1605,7 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+      <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C10">
@@ -1669,7 +1662,7 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+      <c r="B11" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C11">
@@ -1707,7 +1700,7 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C12">
@@ -1758,7 +1751,7 @@
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C13">
@@ -1799,7 +1792,7 @@
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C14">
@@ -1812,7 +1805,8 @@
         <v>240.7</v>
       </c>
       <c r="F14" s="5">
-        <v>231.85</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]</f>
+        <v>159.47499999999999</v>
       </c>
       <c r="I14">
         <v>589</v>
@@ -1825,7 +1819,8 @@
       <c r="N14" s="6"/>
       <c r="O14" s="6"/>
       <c r="P14" s="8">
-        <v>231.85</v>
+        <f>231.85-72.375</f>
+        <v>159.47499999999999</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -1848,7 +1843,7 @@
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B15" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C15">
@@ -1891,7 +1886,7 @@
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="B16" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C16">
@@ -1904,7 +1899,8 @@
         <v>0</v>
       </c>
       <c r="F16" s="5">
-        <v>367.71</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]</f>
+        <v>295.33500000000004</v>
       </c>
       <c r="I16">
         <v>614</v>
@@ -1917,7 +1913,8 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="8">
-        <v>132.27000000000001</v>
+        <f>132.27-72.375</f>
+        <v>59.89500000000001</v>
       </c>
       <c r="Q16" s="8">
         <v>235.44</v>
@@ -1942,7 +1939,7 @@
       </c>
     </row>
     <row r="17" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B17" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C17">
@@ -1959,9 +1956,7 @@
       <c r="N17" s="6"/>
       <c r="O17" s="6"/>
       <c r="P17" s="6"/>
-      <c r="Q17" s="9">
-        <v>154.93</v>
-      </c>
+      <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
       <c r="S17" s="6"/>
       <c r="T17" s="6"/>
@@ -1982,7 +1977,7 @@
       </c>
     </row>
     <row r="18" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B18" t="s">
+      <c r="B18" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C18">
@@ -2031,7 +2026,7 @@
       </c>
     </row>
     <row r="19" spans="2:33" x14ac:dyDescent="0.3">
-      <c r="B19" t="s">
+      <c r="B19" s="5" t="s">
         <v>8</v>
       </c>
       <c r="C19">
@@ -2044,14 +2039,16 @@
         <v>754</v>
       </c>
       <c r="F19" s="5">
-        <v>445.46</v>
+        <f>tb_base_dash_extensao[[#This Row],[produção Agosto 2025]]+tb_base_dash_extensao[[#This Row],[produção Setembro 2025]]+tb_base_dash_extensao[[#This Row],[produção Dezembro 2025]]</f>
+        <v>373.08500000000004</v>
       </c>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6">
-        <v>242.97</v>
+        <f>242.97-72.375</f>
+        <v>170.595</v>
       </c>
       <c r="Q19" s="6">
         <v>148.49</v>

--- a/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEBF2523-B246-4AA1-AD38-80CDB183820F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC3DEE-9F23-4662-862F-278B02A0DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="121">
   <si>
     <t>Obra</t>
   </si>
@@ -397,6 +397,9 @@
   </si>
   <si>
     <t>CT LAGEADO MONTANTE</t>
+  </si>
+  <si>
+    <t>concuido</t>
   </si>
 </sst>
 </file>
@@ -7286,7 +7289,9 @@
       <c r="V145" s="6"/>
       <c r="W145" s="6"/>
       <c r="X145" s="6"/>
-      <c r="Y145" s="6"/>
+      <c r="Y145" s="6">
+        <v>42</v>
+      </c>
       <c r="Z145" s="6"/>
       <c r="AA145" s="6"/>
       <c r="AB145" s="6"/>
@@ -7700,7 +7705,7 @@
       <c r="AE156" s="6"/>
       <c r="AF156" s="6"/>
       <c r="AG156" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="157" spans="2:33" x14ac:dyDescent="0.3">
@@ -9051,6 +9056,9 @@
       <c r="D192" t="s">
         <v>6</v>
       </c>
+      <c r="F192" s="5">
+        <v>78.19</v>
+      </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
       <c r="N192" s="6"/>
@@ -9064,7 +9072,9 @@
       <c r="V192" s="6"/>
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
-      <c r="Y192" s="6"/>
+      <c r="Y192" s="6">
+        <v>78.19</v>
+      </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>
       <c r="AB192" s="6"/>

--- a/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC3DEE-9F23-4662-862F-278B02A0DDE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA6F4DA-0E96-4337-9D01-E8E0A6C3B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BASE_DASH_EXTENSAO" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="634" uniqueCount="121">
   <si>
     <t>Obra</t>
   </si>
@@ -7272,7 +7272,7 @@
         <v>1799.2</v>
       </c>
       <c r="F145" s="5">
-        <v>9</v>
+        <v>81</v>
       </c>
       <c r="L145" s="6"/>
       <c r="M145" s="6"/>
@@ -7290,7 +7290,7 @@
       <c r="W145" s="6"/>
       <c r="X145" s="6"/>
       <c r="Y145" s="6">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="Z145" s="6"/>
       <c r="AA145" s="6"/>
@@ -7743,7 +7743,9 @@
       <c r="X157" s="6">
         <v>8.81</v>
       </c>
-      <c r="Y157" s="6"/>
+      <c r="Y157" s="6">
+        <v>70.84</v>
+      </c>
       <c r="Z157" s="6"/>
       <c r="AA157" s="6"/>
       <c r="AB157" s="6"/>
@@ -7752,7 +7754,7 @@
       <c r="AE157" s="6"/>
       <c r="AF157" s="6"/>
       <c r="AG157" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="158" spans="2:33" x14ac:dyDescent="0.3">
@@ -7810,7 +7812,7 @@
       <c r="AE158" s="6"/>
       <c r="AF158" s="6"/>
       <c r="AG158" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="2:33" x14ac:dyDescent="0.3">
@@ -7844,7 +7846,10 @@
         <v>65.599999999999994</v>
       </c>
       <c r="X159" s="6"/>
-      <c r="Y159" s="6"/>
+      <c r="Y159" s="6">
+        <f>14.84+38.87+23.3</f>
+        <v>77.009999999999991</v>
+      </c>
       <c r="Z159" s="6"/>
       <c r="AA159" s="6"/>
       <c r="AB159" s="6"/>
@@ -7853,7 +7858,7 @@
       <c r="AE159" s="6"/>
       <c r="AF159" s="6"/>
       <c r="AG159" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="160" spans="2:33" x14ac:dyDescent="0.3">
@@ -7902,7 +7907,7 @@
       <c r="AE160" s="6"/>
       <c r="AF160" s="6"/>
       <c r="AG160" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="161" spans="2:33" x14ac:dyDescent="0.3">
@@ -7945,7 +7950,7 @@
       <c r="AE161" s="6"/>
       <c r="AF161" s="6"/>
       <c r="AG161" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
     </row>
     <row r="162" spans="2:33" x14ac:dyDescent="0.3">
@@ -8131,7 +8136,7 @@
       <c r="AE166" s="6"/>
       <c r="AF166" s="6"/>
       <c r="AG166" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="167" spans="2:33" x14ac:dyDescent="0.3">
@@ -8169,7 +8174,7 @@
       <c r="AE167" s="6"/>
       <c r="AF167" s="6"/>
       <c r="AG167" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="168" spans="2:33" x14ac:dyDescent="0.3">
@@ -8218,7 +8223,7 @@
       <c r="AE168" s="6"/>
       <c r="AF168" s="6"/>
       <c r="AG168" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="169" spans="2:33" x14ac:dyDescent="0.3">
@@ -8250,8 +8255,7 @@
       <c r="V169" s="6"/>
       <c r="W169" s="6"/>
       <c r="X169" s="6">
-        <f>11.35+17.44+12.11</f>
-        <v>40.9</v>
+        <v>47.56</v>
       </c>
       <c r="Y169" s="6"/>
       <c r="Z169" s="6"/>
@@ -8262,7 +8266,7 @@
       <c r="AE169" s="6"/>
       <c r="AF169" s="6"/>
       <c r="AG169" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="170" spans="2:33" x14ac:dyDescent="0.3">
@@ -9057,7 +9061,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="5">
-        <v>78.19</v>
+        <v>158.69999999999999</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
@@ -9073,7 +9077,8 @@
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6">
-        <v>78.19</v>
+        <f>78.19+80.53</f>
+        <v>158.72</v>
       </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>
@@ -9490,6 +9495,9 @@
       <c r="AD204" s="6"/>
       <c r="AE204" s="6"/>
       <c r="AF204" s="6"/>
+      <c r="AG204" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="205" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B205" t="s">
@@ -9525,6 +9533,9 @@
       <c r="AD205" s="6"/>
       <c r="AE205" s="6"/>
       <c r="AF205" s="6"/>
+      <c r="AG205" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="206" spans="2:33" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="s">

--- a/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
+++ b/doc/docs/BASE_DASH_EXTENSAO_POWERBI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCA6F4DA-0E96-4337-9D01-E8E0A6C3B1EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3201084-D6CB-45F5-AA24-265FB3B68E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9061,7 +9061,7 @@
         <v>6</v>
       </c>
       <c r="F192" s="5">
-        <v>158.69999999999999</v>
+        <v>268.02</v>
       </c>
       <c r="L192" s="6"/>
       <c r="M192" s="6"/>
@@ -9077,8 +9077,7 @@
       <c r="W192" s="6"/>
       <c r="X192" s="6"/>
       <c r="Y192" s="6">
-        <f>78.19+80.53</f>
-        <v>158.72</v>
+        <v>268.02</v>
       </c>
       <c r="Z192" s="6"/>
       <c r="AA192" s="6"/>
